--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -2027,11 +2027,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NYG +1.5</t>
+          <t>NYG +2.5</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2045,17 +2045,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I24" t="n">
         <v>1.8</v>
       </c>
       <c r="J24" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="K24" t="n">
-        <v>60</v>
+        <v>62.9</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
@@ -2106,13 +2106,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>55.1</v>
+        <v>54.7</v>
       </c>
       <c r="J25" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="K25" t="n">
-        <v>84.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -2141,11 +2141,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>48.5</v>
+        <v>47.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2163,13 +2163,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>39.3</v>
+        <v>38.9</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.6</v>
       </c>
       <c r="K26" t="n">
-        <v>81</v>
+        <v>79.5</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -2198,11 +2198,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HOU -2.5</t>
+          <t>HOU -3</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-2.5</v>
+        <v>-3</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
         <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>63.5</v>
+        <v>62</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
@@ -2255,11 +2255,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2273,17 +2273,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>53.4</v>
+        <v>52.9</v>
       </c>
       <c r="J28" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="K28" t="n">
-        <v>71.2</v>
+        <v>66.3</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -2312,11 +2312,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>46.5</v>
+        <v>47.5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2334,13 +2334,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>54.9</v>
+        <v>54.5</v>
       </c>
       <c r="J29" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>78.8</v>
+        <v>74.7</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
@@ -2483,11 +2483,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Over 39.5</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>39.5</v>
+        <v>38.5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2501,17 +2501,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>47.2</v>
+        <v>42.3</v>
       </c>
       <c r="J32" t="n">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="K32" t="n">
-        <v>76.90000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -2615,17 +2615,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>51.9</v>
+        <v>56</v>
       </c>
       <c r="J34" t="n">
-        <v>4.4</v>
+        <v>8.5</v>
       </c>
       <c r="K34" t="n">
-        <v>66.2</v>
+        <v>79</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -2654,11 +2654,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JAX +3</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-3</v>
+        <v>-2.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2679,10 +2679,10 @@
         <v>-9.5</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.5</v>
+        <v>-12</v>
       </c>
       <c r="K35" t="n">
-        <v>83.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>48.3</v>
+        <v>47.9</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.2</v>
+        <v>-3.6</v>
       </c>
       <c r="K36" t="n">
-        <v>61.9</v>
+        <v>63.5</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -2847,13 +2847,13 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>39.2</v>
+        <v>38.8</v>
       </c>
       <c r="J38" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>78.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
@@ -2882,11 +2882,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Under 43.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>43.5</v>
+        <v>42.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2904,13 +2904,13 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>31.5</v>
+        <v>31.1</v>
       </c>
       <c r="J39" t="n">
-        <v>-12</v>
+        <v>-11.4</v>
       </c>
       <c r="K39" t="n">
-        <v>87.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
@@ -2939,11 +2939,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NE +7</t>
+          <t>NE +6.5</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-7</v>
+        <v>-6.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2964,10 +2964,10 @@
         <v>2.9</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.1</v>
+        <v>-3.6</v>
       </c>
       <c r="K40" t="n">
-        <v>62.3</v>
+        <v>60.8</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
@@ -3018,13 +3018,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>55.4</v>
+        <v>55</v>
       </c>
       <c r="J41" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="K41" t="n">
-        <v>74.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
@@ -3053,11 +3053,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CHI -3</t>
+          <t>CHI -3.5</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-3</v>
+        <v>-3.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3071,17 +3071,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼) ※</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="J42" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="K42" t="n">
-        <v>66.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
@@ -3110,11 +3110,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>42.5</v>
+        <v>43.5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3128,17 +3128,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼) ※</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>48.3</v>
+        <v>46.7</v>
       </c>
       <c r="J43" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="K43" t="n">
-        <v>70.90000000000001</v>
+        <v>62</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
@@ -3246,13 +3246,13 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>34.7</v>
+        <v>34.2</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.8</v>
+        <v>-4.3</v>
       </c>
       <c r="K45" t="n">
-        <v>64.2</v>
+        <v>65.8</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
@@ -3338,11 +3338,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>43.5</v>
+        <v>42.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3356,17 +3356,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>48.4</v>
+        <v>47.9</v>
       </c>
       <c r="J47" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="K47" t="n">
-        <v>67.8</v>
+        <v>69.7</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
@@ -3390,7 +3390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3499,28 +3499,55 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>발행 방향(페이퍼)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>발행 세션 방향 줄 — 패스 포함 전 경기·스프레드+총점(10/1~)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>모델 관찰·참고(페이퍼)</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B5" t="n">
         <v>20</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>11</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>8</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>57.9</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G5" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>EPA 모델 방향 — 백테스트 45%, 검증용</t>
         </is>
@@ -3529,99 +3556,89 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>실베팅 · 시장별</t>
+          <t>평균 CLV · 실베팅</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  spread</t>
+          <t>평균 CLV · 발행 판단</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  total</t>
+          <t>평균 CLV · 발행 방향</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>실베팅 · 등급별</t>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  관심(설명문)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>실베팅 · 시장별</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  실베팅</t>
+          <t xml:space="preserve">  spread</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -3644,27 +3661,53 @@
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  total</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>모델 엣지 구간(전체 페이퍼 — 모델 검증)</t>
+          <t>실베팅 · 등급별</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| &lt;2</t>
+          <t xml:space="preserve">  관심(설명문)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3673,87 +3716,146 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| 2~3.5</t>
+          <t xml:space="preserve">  실베팅</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.09</v>
+        <v>-1</v>
       </c>
       <c r="H15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  |엣지| 3.5~5</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>7</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>모델 엣지 구간(전체 페이퍼 — 모델 검증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  |엣지| &lt;2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  |엣지| 2~3.5</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  |엣지| 3.5~5</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t xml:space="preserve">  |엣지| ≥5</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B21" t="n">
         <v>10</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C21" t="n">
         <v>6</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D21" t="n">
         <v>3</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E21" t="n">
         <v>1</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F21" t="n">
         <v>66.7</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G21" t="n">
         <v>2.45</v>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2079,20 +2079,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>NYG +8.5</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>44.5</v>
+        <v>8.5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2102,26 +2102,24 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="J25" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>83.3</v>
-      </c>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 44.5 · 가격 미기록(−120 티저 환산 손익분기 73.9%)</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026_04_ARI_NYG:total</t>
+          <t>2026_04_ARI_NYG:spread:T</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2129,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ATL@NO</t>
+          <t>ARI@NYG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2141,11 +2139,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>47.5</v>
+        <v>44.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2163,13 +2161,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>38.9</v>
+        <v>54.7</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.6</v>
+        <v>10.2</v>
       </c>
       <c r="K26" t="n">
-        <v>79.5</v>
+        <v>83.3</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -2178,7 +2176,7 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026_04_ATL_NO:total</t>
+          <t>2026_04_ARI_NYG:total</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2186,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DAL@HOU</t>
+          <t>ATL@NO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2198,15 +2196,15 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HOU -3</t>
+          <t>ATL +8.5</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-3</v>
+        <v>8.5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2216,26 +2214,24 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>4</v>
-      </c>
-      <c r="K27" t="n">
-        <v>62</v>
-      </c>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 47.5 · 가격 미기록(−120 티저 환산 손익분기 73.9%)</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026_04_DAL_HOU:spread</t>
+          <t>2026_04_ATL_NO:spread:T</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2241,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DAL@HOU</t>
+          <t>ATL@NO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2255,11 +2251,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>48.5</v>
+        <v>47.5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2273,17 +2269,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>52.9</v>
+        <v>38.9</v>
       </c>
       <c r="J28" t="n">
-        <v>4.4</v>
+        <v>-8.6</v>
       </c>
       <c r="K28" t="n">
-        <v>66.3</v>
+        <v>79.5</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -2292,7 +2288,7 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026_04_DAL_HOU:total</t>
+          <t>2026_04_ATL_NO:total</t>
         </is>
       </c>
     </row>
@@ -2302,21 +2298,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DEN@SF</t>
+          <t>DAL@HOU</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>HOU -3</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>47.5</v>
+        <v>-3</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2334,13 +2330,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>54.5</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>74.7</v>
+        <v>62</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
@@ -2349,7 +2345,7 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026_04_DEN_SF:total</t>
+          <t>2026_04_DAL_HOU:spread</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2355,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DET@CAR</t>
+          <t>DAL@HOU</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2369,11 +2365,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>50.5</v>
+        <v>48.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2391,13 +2387,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="J30" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="K30" t="n">
-        <v>62.6</v>
+        <v>66.3</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -2406,7 +2402,7 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026_04_DET_CAR:total</t>
+          <t>2026_04_DAL_HOU:total</t>
         </is>
       </c>
     </row>
@@ -2416,21 +2412,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GB@TB</t>
+          <t>DEN@SF</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TB +3.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3.5</v>
+        <v>47.5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2444,17 +2440,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>-0.8</v>
+        <v>54.5</v>
       </c>
       <c r="J31" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>58.2</v>
+        <v>74.7</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -2463,7 +2459,7 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:spread</t>
+          <t>2026_04_DEN_SF:total</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2469,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GB@TB</t>
+          <t>DET@CAR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2483,11 +2479,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>Over 50.5</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>38.5</v>
+        <v>50.5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2505,13 +2501,13 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>42.3</v>
+        <v>53.9</v>
       </c>
       <c r="J32" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K32" t="n">
-        <v>64.09999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -2520,7 +2516,7 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:total</t>
+          <t>2026_04_DET_CAR:total</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2526,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IND@WAS</t>
+          <t>GB@TB</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2540,7 +2536,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IND -3.5</t>
+          <t>TB +3.5</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2558,17 +2554,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>-9.300000000000001</v>
+        <v>-0.8</v>
       </c>
       <c r="J33" t="n">
-        <v>-5.8</v>
+        <v>2.7</v>
       </c>
       <c r="K33" t="n">
-        <v>67.2</v>
+        <v>58.2</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -2577,7 +2573,7 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026_04_IND_WAS:spread</t>
+          <t>2026_04_GB_TB:spread</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2583,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IND@WAS</t>
+          <t>GB@TB</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2597,11 +2593,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>47.5</v>
+        <v>38.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2615,17 +2611,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>56</v>
+        <v>42.3</v>
       </c>
       <c r="J34" t="n">
-        <v>8.5</v>
+        <v>3.8</v>
       </c>
       <c r="K34" t="n">
-        <v>79</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -2634,7 +2630,7 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026_04_IND_WAS:total</t>
+          <t>2026_04_GB_TB:total</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2640,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JAX@CIN</t>
+          <t>IND@WAS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2654,11 +2650,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
+          <t>IND -3.5</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2676,13 +2672,13 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>-9.5</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>-12</v>
+        <v>-5.8</v>
       </c>
       <c r="K35" t="n">
-        <v>82.09999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
@@ -2691,7 +2687,7 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:spread</t>
+          <t>2026_04_IND_WAS:spread</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2697,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JAX@CIN</t>
+          <t>IND@WAS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2707,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>51.5</v>
+        <v>47.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2729,17 +2725,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>47.9</v>
+        <v>56</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.6</v>
+        <v>8.5</v>
       </c>
       <c r="K36" t="n">
-        <v>63.5</v>
+        <v>79</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -2748,7 +2744,7 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:total</t>
+          <t>2026_04_IND_WAS:total</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2754,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KC@LV</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2768,11 +2764,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KC -4.5</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2790,13 +2786,13 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>-9.9</v>
+        <v>-9.5</v>
       </c>
       <c r="J37" t="n">
-        <v>-5.4</v>
+        <v>-12</v>
       </c>
       <c r="K37" t="n">
-        <v>66</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -2805,7 +2801,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:spread</t>
+          <t>2026_04_JAX_CIN:spread</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2811,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KC@LV</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2825,11 +2821,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>47.5</v>
+        <v>51.5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2843,17 +2839,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>38.8</v>
+        <v>47.9</v>
       </c>
       <c r="J38" t="n">
-        <v>-8.699999999999999</v>
+        <v>-3.6</v>
       </c>
       <c r="K38" t="n">
-        <v>79.8</v>
+        <v>63.5</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
@@ -2862,7 +2858,7 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:total</t>
+          <t>2026_04_JAX_CIN:total</t>
         </is>
       </c>
     </row>
@@ -2872,21 +2868,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LAC@SEA</t>
+          <t>KC@LV</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>KC -4.5</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>42.5</v>
+        <v>4.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2904,13 +2900,13 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>31.1</v>
+        <v>-9.9</v>
       </c>
       <c r="J39" t="n">
-        <v>-11.4</v>
+        <v>-5.4</v>
       </c>
       <c r="K39" t="n">
-        <v>86.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
@@ -2919,7 +2915,7 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026_04_LAC_SEA:total</t>
+          <t>2026_04_KC_LV:spread</t>
         </is>
       </c>
     </row>
@@ -2929,21 +2925,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>KC@LV</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NE +6.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-6.5</v>
+        <v>47.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2961,13 +2957,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>38.8</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.6</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>60.8</v>
+        <v>79.8</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
@@ -2976,7 +2972,7 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:spread</t>
+          <t>2026_04_KC_LV:total</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2982,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>LAC@SEA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2996,11 +2992,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>48.5</v>
+        <v>42.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3018,13 +3014,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>55</v>
+        <v>31.1</v>
       </c>
       <c r="J41" t="n">
-        <v>6.5</v>
+        <v>-11.4</v>
       </c>
       <c r="K41" t="n">
-        <v>73.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
@@ -3033,7 +3029,7 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:total</t>
+          <t>2026_04_LAC_SEA:total</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3039,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NYJ@CHI</t>
+          <t>NE@BUF</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3053,11 +3049,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CHI -3.5</t>
+          <t>NE +6.5</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-3.5</v>
+        <v>-6.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3075,13 +3071,13 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>10</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
-        <v>6.5</v>
+        <v>-3.6</v>
       </c>
       <c r="K42" t="n">
-        <v>69.09999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
@@ -3090,7 +3086,7 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:spread</t>
+          <t>2026_04_NE_BUF:spread</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3096,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NYJ@CHI</t>
+          <t>NE@BUF</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3110,11 +3106,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>43.5</v>
+        <v>48.5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3128,17 +3124,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>46.7</v>
+        <v>55</v>
       </c>
       <c r="J43" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="K43" t="n">
-        <v>62</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
@@ -3147,7 +3143,7 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:total</t>
+          <t>2026_04_NE_BUF:total</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3153,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>NYJ@CHI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3167,11 +3163,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CLE +3</t>
+          <t>CHI -3.5</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>-3.5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3185,17 +3181,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>-0.7</v>
+        <v>10</v>
       </c>
       <c r="J44" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="K44" t="n">
-        <v>56.9</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
@@ -3204,7 +3200,7 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:spread</t>
+          <t>2026_04_NYJ_CHI:spread</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3210,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>NYJ@CHI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3224,11 +3220,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>38.5</v>
+        <v>43.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3246,13 +3242,13 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>34.2</v>
+        <v>46.7</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.3</v>
+        <v>3.2</v>
       </c>
       <c r="K45" t="n">
-        <v>65.8</v>
+        <v>62</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
@@ -3261,7 +3257,7 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:total</t>
+          <t>2026_04_NYJ_CHI:total</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3267,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TEN@BAL</t>
+          <t>PIT@CLE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3281,11 +3277,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BAL -11.5</t>
+          <t>CLE +3</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-11.5</v>
+        <v>3</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3303,13 +3299,13 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>13.9</v>
+        <v>-0.7</v>
       </c>
       <c r="J46" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="K46" t="n">
-        <v>57.4</v>
+        <v>56.9</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
@@ -3318,7 +3314,7 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026_04_TEN_BAL:spread</t>
+          <t>2026_04_PIT_CLE:spread</t>
         </is>
       </c>
     </row>
@@ -3328,25 +3324,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TEN@BAL</t>
+          <t>PIT@CLE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>CLE +8.5</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>42.5</v>
+        <v>8.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-270</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3356,24 +3352,193 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="J47" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K47" t="n">
-        <v>69.7</v>
-      </c>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 38.5 · 가격 Polymarket No 73c(표시가 — 실베팅 아님)</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026_04_PIT_CLE:spread:T</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PIT@CLE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Under 38.5</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="K48" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026_04_PIT_CLE:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>BAL -11.5</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K49" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026_04_TEN_BAL:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Over 42.5</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="J50" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K50" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
         <is>
           <t>2026_04_TEN_BAL:total</t>
         </is>
@@ -3390,7 +3555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3556,47 +3721,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>평균 CLV · 실베팅</t>
+          <t>티저 다리(관찰·페이퍼)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+          <t>웡 티저 다리(10/1~) — 손익분기 73.9%(−120 2팀 환산) · 60다리 보고 · &lt;72% 폐기</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>평균 CLV · 발행 판단</t>
+          <t>평균 CLV · 실베팅</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -3607,64 +3775,62 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>평균 CLV · 발행 판단</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>평균 CLV · 발행 방향</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>실베팅 · 시장별</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  spread</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>실베팅 · 시장별</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  total</t>
+          <t xml:space="preserve">  spread</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -3690,40 +3856,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>실베팅 · 등급별</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  total</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  관심(설명문)</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>실베팅 · 등급별</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  실베팅</t>
+          <t xml:space="preserve">  관심(설명문)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3746,50 +3912,50 @@
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>모델 엣지 구간(전체 페이퍼 — 모델 검증)</t>
-        </is>
-      </c>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  실베팅</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| &lt;2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>모델 엣지 구간(전체 페이퍼 — 모델 검증)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| 2~3.5</t>
+          <t xml:space="preserve">  |엣지| &lt;2</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
@@ -3798,64 +3964,90 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.09</v>
+        <v>-2</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| 3.5~5</t>
+          <t xml:space="preserve">  |엣지| 2~3.5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>57.1</v>
+        <v>33.3</v>
       </c>
       <c r="G20" t="n">
-        <v>0.64</v>
+        <v>-1.09</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| ≥5</t>
+          <t xml:space="preserve">  |엣지| 3.5~5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
       </c>
       <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  |엣지| ≥5</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
         <v>1</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>66.7</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>2.45</v>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -3555,7 +3555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3748,47 +3748,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>평균 CLV · 실베팅</t>
+          <t>바람 언더(관찰·페이퍼)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+          <t>실외 · 킥오프 예보 지속 15mph+ 언더(10/1~) — 손익분기 52.4% · 40픽 또는 시즌 종료 때 보고 · &lt;52.4% 폐기</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>평균 CLV · 발행 판단</t>
+          <t>평균 CLV · 실베팅</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -3799,22 +3802,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>평균 CLV · 발행 판단</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>평균 CLV · 발행 방향</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
         </is>
@@ -3823,73 +3850,64 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>실베팅 · 시장별</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  spread</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>평균 CLV · 바람 언더</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  total</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>실베팅 · 시장별</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>실베팅 · 등급별</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  spread</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  관심(설명문)</t>
+          <t xml:space="preserve">  total</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3915,139 +3933,172 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  실베팅</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+          <t>실베팅 · 등급별</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  관심(설명문)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>1</v>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>-1</v>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>모델 엣지 구간(전체 페이퍼 — 모델 검증)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  |엣지| &lt;2</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t xml:space="preserve">  실베팅</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| 2~3.5</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>모델 엣지 구간(전체 페이퍼 — 모델 검증)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| 3.5~5</t>
+          <t xml:space="preserve">  |엣지| &lt;2</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.64</v>
+        <v>-2</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t xml:space="preserve">  |엣지| 2~3.5</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  |엣지| 3.5~5</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t xml:space="preserve">  |엣지| ≥5</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B24" t="n">
         <v>10</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C24" t="n">
         <v>6</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D24" t="n">
         <v>3</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E24" t="n">
         <v>1</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F24" t="n">
         <v>66.7</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G24" t="n">
         <v>2.45</v>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DET@CAR</t>
+          <t>GB@TB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2479,11 +2479,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>50.5</v>
+        <v>38.5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>53.9</v>
+        <v>42.3</v>
       </c>
       <c r="J32" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K32" t="n">
-        <v>62.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -2516,7 +2516,7 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026_04_DET_CAR:total</t>
+          <t>2026_04_GB_TB:total</t>
         </is>
       </c>
     </row>
@@ -2526,21 +2526,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GB@TB</t>
+          <t>IND@WAS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TB +3.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3.5</v>
+        <v>47.5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2554,17 +2554,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>-0.8</v>
+        <v>56</v>
       </c>
       <c r="J33" t="n">
-        <v>2.7</v>
+        <v>8.5</v>
       </c>
       <c r="K33" t="n">
-        <v>58.2</v>
+        <v>79</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -2573,7 +2573,7 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:spread</t>
+          <t>2026_04_IND_WAS:total</t>
         </is>
       </c>
     </row>
@@ -2583,21 +2583,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GB@TB</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>38.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2611,17 +2611,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>42.3</v>
+        <v>-9.5</v>
       </c>
       <c r="J34" t="n">
-        <v>3.8</v>
+        <v>-12</v>
       </c>
       <c r="K34" t="n">
-        <v>64.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -2630,7 +2630,7 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:total</t>
+          <t>2026_04_JAX_CIN:spread</t>
         </is>
       </c>
     </row>
@@ -2640,21 +2640,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IND@WAS</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IND -3.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3.5</v>
+        <v>51.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2668,17 +2668,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>-9.300000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.8</v>
+        <v>-3.6</v>
       </c>
       <c r="K35" t="n">
-        <v>67.2</v>
+        <v>63.5</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026_04_IND_WAS:spread</t>
+          <t>2026_04_JAX_CIN:total</t>
         </is>
       </c>
     </row>
@@ -2697,21 +2697,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IND@WAS</t>
+          <t>KC@LV</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>KC -4.5</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>47.5</v>
+        <v>4.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2729,13 +2729,13 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>56</v>
+        <v>-9.9</v>
       </c>
       <c r="J36" t="n">
-        <v>8.5</v>
+        <v>-5.4</v>
       </c>
       <c r="K36" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -2744,7 +2744,7 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026_04_IND_WAS:total</t>
+          <t>2026_04_KC_LV:spread</t>
         </is>
       </c>
     </row>
@@ -2754,21 +2754,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JAX@CIN</t>
+          <t>KC@LV</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-2.5</v>
+        <v>47.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>-9.5</v>
+        <v>38.8</v>
       </c>
       <c r="J37" t="n">
-        <v>-12</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>82.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:spread</t>
+          <t>2026_04_KC_LV:total</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JAX@CIN</t>
+          <t>LAC@SEA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2821,11 +2821,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>51.5</v>
+        <v>42.5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2839,17 +2839,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>47.9</v>
+        <v>31.1</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.6</v>
+        <v>-11.4</v>
       </c>
       <c r="K38" t="n">
-        <v>63.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:total</t>
+          <t>2026_04_LAC_SEA:total</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KC@LV</t>
+          <t>NE@BUF</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2878,11 +2878,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KC -4.5</t>
+          <t>NE +6.5</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4.5</v>
+        <v>-6.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2900,13 +2900,13 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>-9.9</v>
+        <v>2.9</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.4</v>
+        <v>-3.6</v>
       </c>
       <c r="K39" t="n">
-        <v>66</v>
+        <v>60.8</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
@@ -2915,7 +2915,7 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:spread</t>
+          <t>2026_04_NE_BUF:spread</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KC@LV</t>
+          <t>NE@BUF</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2935,11 +2935,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>38.8</v>
+        <v>55</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="K40" t="n">
-        <v>79.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
@@ -2972,7 +2972,7 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:total</t>
+          <t>2026_04_NE_BUF:total</t>
         </is>
       </c>
     </row>
@@ -2982,21 +2982,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LAC@SEA</t>
+          <t>NYJ@CHI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>CHI -3.5</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>42.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3014,13 +3014,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>31.1</v>
+        <v>10</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.4</v>
+        <v>6.5</v>
       </c>
       <c r="K41" t="n">
-        <v>86.09999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026_04_LAC_SEA:total</t>
+          <t>2026_04_NYJ_CHI:spread</t>
         </is>
       </c>
     </row>
@@ -3039,21 +3039,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>NYJ@CHI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NE +6.5</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-6.5</v>
+        <v>43.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3067,17 +3067,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>46.7</v>
       </c>
       <c r="J42" t="n">
-        <v>-3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K42" t="n">
-        <v>60.8</v>
+        <v>62</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
@@ -3086,7 +3086,7 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:spread</t>
+          <t>2026_04_NYJ_CHI:total</t>
         </is>
       </c>
     </row>
@@ -3096,25 +3096,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>PIT@CLE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>CLE +8.5</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>48.5</v>
+        <v>8.5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-270</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3124,26 +3124,24 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>55</v>
-      </c>
-      <c r="J43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K43" t="n">
-        <v>73.09999999999999</v>
-      </c>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 38.5 · 가격 Polymarket No 73c(표시가 — 실베팅 아님)</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:total</t>
+          <t>2026_04_PIT_CLE:spread:T</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3151,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NYJ@CHI</t>
+          <t>PIT@CLE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3163,11 +3161,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CHI -3.5</t>
+          <t>PIT -2.5</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3181,26 +3179,30 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>10</v>
+        <v>-0.7</v>
       </c>
       <c r="J44" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="K44" t="n">
-        <v>69.09999999999999</v>
+        <v>56.9</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:spread</t>
+          <t>2026_04_PIT_CLE:spread:D</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3212,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NYJ@CHI</t>
+          <t>PIT@CLE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3220,11 +3222,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>Under 38.5</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>43.5</v>
+        <v>38.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3242,13 +3244,13 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>46.7</v>
+        <v>34.2</v>
       </c>
       <c r="J45" t="n">
-        <v>3.2</v>
+        <v>-4.3</v>
       </c>
       <c r="K45" t="n">
-        <v>62</v>
+        <v>65.8</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
@@ -3257,7 +3259,7 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:total</t>
+          <t>2026_04_PIT_CLE:total</t>
         </is>
       </c>
     </row>
@@ -3272,16 +3274,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CLE +3</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>38.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3295,26 +3297,30 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>-0.7</v>
+        <v>34.2</v>
       </c>
       <c r="J46" t="n">
-        <v>2.3</v>
+        <v>-4.3</v>
       </c>
       <c r="K46" t="n">
-        <v>56.9</v>
+        <v>65.8</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:spread</t>
+          <t>2026_04_PIT_CLE:total:D</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3330,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>TEN@BAL</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3334,15 +3340,15 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CLE +8.5</t>
+          <t>BAL -11.5</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>8.5</v>
+        <v>-11.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-270</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3352,24 +3358,26 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K47" t="n">
+        <v>57.4</v>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>원 라인 +2.5 · 총점 38.5 · 가격 Polymarket No 73c(표시가 — 실베팅 아님)</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:spread:T</t>
+          <t>2026_04_TEN_BAL:spread</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3387,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>TEN@BAL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3389,11 +3397,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>38.5</v>
+        <v>42.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3407,17 +3415,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>34.2</v>
+        <v>47.9</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.3</v>
+        <v>5.4</v>
       </c>
       <c r="K48" t="n">
-        <v>65.8</v>
+        <v>69.7</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
@@ -3425,120 +3433,6 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
-        <is>
-          <t>2026_04_PIT_CLE:total</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>4</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>TEN@BAL</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>BAL -11.5</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-110</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K49" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>2026_04_TEN_BAL:spread</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>4</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>TEN@BAL</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Over 42.5</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-110</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="J50" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K50" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
         <is>
           <t>2026_04_TEN_BAL:total</t>
         </is>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3217,49 +3217,51 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>PIT -2.5</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>38.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>suggested</t>
+          <t>placed</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="J45" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="K45" t="n">
-        <v>65.8</v>
-      </c>
+          <t>실베팅</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:36</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Paul 자체 판단 0.5u — 발행 판단은 패스(굳이 하나만 PIT -2.5). 배당 미확인 — 발행 시점 시장가 -120 으로 임시(Paul 확인 시 정정). Ramsey(PIT CB) Q 상태에서 베팅</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:total</t>
+          <t>2026_04_PIT_CLE:spread:P</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3281,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>Under 38.5</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -3297,7 +3299,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3313,14 +3315,10 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:total:D</t>
+          <t>2026_04_PIT_CLE:total</t>
         </is>
       </c>
     </row>
@@ -3330,21 +3328,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TEN@BAL</t>
+          <t>PIT@CLE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BAL -11.5</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-11.5</v>
+        <v>38.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3358,26 +3356,30 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>13.9</v>
+        <v>34.2</v>
       </c>
       <c r="J47" t="n">
-        <v>2.4</v>
+        <v>-4.3</v>
       </c>
       <c r="K47" t="n">
-        <v>57.4</v>
+        <v>65.8</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026_04_TEN_BAL:spread</t>
+          <t>2026_04_PIT_CLE:total:D</t>
         </is>
       </c>
     </row>
@@ -3392,16 +3394,16 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>BAL -11.5</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>42.5</v>
+        <v>-11.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3415,17 +3417,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>47.9</v>
+        <v>13.9</v>
       </c>
       <c r="J48" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="K48" t="n">
-        <v>69.7</v>
+        <v>57.4</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
@@ -3433,6 +3435,63 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026_04_TEN_BAL:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Over 42.5</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="J49" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K49" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>2026_04_TEN_BAL:total</t>
         </is>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -3230,7 +3230,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-108</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Paul 자체 판단 0.5u — 발행 판단은 패스(굳이 하나만 PIT -2.5). 배당 미확인 — 발행 시점 시장가 -120 으로 임시(Paul 확인 시 정정). Ramsey(PIT CB) Q 상태에서 베팅</t>
+          <t>Paul 자체 판단 0.5u — 발행 판단은 패스(굳이 하나만 PIT -2.5). 체결 Polymarket 「PIT to win by over 2.5 → Yes」 52c(≈ -108, 손익분기 52.0%). Ramsey(PIT CB) Q 상태에서 베팅</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -2536,11 +2536,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2561,10 +2561,10 @@
         <v>56</v>
       </c>
       <c r="J33" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="K33" t="n">
-        <v>79</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -2878,11 +2878,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NE +6.5</t>
+          <t>NE +7</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-6.5</v>
+        <v>-7</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2903,10 +2903,10 @@
         <v>2.9</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.6</v>
+        <v>-4.1</v>
       </c>
       <c r="K39" t="n">
-        <v>60.8</v>
+        <v>62.3</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
@@ -3130,9 +3130,19 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0.37</v>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -3191,9 +3201,19 @@
       <c r="K44" t="n">
         <v>56.9</v>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>-1</v>
+      </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -3246,9 +3266,19 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
           <t>2026-10-01 11:36</t>
@@ -3311,9 +3341,19 @@
       <c r="K46" t="n">
         <v>65.8</v>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>-1</v>
+      </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
@@ -3368,9 +3408,19 @@
       <c r="K47" t="n">
         <v>65.8</v>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -3564,13 +3614,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3579,7 +3629,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-2</v>
+        <v>-2.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3621,19 +3671,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
+      <c r="F4" t="n">
+        <v>50</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -3648,22 +3701,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>57.9</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -3678,10 +3731,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -3689,12 +3742,15 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>웡 티저 다리(10/1~) — 손익분기 73.9%(−120 2팀 환산) · 60다리 보고 · &lt;72% 폐기</t>
+          <t>웡 티저 다리(10/1~) — 손익분기 73.9%(−120 2팀 환산) · 60다리 보고 · &lt;72% 폐기 · 평균 표시가 73.0c(n 1)</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3788,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -3741,10 +3797,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -3783,7 +3839,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -3792,6 +3848,9 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
@@ -3838,13 +3897,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3853,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -3923,13 +3982,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -3938,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -3956,22 +4015,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>-2</v>
+        <v>-2.13</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -3982,22 +4041,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.09</v>
+        <v>-2.09</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -4008,22 +4067,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
         <v>4</v>
       </c>
-      <c r="D23" t="n">
-        <v>3</v>
-      </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>57.1</v>
+        <v>55.6</v>
       </c>
       <c r="G23" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -4064,7 +4123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4172,6 +4231,44 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K24" t="n">
-        <v>62.9</v>
+        <v>63.2</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
@@ -2134,16 +2134,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>ARI -2.5</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>44.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2157,26 +2157,30 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>54.7</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>10.2</v>
+        <v>4.4</v>
       </c>
       <c r="K26" t="n">
-        <v>83.3</v>
+        <v>63.2</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026_04_ARI_NYG:total</t>
+          <t>2026_04_ARI_NYG:spread:D</t>
         </is>
       </c>
     </row>
@@ -2186,25 +2190,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ATL@NO</t>
+          <t>ARI@NYG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ATL +8.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>8.5</v>
+        <v>44.5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2214,24 +2218,26 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>83.59999999999999</v>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>원 라인 +2.5 · 총점 47.5 · 가격 미기록(−120 티저 환산 손익분기 73.9%)</t>
-        </is>
-      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026_04_ATL_NO:spread:T</t>
+          <t>2026_04_ARI_NYG:total</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2247,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ATL@NO</t>
+          <t>ARI@NYG</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2251,11 +2257,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>47.5</v>
+        <v>44.5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2269,26 +2275,30 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>38.9</v>
+        <v>54.8</v>
       </c>
       <c r="J28" t="n">
-        <v>-8.6</v>
+        <v>10.3</v>
       </c>
       <c r="K28" t="n">
-        <v>79.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026_04_ATL_NO:total</t>
+          <t>2026_04_ARI_NYG:total:D</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2308,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DAL@HOU</t>
+          <t>ATL@NO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2308,15 +2318,15 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>HOU -3</t>
+          <t>ATL +7.5</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-3</v>
+        <v>7.5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-120</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2326,26 +2336,24 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>7</v>
-      </c>
-      <c r="J29" t="n">
-        <v>4</v>
-      </c>
-      <c r="K29" t="n">
-        <v>62</v>
-      </c>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>원 라인 +1.5 · 총점 47.5 · 가격 미기록(−120 티저 환산 손익분기 73.9%)</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026_04_DAL_HOU:spread</t>
+          <t>2026_04_ATL_NO:spread:T</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2363,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DAL@HOU</t>
+          <t>ATL@NO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2365,11 +2373,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>48.5</v>
+        <v>47.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2383,17 +2391,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>52.9</v>
+        <v>39</v>
       </c>
       <c r="J30" t="n">
-        <v>4.4</v>
+        <v>-8.5</v>
       </c>
       <c r="K30" t="n">
-        <v>66.3</v>
+        <v>79</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -2402,7 +2410,7 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026_04_DAL_HOU:total</t>
+          <t>2026_04_ATL_NO:total</t>
         </is>
       </c>
     </row>
@@ -2412,21 +2420,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DEN@SF</t>
+          <t>DAL@HOU</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>HOU -3</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>47.5</v>
+        <v>-3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2444,13 +2452,13 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>54.5</v>
+        <v>7.2</v>
       </c>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="K31" t="n">
-        <v>74.7</v>
+        <v>62.7</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -2459,7 +2467,7 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026_04_DEN_SF:total</t>
+          <t>2026_04_DAL_HOU:spread</t>
         </is>
       </c>
     </row>
@@ -2469,21 +2477,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GB@TB</t>
+          <t>DAL@HOU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>HOU -3</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>38.5</v>
+        <v>-3</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2497,26 +2505,30 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>42.3</v>
+        <v>7.2</v>
       </c>
       <c r="J32" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="K32" t="n">
-        <v>64.09999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:total</t>
+          <t>2026_04_DAL_HOU:spread:D</t>
         </is>
       </c>
     </row>
@@ -2526,21 +2538,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IND@WAS</t>
+          <t>DAL@HOU</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>HOU -3</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>48.5</v>
+        <v>-3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2554,26 +2566,24 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>56</v>
-      </c>
-      <c r="J33" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="K33" t="n">
-        <v>76.09999999999999</v>
-      </c>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>언더독 DAL 드라이브 득점 차 우위 +0.91 → 반대 HOU · 10-04 09:01 PT 판</t>
+        </is>
+      </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026_04_IND_WAS:total</t>
+          <t>2026_04_DAL_HOU:spread:A2</t>
         </is>
       </c>
     </row>
@@ -2583,21 +2593,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JAX@CIN</t>
+          <t>DAL@HOU</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-2.5</v>
+        <v>48.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2611,17 +2621,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>-9.5</v>
+        <v>53</v>
       </c>
       <c r="J34" t="n">
-        <v>-12</v>
+        <v>4.5</v>
       </c>
       <c r="K34" t="n">
-        <v>82.09999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -2630,7 +2640,7 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:spread</t>
+          <t>2026_04_DAL_HOU:total</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2650,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JAX@CIN</t>
+          <t>DAL@HOU</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2650,11 +2660,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>51.5</v>
+        <v>48.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2668,26 +2678,30 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>47.9</v>
+        <v>53</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.6</v>
+        <v>4.5</v>
       </c>
       <c r="K35" t="n">
-        <v>63.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:total</t>
+          <t>2026_04_DAL_HOU:total:D</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2711,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KC@LV</t>
+          <t>DEN@SF</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2707,11 +2721,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KC -4.5</t>
+          <t>DEN +3</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2725,26 +2739,24 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="J36" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="K36" t="n">
-        <v>66</v>
-      </c>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:spread</t>
+          <t>2026_04_DEN_SF:spread:D</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KC@LV</t>
+          <t>DEN@SF</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2764,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2786,13 +2798,13 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>38.8</v>
+        <v>54.4</v>
       </c>
       <c r="J37" t="n">
-        <v>-8.699999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="K37" t="n">
-        <v>79.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -2801,7 +2813,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:total</t>
+          <t>2026_04_DEN_SF:total</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2823,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LAC@SEA</t>
+          <t>DEN@SF</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2821,11 +2833,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>42.5</v>
+        <v>48.5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2839,26 +2851,30 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>31.1</v>
+        <v>54.4</v>
       </c>
       <c r="J38" t="n">
-        <v>-11.4</v>
+        <v>5.9</v>
       </c>
       <c r="K38" t="n">
-        <v>86.09999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026_04_LAC_SEA:total</t>
+          <t>2026_04_DEN_SF:total:D</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2884,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>DET@CAR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2878,11 +2894,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NE +7</t>
+          <t>DET -3.5</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-7</v>
+        <v>-3.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2896,26 +2912,24 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J39" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>62.3</v>
-      </c>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:spread</t>
+          <t>2026_04_DET_CAR:spread:D</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2939,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>DET@CAR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2935,11 +2949,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>48.5</v>
+        <v>51.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2953,26 +2967,24 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>55</v>
-      </c>
-      <c r="J40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K40" t="n">
-        <v>73.09999999999999</v>
-      </c>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:total</t>
+          <t>2026_04_DET_CAR:total:D</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2994,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NYJ@CHI</t>
+          <t>GB@TB</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2992,11 +3004,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CHI -3.5</t>
+          <t>GB -3</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-3.5</v>
+        <v>3</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3010,17 +3022,17 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>10</v>
+        <v>-5.5</v>
       </c>
       <c r="J41" t="n">
-        <v>6.5</v>
+        <v>-2.5</v>
       </c>
       <c r="K41" t="n">
-        <v>69.09999999999999</v>
+        <v>57.6</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
@@ -3029,7 +3041,7 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:spread</t>
+          <t>2026_04_GB_TB:spread</t>
         </is>
       </c>
     </row>
@@ -3039,21 +3051,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NYJ@CHI</t>
+          <t>GB@TB</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>GB -3</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>43.5</v>
+        <v>-3</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3067,26 +3079,30 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>46.7</v>
+        <v>-5.5</v>
       </c>
       <c r="J42" t="n">
-        <v>3.2</v>
+        <v>-2.5</v>
       </c>
       <c r="K42" t="n">
-        <v>62</v>
+        <v>57.6</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:total</t>
+          <t>2026_04_GB_TB:spread:D</t>
         </is>
       </c>
     </row>
@@ -3096,25 +3112,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>GB@TB</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CLE +8.5</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8.5</v>
+        <v>38.5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-270</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3124,34 +3140,26 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>PIT 24-27 CLE</t>
-        </is>
-      </c>
-      <c r="N43" t="n">
-        <v>0.37</v>
-      </c>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>43</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>원 라인 +2.5 · 총점 38.5 · 가격 Polymarket No 73c(표시가 — 실베팅 아님)</t>
-        </is>
-      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:spread:T</t>
+          <t>2026_04_GB_TB:total</t>
         </is>
       </c>
     </row>
@@ -3161,21 +3169,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>GB@TB</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PIT -2.5</t>
+          <t>Under 38.5</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-2.5</v>
+        <v>38.5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3193,27 +3201,17 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>-0.7</v>
+        <v>43</v>
       </c>
       <c r="J44" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="K44" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>PIT 24-27 CLE</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>-1</v>
-      </c>
+        <v>66.5</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -3222,7 +3220,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:spread:D</t>
+          <t>2026_04_GB_TB:total:D</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3230,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>IND@WAS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3242,56 +3240,44 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>PIT -2.5</t>
+          <t>IND -4.5</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-108</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>placed</t>
+          <t>suggested</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>실베팅</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>PIT 24-27 CLE</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>2026-10-01 11:36</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Paul 자체 판단 0.5u — 발행 판단은 패스(굳이 하나만 PIT -2.5). 체결 Polymarket 「PIT to win by over 2.5 → Yes」 52c(≈ -108, 손익분기 52.0%). Ramsey(PIT CB) Q 상태에서 베팅</t>
-        </is>
-      </c>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:spread:P</t>
+          <t>2026_04_IND_WAS:spread</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3287,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>IND@WAS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3311,11 +3297,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>38.5</v>
+        <v>46.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3329,36 +3315,26 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>34.2</v>
+        <v>51.6</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.3</v>
+        <v>5.1</v>
       </c>
       <c r="K46" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>PIT 24-27 CLE</t>
-        </is>
-      </c>
-      <c r="N46" t="n">
-        <v>-1</v>
-      </c>
+        <v>68.8</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:total</t>
+          <t>2026_04_IND_WAS:total</t>
         </is>
       </c>
     </row>
@@ -3368,21 +3344,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>38.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3396,40 +3372,26 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>34.2</v>
+        <v>-9.5</v>
       </c>
       <c r="J47" t="n">
-        <v>-4.3</v>
+        <v>-12</v>
       </c>
       <c r="K47" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>PIT 24-27 CLE</t>
-        </is>
-      </c>
-      <c r="N47" t="n">
-        <v>0.909</v>
-      </c>
+        <v>82.3</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:total:D</t>
+          <t>2026_04_JAX_CIN:spread</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3401,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TEN@BAL</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3449,11 +3411,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BAL -11.5</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-11.5</v>
+        <v>2.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3467,26 +3429,30 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>13.9</v>
+        <v>-9.5</v>
       </c>
       <c r="J48" t="n">
-        <v>2.4</v>
+        <v>-12</v>
       </c>
       <c r="K48" t="n">
-        <v>57.4</v>
+        <v>82.3</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026_04_TEN_BAL:spread</t>
+          <t>2026_04_JAX_CIN:spread:D</t>
         </is>
       </c>
     </row>
@@ -3496,21 +3462,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TEN@BAL</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>CIN -2.5</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>42.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3524,26 +3490,2003 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="J49" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K49" t="n">
-        <v>69.7</v>
-      </c>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>언더독 JAX 드라이브 득점 차 우위 +0.98 → 반대 CIN · 10-04 09:01 PT 판</t>
+        </is>
+      </c>
       <c r="Q49" t="inlineStr">
         <is>
+          <t>2026_04_JAX_CIN:spread:A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>JAX@CIN</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Under 51.5</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="K50" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026_04_JAX_CIN:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>JAX@CIN</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Over 51.5</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="K51" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026_04_JAX_CIN:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>4</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>KC@LV</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>KC -4.5</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026_04_KC_LV:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>KC@LV</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>KC -4.5</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2026_04_KC_LV:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>KC@LV</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Under 47.5</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="K54" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2026_04_KC_LV:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>KC@LV</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Under 47.5</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="K55" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2026_04_KC_LV:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LA@PHI</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LA -3.5</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>2026_04_LA_PHI:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LA@PHI</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Over 42.5</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="J57" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>2026_04_LA_PHI:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LA@PHI</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Under 42.5</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>2026_04_LA_PHI:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LAC@SEA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LAC +7</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J59" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>2026_04_LAC_SEA:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LAC@SEA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SEA -7</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J60" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2026_04_LAC_SEA:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>4</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LAC@SEA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Under 42.5</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K61" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>2026_04_LAC_SEA:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LAC@SEA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Under 42.5</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J62" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K62" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>2026_04_LAC_SEA:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MIA@MIN</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>MIA +10</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>10</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>2026_04_MIA_MIN:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MIA@MIN</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Under 38.5</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>2026_04_MIA_MIN:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>NE@BUF</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NE +7</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="K65" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>2026_04_NE_BUF:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>4</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NE@BUF</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>BUF -7</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="K66" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>2026_04_NE_BUF:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>4</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>NE@BUF</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Over 49.5</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="J67" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K67" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2026_04_NE_BUF:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NE@BUF</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Under 49.5</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>바람 언더(관찰)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>예보 16mph(NWS 지속·10-04 08:30 PT) · 총점 42+</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>2026_04_NE_BUF:total:wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NE@BUF</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Over 49.5</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="J69" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K69" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>2026_04_NE_BUF:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>4</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NYJ@CHI</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CHI -3.5</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K70" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>2026_04_NYJ_CHI:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>4</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NYJ@CHI</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NYJ +3.5</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K71" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>2026_04_NYJ_CHI:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>4</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NYJ@CHI</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Over 43.5</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="J72" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K72" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>2026_04_NYJ_CHI:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NYJ@CHI</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Under 43.5</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="J73" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K73" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>2026_04_NYJ_CHI:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PIT@CLE</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CLE +8.5</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-270</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 38.5 · 가격 Polymarket No 73c(표시가 — 실베팅 아님)</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2026_04_PIT_CLE:spread:T</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PIT@CLE</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>PIT -2.5</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K75" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>2026_04_PIT_CLE:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PIT@CLE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>PIT -2.5</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-108</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>placed</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>실베팅</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:36</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Paul 자체 판단 0.5u — 발행 판단은 패스(굳이 하나만 PIT -2.5). 체결 Polymarket 「PIT to win by over 2.5 → Yes」 52c(≈ -108, 손익분기 52.0%). Ramsey(PIT CB) Q 상태에서 베팅</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2026_04_PIT_CLE:spread:P</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>4</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PIT@CLE</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Under 38.5</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="J77" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="K77" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>2026_04_PIT_CLE:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>4</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PIT@CLE</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Over 38.5</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="K78" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>2026_04_PIT_CLE:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BAL -11.5</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J79" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K79" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>2026_04_TEN_BAL:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>TEN +11.5</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J80" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K80" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>2026_04_TEN_BAL:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Over 42.5</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>48</v>
+      </c>
+      <c r="J81" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K81" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
           <t>2026_04_TEN_BAL:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Under 42.5</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>48</v>
+      </c>
+      <c r="J82" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K82" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>2026_04_TEN_BAL:total:D</t>
         </is>
       </c>
     </row>
@@ -3558,7 +5501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3784,34 +5727,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>평균 CLV · 실베팅</t>
+          <t>각도 관찰 A1(원정 큰 페이버릿 반대)·페이퍼</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+          <t>2023~25 탐색 약한 꼴(10/4~) — 30픽/시즌 끝 보고 · &lt;50% 폐기 · ≥55% &amp; CLV ≥0 이면 상정</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>평균 CLV · 발행 판단</t>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)·페이퍼</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -3826,23 +5769,26 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+          <t>2023~25 탐색 약한 꼴(10/4~) — 30픽/시즌 끝 보고 · &lt;50% 폐기 · ≥55% &amp; CLV ≥0 이면 상정</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>평균 CLV · 발행 방향</t>
+          <t>평균 CLV · 실베팅</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -3851,7 +5797,7 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -3862,7 +5808,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>평균 CLV · 바람 언더</t>
+          <t>평균 CLV · 발행 판단</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -3878,6 +5824,33 @@
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>평균 CLV · 발행 방향</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
         </is>
@@ -3886,73 +5859,64 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>실베팅 · 시장별</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  spread</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>평균 CLV · 바람 언더</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  total</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>실베팅 · 시장별</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>실베팅 · 등급별</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  spread</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  관심(설명문)</t>
+          <t xml:space="preserve">  total</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -3978,139 +5942,172 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  실베팅</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>실베팅 · 등급별</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  관심(설명문)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>모델 엣지 구간(전체 페이퍼 — 모델 검증)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  |엣지| &lt;2</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>4</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>25</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t xml:space="preserve">  실베팅</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| 2~3.5</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>4</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>25</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>모델 엣지 구간(전체 페이퍼 — 모델 검증)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| 3.5~5</t>
+          <t xml:space="preserve">  |엣지| &lt;2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>55.6</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>0.55</v>
+        <v>-2.13</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| ≥5</t>
+          <t xml:space="preserve">  |엣지| 2~3.5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
       </c>
       <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>25</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  |엣지| 3.5~5</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  |엣지| ≥5</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
         <v>1</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>66.7</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>2.45</v>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2425,49 +2425,49 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>HOU -3</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>-3</v>
-      </c>
+          <t>HOU ML</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-148</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>suggested</t>
+          <t>placed</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>62.7</v>
-      </c>
+          <t>실베팅</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-10-04 09:27</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Paul 실베팅 — A2 패턴(드라이브 우위 언더독 DAL의 반대) ML. 배당은 수집값(DK −148) 그대로(Paul). 금액 미확인 — 권장 0.5u 로 임시</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026_04_DAL_HOU:spread</t>
+          <t>2026_04_DAL_HOU:ml:P</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2521,14 +2521,10 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026_04_DAL_HOU:spread:D</t>
+          <t>2026_04_DAL_HOU:spread</t>
         </is>
       </c>
     </row>
@@ -2566,24 +2562,30 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>62.7</v>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>언더독 DAL 드라이브 득점 차 우위 +0.91 → 반대 HOU · 10-04 09:01 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026_04_DAL_HOU:spread:A2</t>
+          <t>2026_04_DAL_HOU:spread:D</t>
         </is>
       </c>
     </row>
@@ -2598,16 +2600,16 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>HOU -3</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>48.5</v>
+        <v>-3</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2621,26 +2623,24 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>53</v>
-      </c>
-      <c r="J34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K34" t="n">
-        <v>66.59999999999999</v>
-      </c>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>언더독 DAL 드라이브 득점 차 우위 +0.91 → 반대 HOU · 10-04 09:01 PT 판</t>
+        </is>
+      </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026_04_DAL_HOU:total</t>
+          <t>2026_04_DAL_HOU:spread:A2</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2694,14 +2694,10 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026_04_DAL_HOU:total:D</t>
+          <t>2026_04_DAL_HOU:total</t>
         </is>
       </c>
     </row>
@@ -2711,21 +2707,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DEN@SF</t>
+          <t>DAL@HOU</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DEN +3</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>48.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2742,9 +2738,15 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>53</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>66.59999999999999</v>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -2756,7 +2758,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026_04_DEN_SF:spread:D</t>
+          <t>2026_04_DAL_HOU:total:D</t>
         </is>
       </c>
     </row>
@@ -2771,16 +2773,16 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>DEN +3</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>48.5</v>
+        <v>3</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2794,26 +2796,24 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="J37" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K37" t="n">
-        <v>71.40000000000001</v>
-      </c>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026_04_DEN_SF:total</t>
+          <t>2026_04_DEN_SF:spread:D</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2867,14 +2867,10 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026_04_DEN_SF:total:D</t>
+          <t>2026_04_DEN_SF:total</t>
         </is>
       </c>
     </row>
@@ -2884,21 +2880,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DET@CAR</t>
+          <t>DEN@SF</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DET -3.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-3.5</v>
+        <v>48.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2915,9 +2911,15 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K39" t="n">
+        <v>71.40000000000001</v>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -2929,7 +2931,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026_04_DET_CAR:spread:D</t>
+          <t>2026_04_DEN_SF:total:D</t>
         </is>
       </c>
     </row>
@@ -2944,16 +2946,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>DET -3.5</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>51.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2984,7 +2986,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026_04_DET_CAR:total:D</t>
+          <t>2026_04_DET_CAR:spread:D</t>
         </is>
       </c>
     </row>
@@ -2994,21 +2996,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GB@TB</t>
+          <t>DET@CAR</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GB -3</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>51.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3022,26 +3024,24 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="J41" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="K41" t="n">
-        <v>57.6</v>
-      </c>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:spread</t>
+          <t>2026_04_DET_CAR:total:D</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3095,14 +3095,10 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:spread:D</t>
+          <t>2026_04_GB_TB:spread</t>
         </is>
       </c>
     </row>
@@ -3117,16 +3113,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>GB -3</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>38.5</v>
+        <v>-3</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3140,26 +3136,30 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>43</v>
+        <v>-5.5</v>
       </c>
       <c r="J43" t="n">
-        <v>4.5</v>
+        <v>-2.5</v>
       </c>
       <c r="K43" t="n">
-        <v>66.5</v>
+        <v>57.6</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:total</t>
+          <t>2026_04_GB_TB:spread:D</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3213,14 +3213,10 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:total:D</t>
+          <t>2026_04_GB_TB:total</t>
         </is>
       </c>
     </row>
@@ -3230,54 +3226,58 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IND@WAS</t>
+          <t>GB@TB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>IND -4.5</t>
+          <t>Under 38.5</t>
         </is>
       </c>
       <c r="E45" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>43</v>
+      </c>
+      <c r="J45" t="n">
         <v>4.5</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>-110</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>-9.6</v>
-      </c>
-      <c r="J45" t="n">
-        <v>-5.1</v>
-      </c>
       <c r="K45" t="n">
-        <v>65.3</v>
+        <v>66.5</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026_04_IND_WAS:spread</t>
+          <t>2026_04_GB_TB:total:D</t>
         </is>
       </c>
     </row>
@@ -3292,16 +3292,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>IND -4.5</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>46.5</v>
+        <v>4.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3319,13 +3319,13 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>51.6</v>
+        <v>-9.6</v>
       </c>
       <c r="J46" t="n">
-        <v>5.1</v>
+        <v>-5.1</v>
       </c>
       <c r="K46" t="n">
-        <v>68.8</v>
+        <v>65.3</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
@@ -3334,7 +3334,7 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026_04_IND_WAS:total</t>
+          <t>2026_04_IND_WAS:spread</t>
         </is>
       </c>
     </row>
@@ -3344,21 +3344,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JAX@CIN</t>
+          <t>IND@WAS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-2.5</v>
+        <v>46.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3376,13 +3376,13 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>-9.5</v>
+        <v>51.6</v>
       </c>
       <c r="J47" t="n">
-        <v>-12</v>
+        <v>5.1</v>
       </c>
       <c r="K47" t="n">
-        <v>82.3</v>
+        <v>68.8</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
@@ -3391,7 +3391,7 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:spread</t>
+          <t>2026_04_IND_WAS:total</t>
         </is>
       </c>
     </row>
@@ -3406,53 +3406,49 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>2.5</v>
-      </c>
+          <t>CIN ML</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-148</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>suggested</t>
+          <t>placed</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="J48" t="n">
-        <v>-12</v>
-      </c>
-      <c r="K48" t="n">
-        <v>82.3</v>
-      </c>
+          <t>실베팅</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2026-10-04 09:27</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>Paul 실베팅 — A2 패턴(드라이브 우위 언더독 JAX의 반대) ML. 배당은 수집값(DK −148) 그대로(Paul). 금액 미확인 — 권장 0.5u 로 임시</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:spread:D</t>
+          <t>2026_04_JAX_CIN:ml:P</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3468,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CIN -2.5</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -3490,24 +3486,26 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K49" t="n">
+        <v>82.3</v>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>언더독 JAX 드라이브 득점 차 우위 +0.98 → 반대 CIN · 10-04 09:01 PT 판</t>
-        </is>
-      </c>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:spread:A2</t>
+          <t>2026_04_JAX_CIN:spread</t>
         </is>
       </c>
     </row>
@@ -3522,16 +3520,16 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>51.5</v>
+        <v>2.5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3545,26 +3543,30 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>48.1</v>
+        <v>-9.5</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.4</v>
+        <v>-12</v>
       </c>
       <c r="K50" t="n">
-        <v>62.7</v>
+        <v>82.3</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:total</t>
+          <t>2026_04_JAX_CIN:spread:D</t>
         </is>
       </c>
     </row>
@@ -3579,16 +3581,16 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>CIN -2.5</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>51.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3602,30 +3604,24 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="J51" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="K51" t="n">
-        <v>62.7</v>
-      </c>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>언더독 JAX 드라이브 득점 차 우위 +0.98 → 반대 CIN · 10-04 09:01 PT 판</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:total:D</t>
+          <t>2026_04_JAX_CIN:spread:A2</t>
         </is>
       </c>
     </row>
@@ -3635,21 +3631,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KC@LV</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>KC -4.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4.5</v>
+        <v>51.5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3663,17 +3659,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>-10</v>
+        <v>48.1</v>
       </c>
       <c r="J52" t="n">
-        <v>-5.5</v>
+        <v>-3.4</v>
       </c>
       <c r="K52" t="n">
-        <v>66.3</v>
+        <v>62.7</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
@@ -3682,7 +3678,7 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:spread</t>
+          <t>2026_04_JAX_CIN:total</t>
         </is>
       </c>
     </row>
@@ -3692,21 +3688,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KC@LV</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>KC -4.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>-4.5</v>
+        <v>51.5</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3724,13 +3720,13 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>-10</v>
+        <v>48.1</v>
       </c>
       <c r="J53" t="n">
-        <v>-5.5</v>
+        <v>-3.4</v>
       </c>
       <c r="K53" t="n">
-        <v>66.3</v>
+        <v>62.7</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
@@ -3743,7 +3739,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:spread:D</t>
+          <t>2026_04_JAX_CIN:total:D</t>
         </is>
       </c>
     </row>
@@ -3758,16 +3754,16 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>KC -4.5</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>47.5</v>
+        <v>4.5</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3785,13 +3781,13 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>38.9</v>
+        <v>-10</v>
       </c>
       <c r="J54" t="n">
-        <v>-8.6</v>
+        <v>-5.5</v>
       </c>
       <c r="K54" t="n">
-        <v>79.3</v>
+        <v>66.3</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
@@ -3800,7 +3796,7 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:total</t>
+          <t>2026_04_KC_LV:spread</t>
         </is>
       </c>
     </row>
@@ -3815,16 +3811,16 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>KC -4.5</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>47.5</v>
+        <v>-4.5</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3842,13 +3838,13 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>38.9</v>
+        <v>-10</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.6</v>
+        <v>-5.5</v>
       </c>
       <c r="K55" t="n">
-        <v>79.3</v>
+        <v>66.3</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
@@ -3861,7 +3857,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:total:D</t>
+          <t>2026_04_KC_LV:spread:D</t>
         </is>
       </c>
     </row>
@@ -3871,21 +3867,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LA@PHI</t>
+          <t>KC@LV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LA -3.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>-3.5</v>
+        <v>47.5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3899,24 +3895,26 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="K56" t="n">
+        <v>79.3</v>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026_04_LA_PHI:spread:D</t>
+          <t>2026_04_KC_LV:total</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3924,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LA@PHI</t>
+          <t>KC@LV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3936,11 +3934,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>42.5</v>
+        <v>47.5</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3954,26 +3952,30 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>46.6</v>
+        <v>38.9</v>
       </c>
       <c r="J57" t="n">
-        <v>4.1</v>
+        <v>-8.6</v>
       </c>
       <c r="K57" t="n">
-        <v>65.2</v>
+        <v>79.3</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026_04_LA_PHI:total</t>
+          <t>2026_04_KC_LV:total:D</t>
         </is>
       </c>
     </row>
@@ -3988,16 +3990,16 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>LA -3.5</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>42.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4014,15 +4016,9 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="J58" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>65.2</v>
-      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -4034,7 +4030,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026_04_LA_PHI:total:D</t>
+          <t>2026_04_LA_PHI:spread:D</t>
         </is>
       </c>
     </row>
@@ -4044,21 +4040,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LAC@SEA</t>
+          <t>LA@PHI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LAC +7</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>-7</v>
+        <v>42.5</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4076,13 +4072,13 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.9</v>
+        <v>46.6</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.1</v>
+        <v>4.1</v>
       </c>
       <c r="K59" t="n">
-        <v>56.4</v>
+        <v>65.2</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
@@ -4091,7 +4087,7 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026_04_LAC_SEA:spread</t>
+          <t>2026_04_LA_PHI:total</t>
         </is>
       </c>
     </row>
@@ -4101,21 +4097,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LAC@SEA</t>
+          <t>LA@PHI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SEA -7</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>-7</v>
+        <v>42.5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4133,13 +4129,13 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.9</v>
+        <v>46.6</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.1</v>
+        <v>4.1</v>
       </c>
       <c r="K60" t="n">
-        <v>56.4</v>
+        <v>65.2</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
@@ -4152,7 +4148,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026_04_LAC_SEA:spread:D</t>
+          <t>2026_04_LA_PHI:total:D</t>
         </is>
       </c>
     </row>
@@ -4167,16 +4163,16 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>LAC +7</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>42.5</v>
+        <v>-7</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4190,17 +4186,17 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>31.5</v>
+        <v>4.9</v>
       </c>
       <c r="J61" t="n">
-        <v>-11</v>
+        <v>-2.1</v>
       </c>
       <c r="K61" t="n">
-        <v>85.3</v>
+        <v>56.4</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
@@ -4209,7 +4205,7 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026_04_LAC_SEA:total</t>
+          <t>2026_04_LAC_SEA:spread</t>
         </is>
       </c>
     </row>
@@ -4224,16 +4220,16 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>SEA -7</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>42.5</v>
+        <v>-7</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -4251,13 +4247,13 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>31.5</v>
+        <v>4.9</v>
       </c>
       <c r="J62" t="n">
-        <v>-11</v>
+        <v>-2.1</v>
       </c>
       <c r="K62" t="n">
-        <v>85.3</v>
+        <v>56.4</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -4270,7 +4266,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026_04_LAC_SEA:total:D</t>
+          <t>2026_04_LAC_SEA:spread:D</t>
         </is>
       </c>
     </row>
@@ -4280,21 +4276,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MIA@MIN</t>
+          <t>LAC@SEA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>MIA +10</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>42.5</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -4308,24 +4304,26 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J63" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K63" t="n">
+        <v>85.3</v>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026_04_MIA_MIN:spread:D</t>
+          <t>2026_04_LAC_SEA:total</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4333,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MIA@MIN</t>
+          <t>LAC@SEA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4345,11 +4343,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>38.5</v>
+        <v>42.5</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -4366,9 +4364,15 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K64" t="n">
+        <v>85.3</v>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
@@ -4380,7 +4384,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026_04_MIA_MIN:total:D</t>
+          <t>2026_04_LAC_SEA:total:D</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4394,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>MIA@MIN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4400,11 +4404,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NE +7</t>
+          <t>MIA +10</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>-7</v>
+        <v>10</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4418,26 +4422,24 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J65" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="K65" t="n">
-        <v>63.2</v>
-      </c>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:spread</t>
+          <t>2026_04_MIA_MIN:spread:D</t>
         </is>
       </c>
     </row>
@@ -4447,21 +4449,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>MIA@MIN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BUF -7</t>
+          <t>Under 38.5</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>-7</v>
+        <v>38.5</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4478,15 +4480,9 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J66" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="K66" t="n">
-        <v>63.2</v>
-      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -4498,7 +4494,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:spread:D</t>
+          <t>2026_04_MIA_MIN:total:D</t>
         </is>
       </c>
     </row>
@@ -4513,16 +4509,16 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>NE +7</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>49.5</v>
+        <v>-7</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4540,13 +4536,13 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>55.3</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
-        <v>5.8</v>
+        <v>-4.4</v>
       </c>
       <c r="K67" t="n">
-        <v>70.90000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
@@ -4555,7 +4551,7 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:total</t>
+          <t>2026_04_NE_BUF:spread</t>
         </is>
       </c>
     </row>
@@ -4570,16 +4566,16 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>BUF -7</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>49.5</v>
+        <v>-7</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4593,24 +4589,30 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>바람 언더(관찰)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J68" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="K68" t="n">
+        <v>63.2</v>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>예보 16mph(NWS 지속·10-04 08:30 PT) · 총점 42+</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:total:wind</t>
+          <t>2026_04_NE_BUF:spread:D</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4650,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4664,14 +4666,10 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:total:D</t>
+          <t>2026_04_NE_BUF:total</t>
         </is>
       </c>
     </row>
@@ -4681,21 +4679,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NYJ@CHI</t>
+          <t>NE@BUF</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CHI -3.5</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>-3.5</v>
+        <v>49.5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4709,26 +4707,24 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J70" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K70" t="n">
-        <v>69.5</v>
-      </c>
+          <t>바람 언더(관찰)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>예보 16mph(NWS 지속·10-04 08:30 PT) · 총점 42+</t>
+        </is>
+      </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:spread</t>
+          <t>2026_04_NE_BUF:total:wind</t>
         </is>
       </c>
     </row>
@@ -4738,21 +4734,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NYJ@CHI</t>
+          <t>NE@BUF</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NYJ +3.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3.5</v>
+        <v>49.5</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4770,13 +4766,13 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>10.1</v>
+        <v>55.3</v>
       </c>
       <c r="J71" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="K71" t="n">
-        <v>69.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
@@ -4789,7 +4785,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:spread:D</t>
+          <t>2026_04_NE_BUF:total:D</t>
         </is>
       </c>
     </row>
@@ -4804,16 +4800,16 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>CHI -3.5</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>43.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4827,17 +4823,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>46.9</v>
+        <v>10.1</v>
       </c>
       <c r="J72" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="K72" t="n">
-        <v>62.7</v>
+        <v>69.5</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
@@ -4846,7 +4842,7 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:total</t>
+          <t>2026_04_NYJ_CHI:spread</t>
         </is>
       </c>
     </row>
@@ -4861,16 +4857,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Under 43.5</t>
+          <t>NYJ +3.5</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>43.5</v>
+        <v>3.5</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4888,13 +4884,13 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>46.9</v>
+        <v>10.1</v>
       </c>
       <c r="J73" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="K73" t="n">
-        <v>62.7</v>
+        <v>69.5</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
@@ -4907,7 +4903,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:total:D</t>
+          <t>2026_04_NYJ_CHI:spread:D</t>
         </is>
       </c>
     </row>
@@ -4917,25 +4913,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>NYJ@CHI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CLE +8.5</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>8.5</v>
+        <v>43.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-270</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4945,34 +4941,26 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>PIT 24-27 CLE</t>
-        </is>
-      </c>
-      <c r="N74" t="n">
-        <v>0.37</v>
-      </c>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="J74" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K74" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>원 라인 +2.5 · 총점 38.5 · 가격 Polymarket No 73c(표시가 — 실베팅 아님)</t>
-        </is>
-      </c>
+      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:spread:T</t>
+          <t>2026_04_NYJ_CHI:total</t>
         </is>
       </c>
     </row>
@@ -4982,21 +4970,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>NYJ@CHI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PIT -2.5</t>
+          <t>Under 43.5</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>-2.5</v>
+        <v>43.5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -5014,27 +5002,17 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>-0.7</v>
+        <v>46.9</v>
       </c>
       <c r="J75" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="K75" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>PIT 24-27 CLE</t>
-        </is>
-      </c>
-      <c r="N75" t="n">
-        <v>-1</v>
-      </c>
+        <v>62.7</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -5043,7 +5021,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:spread:D</t>
+          <t>2026_04_NYJ_CHI:total:D</t>
         </is>
       </c>
     </row>
@@ -5063,25 +5041,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PIT -2.5</t>
+          <t>CLE +8.5</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>-2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-108</t>
+          <t>-270</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>placed</t>
+          <t>suggested</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>실베팅</t>
+          <t>티저 다리(관찰)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -5089,7 +5067,7 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5098,21 +5076,17 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>2026-10-01 11:36</t>
-        </is>
-      </c>
+        <v>0.37</v>
+      </c>
+      <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Paul 자체 판단 0.5u — 발행 판단은 패스(굳이 하나만 PIT -2.5). 체결 Polymarket 「PIT to win by over 2.5 → Yes」 52c(≈ -108, 손익분기 52.0%). Ramsey(PIT CB) Q 상태에서 베팅</t>
+          <t>원 라인 +2.5 · 총점 38.5 · 가격 Polymarket No 73c(표시가 — 실베팅 아님)</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:spread:P</t>
+          <t>2026_04_PIT_CLE:spread:T</t>
         </is>
       </c>
     </row>
@@ -5127,16 +5101,16 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>PIT -2.5</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>38.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -5150,17 +5124,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>34.2</v>
+        <v>-0.7</v>
       </c>
       <c r="J77" t="n">
-        <v>-4.3</v>
+        <v>2.3</v>
       </c>
       <c r="K77" t="n">
-        <v>65.8</v>
+        <v>56.9</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -5176,10 +5150,14 @@
         <v>-1</v>
       </c>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:total</t>
+          <t>2026_04_PIT_CLE:spread:D</t>
         </is>
       </c>
     </row>
@@ -5194,44 +5172,38 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>PIT -2.5</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>38.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-108</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>suggested</t>
+          <t>placed</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="J78" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="K78" t="n">
-        <v>65.8</v>
-      </c>
+          <t>실베팅</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5240,17 +5212,21 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="O78" t="inlineStr"/>
+        <v>-0.5</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:36</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>Paul 자체 판단 0.5u — 발행 판단은 패스(굳이 하나만 PIT -2.5). 체결 Polymarket 「PIT to win by over 2.5 → Yes」 52c(≈ -108, 손익분기 52.0%). Ramsey(PIT CB) Q 상태에서 베팅</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:total:D</t>
+          <t>2026_04_PIT_CLE:spread:P</t>
         </is>
       </c>
     </row>
@@ -5260,21 +5236,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TEN@BAL</t>
+          <t>PIT@CLE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>BAL -11.5</t>
+          <t>Under 38.5</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>-11.5</v>
+        <v>38.5</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -5292,22 +5268,32 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>13.9</v>
+        <v>34.2</v>
       </c>
       <c r="J79" t="n">
-        <v>2.4</v>
+        <v>-4.3</v>
       </c>
       <c r="K79" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+        <v>65.8</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>-1</v>
+      </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>2026_04_TEN_BAL:spread</t>
+          <t>2026_04_PIT_CLE:total</t>
         </is>
       </c>
     </row>
@@ -5317,21 +5303,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TEN@BAL</t>
+          <t>PIT@CLE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TEN +11.5</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>11.5</v>
+        <v>38.5</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -5349,17 +5335,27 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>13.9</v>
+        <v>34.2</v>
       </c>
       <c r="J80" t="n">
-        <v>2.4</v>
+        <v>-4.3</v>
       </c>
       <c r="K80" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+        <v>65.8</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -5368,7 +5364,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2026_04_TEN_BAL:spread:D</t>
+          <t>2026_04_PIT_CLE:total:D</t>
         </is>
       </c>
     </row>
@@ -5383,16 +5379,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>BAL -11.5</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>42.5</v>
+        <v>-11.5</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -5406,17 +5402,17 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>48</v>
+        <v>13.9</v>
       </c>
       <c r="J81" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="K81" t="n">
-        <v>69.90000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
@@ -5425,7 +5421,7 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>2026_04_TEN_BAL:total</t>
+          <t>2026_04_TEN_BAL:spread</t>
         </is>
       </c>
     </row>
@@ -5440,16 +5436,16 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>TEN +11.5</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>42.5</v>
+        <v>11.5</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -5467,13 +5463,13 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>48</v>
+        <v>13.9</v>
       </c>
       <c r="J82" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="K82" t="n">
-        <v>69.90000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
@@ -5485,6 +5481,124 @@
         </is>
       </c>
       <c r="Q82" t="inlineStr">
+        <is>
+          <t>2026_04_TEN_BAL:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>4</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Over 42.5</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>48</v>
+      </c>
+      <c r="J83" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K83" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>2026_04_TEN_BAL:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>4</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Under 42.5</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>48</v>
+      </c>
+      <c r="J84" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K84" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
         <is>
           <t>2026_04_TEN_BAL:total:D</t>
         </is>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -2057,9 +2057,19 @@
       <c r="K24" t="n">
         <v>63.2</v>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ARI 24-36 NYG</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
@@ -2108,9 +2118,19 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ARI 24-36 NYG</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0.833</v>
+      </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -2169,9 +2189,19 @@
       <c r="K26" t="n">
         <v>63.2</v>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>ARI 24-36 NYG</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>-1</v>
+      </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -2222,17 +2252,27 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="J27" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="K27" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+        <v>83.3</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>ARI 24-36 NYG</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
@@ -2287,9 +2327,19 @@
       <c r="K28" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>ARI 24-36 NYG</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>-1</v>
+      </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -2395,13 +2445,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.5</v>
+        <v>-8.6</v>
       </c>
       <c r="K30" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -2452,9 +2502,19 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>DAL 34-30 HOU</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>2026-10-04 09:27</t>
@@ -2517,9 +2577,19 @@
       <c r="K32" t="n">
         <v>62.7</v>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>DAL 34-30 HOU</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>-1</v>
+      </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
@@ -2574,9 +2644,19 @@
       <c r="K33" t="n">
         <v>62.7</v>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>DAL 34-30 HOU</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>-1</v>
+      </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -2629,9 +2709,19 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>DAL 34-30 HOU</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>-1</v>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -2682,17 +2772,27 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
       <c r="J35" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K35" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+        <v>66.2</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>DAL 34-30 HOU</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
@@ -2747,9 +2847,19 @@
       <c r="K36" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>DAL 34-30 HOU</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -2802,9 +2912,19 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>DEN 14-24 SF</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>-1</v>
+      </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -2855,17 +2975,27 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="J38" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="K38" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>DEN 14-24 SF</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>-1</v>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
@@ -2920,9 +3050,19 @@
       <c r="K39" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>DEN 14-24 SF</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>-1</v>
+      </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -2975,9 +3115,19 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>DET 26-32 CAR</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>-1</v>
+      </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -3030,9 +3180,19 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>DET 26-32 CAR</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -3091,9 +3251,19 @@
       <c r="K42" t="n">
         <v>57.6</v>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>GB 17-14 TB</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
@@ -3148,9 +3318,19 @@
       <c r="K43" t="n">
         <v>57.6</v>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>GB 17-14 TB</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -3201,17 +3381,27 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="J44" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K44" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+        <v>66.2</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>GB 17-14 TB</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>-1</v>
+      </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
@@ -3266,9 +3456,19 @@
       <c r="K45" t="n">
         <v>66.5</v>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>GB 17-14 TB</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -3327,9 +3527,19 @@
       <c r="K46" t="n">
         <v>65.3</v>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>IND 30-13 WAS</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
@@ -3382,11 +3592,21 @@
         <v>5.1</v>
       </c>
       <c r="K47" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+        <v>68.5</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>IND 30-13 WAS</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>-1</v>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
@@ -3433,9 +3653,19 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>JAX 22-17 CIN</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>2026-10-04 09:27</t>
@@ -3498,9 +3728,19 @@
       <c r="K49" t="n">
         <v>82.3</v>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>JAX 22-17 CIN</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
@@ -3555,9 +3795,19 @@
       <c r="K50" t="n">
         <v>82.3</v>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>JAX 22-17 CIN</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -3610,9 +3860,19 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>JAX 22-17 CIN</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>-1</v>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -3663,17 +3923,27 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="J52" t="n">
-        <v>-3.4</v>
+        <v>-3.5</v>
       </c>
       <c r="K52" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>JAX 22-17 CIN</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
@@ -3728,9 +3998,19 @@
       <c r="K53" t="n">
         <v>62.7</v>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>JAX 22-17 CIN</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>-1</v>
+      </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -3789,9 +4069,19 @@
       <c r="K54" t="n">
         <v>66.3</v>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>KC 30-27 LV</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>-1</v>
+      </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
@@ -3846,9 +4136,19 @@
       <c r="K55" t="n">
         <v>66.3</v>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>KC 30-27 LV</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>-1</v>
+      </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -3899,17 +4199,27 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.6</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+        <v>79.5</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>KC 30-27 LV</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>-1</v>
+      </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
@@ -3964,9 +4274,19 @@
       <c r="K57" t="n">
         <v>79.3</v>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>KC 30-27 LV</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>-1</v>
+      </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -4019,9 +4339,19 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>LA 24-20 PHI</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -4072,17 +4402,27 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="J59" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K59" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+        <v>64.90000000000001</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>LA 24-20 PHI</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
@@ -4137,9 +4477,19 @@
       <c r="K60" t="n">
         <v>65.2</v>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>LA 24-20 PHI</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>-1</v>
+      </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -4198,9 +4548,19 @@
       <c r="K61" t="n">
         <v>56.4</v>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>LAC 23-30 SEA</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
@@ -4255,9 +4615,19 @@
       <c r="K62" t="n">
         <v>56.4</v>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>LAC 23-30 SEA</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -4308,17 +4678,27 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="J63" t="n">
-        <v>-11</v>
+        <v>-11.1</v>
       </c>
       <c r="K63" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+        <v>85.5</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>LAC 23-30 SEA</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>-1</v>
+      </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
@@ -4373,9 +4753,19 @@
       <c r="K64" t="n">
         <v>85.3</v>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>LAC 23-30 SEA</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>-1</v>
+      </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -4428,9 +4818,19 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>MIA 10-15 MIN</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -4483,9 +4883,19 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>MIA 10-15 MIN</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -4544,9 +4954,19 @@
       <c r="K67" t="n">
         <v>63.2</v>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>NE 29-26 BUF</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
@@ -4601,9 +5021,19 @@
       <c r="K68" t="n">
         <v>63.2</v>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>NE 29-26 BUF</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>-1</v>
+      </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -4654,17 +5084,27 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>55.3</v>
+        <v>55.2</v>
       </c>
       <c r="J69" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="K69" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+        <v>70.59999999999999</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>NE 29-26 BUF</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
@@ -4713,13 +5153,23 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>NE 29-26 BUF</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>-1</v>
+      </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>예보 16mph(NWS 지속·10-04 08:30 PT) · 총점 42+</t>
+          <t>예보 16mph(NWS 지속·10-04 08:30 PT) · 총점 42+ · 실측 wind 결측</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -4774,9 +5224,19 @@
       <c r="K71" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>NE 29-26 BUF</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -4835,9 +5295,19 @@
       <c r="K72" t="n">
         <v>69.5</v>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>NYJ 12-23 CHI</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
@@ -4892,9 +5362,19 @@
       <c r="K73" t="n">
         <v>69.5</v>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>NYJ 12-23 CHI</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>-1</v>
+      </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -4945,17 +5425,27 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
       <c r="J74" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K74" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+        <v>62.4</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>NYJ 12-23 CHI</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>-1</v>
+      </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
@@ -5010,9 +5500,19 @@
       <c r="K75" t="n">
         <v>62.7</v>
       </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>NYJ 12-23 CHI</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -5414,9 +5914,19 @@
       <c r="K81" t="n">
         <v>57.2</v>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>TEN 18-24 BAL</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>-1</v>
+      </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
@@ -5471,9 +5981,19 @@
       <c r="K82" t="n">
         <v>57.2</v>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>TEN 18-24 BAL</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -5524,17 +6044,27 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="J83" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K83" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+        <v>69.59999999999999</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>TEN 18-24 BAL</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>-1</v>
+      </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
@@ -5589,9 +6119,19 @@
       <c r="K84" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>TEN 18-24 BAL</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -5671,13 +6211,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -5686,7 +6226,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -5728,22 +6268,22 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.09</v>
+        <v>-3.09</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -5758,22 +6298,22 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>43</v>
+      </c>
+      <c r="C5" t="n">
         <v>21</v>
       </c>
-      <c r="C5" t="n">
-        <v>11</v>
-      </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>52.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.09</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -5788,10 +6328,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -5803,7 +6343,7 @@
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>0.37</v>
+        <v>1.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -5818,19 +6358,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -5872,19 +6415,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -5950,19 +6496,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -5977,7 +6523,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -5986,6 +6532,9 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
@@ -6093,13 +6642,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -6108,7 +6657,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5</v>
+        <v>-2.5</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -6126,22 +6675,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.13</v>
+        <v>-3.66</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -6152,22 +6701,22 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>13</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" t="n">
         <v>4</v>
       </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>3</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.09</v>
+        <v>-3.27</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -6178,22 +6727,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>55.6</v>
+        <v>54.5</v>
       </c>
       <c r="G25" t="n">
-        <v>0.55</v>
+        <v>0.91</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -6204,22 +6753,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>66.7</v>
+        <v>48.3</v>
       </c>
       <c r="G26" t="n">
-        <v>2.45</v>
+        <v>-2.27</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -6347,13 +6896,13 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -6362,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2049,27 +2049,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="K24" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>ARI 24-36 NYG</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>0.909</v>
-      </c>
+        <v>67.7</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
@@ -2252,27 +2242,17 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>54.7</v>
+        <v>50.7</v>
       </c>
       <c r="J27" t="n">
-        <v>10.2</v>
+        <v>6.2</v>
       </c>
       <c r="K27" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>ARI 24-36 NYG</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>0.909</v>
-      </c>
+        <v>72.40000000000001</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
@@ -2451,7 +2431,7 @@
         <v>-8.6</v>
       </c>
       <c r="K30" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -2569,27 +2549,17 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J32" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K32" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>DAL 34-30 HOU</t>
-        </is>
-      </c>
-      <c r="N32" t="n">
-        <v>-1</v>
-      </c>
+        <v>62.4</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
@@ -2768,31 +2738,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>52.9</v>
+        <v>55.8</v>
       </c>
       <c r="J35" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="K35" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>DAL 34-30 HOU</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
-        <v>0.909</v>
-      </c>
+        <v>75.7</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
@@ -2975,27 +2935,17 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>54.3</v>
+        <v>55.6</v>
       </c>
       <c r="J38" t="n">
-        <v>5.8</v>
+        <v>7.1</v>
       </c>
       <c r="K38" t="n">
-        <v>71</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>DEN 14-24 SF</t>
-        </is>
-      </c>
-      <c r="N38" t="n">
-        <v>-1</v>
-      </c>
+        <v>75.2</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
@@ -3151,16 +3101,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>CAR +4.5</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>51.5</v>
+        <v>4.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3174,34 +3124,26 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>DET 26-32 CAR</t>
-        </is>
-      </c>
-      <c r="N41" t="n">
-        <v>0.909</v>
-      </c>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K41" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026_04_DET_CAR:total:D</t>
+          <t>2026_04_DET_CAR:spread</t>
         </is>
       </c>
     </row>
@@ -3211,21 +3153,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GB@TB</t>
+          <t>DET@CAR</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GB -3</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>51.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3239,36 +3181,34 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="J42" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="K42" t="n">
-        <v>57.6</v>
-      </c>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>GB 17-14 TB</t>
+          <t>DET 26-32 CAR</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>0.909</v>
       </c>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:spread</t>
+          <t>2026_04_DET_CAR:total:D</t>
         </is>
       </c>
     </row>
@@ -3278,21 +3218,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GB@TB</t>
+          <t>DET@CAR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GB -3</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-3</v>
+        <v>52.5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3306,40 +3246,26 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>-5.5</v>
+        <v>57.5</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.5</v>
+        <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>GB 17-14 TB</t>
-        </is>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
+        <v>68.2</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:spread:D</t>
+          <t>2026_04_DET_CAR:total</t>
         </is>
       </c>
     </row>
@@ -3354,16 +3280,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>GB -3</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>38.5</v>
+        <v>3</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3381,32 +3307,22 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>42.9</v>
+        <v>-5.8</v>
       </c>
       <c r="J44" t="n">
-        <v>4.4</v>
+        <v>-2.8</v>
       </c>
       <c r="K44" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>GB 17-14 TB</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>-1</v>
-      </c>
+        <v>58.6</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:total</t>
+          <t>2026_04_GB_TB:spread</t>
         </is>
       </c>
     </row>
@@ -3421,16 +3337,16 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>GB -3</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>38.5</v>
+        <v>-3</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3448,17 +3364,17 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>43</v>
+        <v>-5.5</v>
       </c>
       <c r="J45" t="n">
-        <v>4.5</v>
+        <v>-2.5</v>
       </c>
       <c r="K45" t="n">
-        <v>66.5</v>
+        <v>57.6</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>P</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3467,7 +3383,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0.909</v>
+        <v>0</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -3477,7 +3393,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:total:D</t>
+          <t>2026_04_GB_TB:spread:D</t>
         </is>
       </c>
     </row>
@@ -3487,21 +3403,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IND@WAS</t>
+          <t>GB@TB</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>IND -4.5</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4.5</v>
+        <v>38.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3515,36 +3431,26 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>-9.6</v>
+        <v>42.6</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.1</v>
+        <v>4.1</v>
       </c>
       <c r="K46" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>IND 30-13 WAS</t>
-        </is>
-      </c>
-      <c r="N46" t="n">
-        <v>0.909</v>
-      </c>
+        <v>65.09999999999999</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026_04_IND_WAS:spread</t>
+          <t>2026_04_GB_TB:total</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3460,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IND@WAS</t>
+          <t>GB@TB</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3564,11 +3470,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Under 38.5</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>46.5</v>
+        <v>38.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3582,36 +3488,40 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>51.6</v>
+        <v>43</v>
       </c>
       <c r="J47" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="K47" t="n">
-        <v>68.5</v>
+        <v>66.5</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>IND 30-13 WAS</t>
+          <t>GB 17-14 TB</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026_04_IND_WAS:total</t>
+          <t>2026_04_GB_TB:total:D</t>
         </is>
       </c>
     </row>
@@ -3621,64 +3531,54 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JAX@CIN</t>
+          <t>IND@WAS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CIN ML</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>IND -4.5</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4.5</v>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-148</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>placed</t>
+          <t>suggested</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>실베팅</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>JAX 22-17 CIN</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>2026-10-04 09:27</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Paul 실베팅 — A2 패턴(드라이브 우위 언더독 JAX의 반대) ML. 배당은 수집값(DK −148) 그대로(Paul). 금액 미확인 — 권장 0.5u 로 임시</t>
-        </is>
-      </c>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="K48" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:ml:P</t>
+          <t>2026_04_IND_WAS:spread</t>
         </is>
       </c>
     </row>
@@ -3688,21 +3588,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JAX@CIN</t>
+          <t>IND@WAS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-2.5</v>
+        <v>46.5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3720,32 +3620,32 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>-9.5</v>
+        <v>51.6</v>
       </c>
       <c r="J49" t="n">
-        <v>-12</v>
+        <v>5.1</v>
       </c>
       <c r="K49" t="n">
-        <v>82.3</v>
+        <v>68.5</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>JAX 22-17 CIN</t>
+          <t>IND 30-13 WAS</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:spread</t>
+          <t>2026_04_IND_WAS:total</t>
         </is>
       </c>
     </row>
@@ -3760,44 +3660,36 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>2.5</v>
-      </c>
+          <t>CIN ML</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-148</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>suggested</t>
+          <t>placed</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="J50" t="n">
-        <v>-12</v>
-      </c>
-      <c r="K50" t="n">
-        <v>82.3</v>
-      </c>
+          <t>실베팅</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3806,17 +3698,21 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="O50" t="inlineStr"/>
+        <v>-0.5</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2026-10-04 09:27</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>Paul 실베팅 — A2 패턴(드라이브 우위 언더독 JAX의 반대) ML. 배당은 수집값(DK −148) 그대로(Paul). 금액 미확인 — 권장 0.5u 로 임시</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:spread:D</t>
+          <t>2026_04_JAX_CIN:ml:P</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3732,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CIN -2.5</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -3854,34 +3750,26 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>JAX 22-17 CIN</t>
-        </is>
-      </c>
-      <c r="N51" t="n">
-        <v>-1</v>
-      </c>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="K51" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>언더독 JAX 드라이브 득점 차 우위 +0.98 → 반대 CIN · 10-04 09:01 PT 판</t>
-        </is>
-      </c>
+      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:spread:A2</t>
+          <t>2026_04_JAX_CIN:spread</t>
         </is>
       </c>
     </row>
@@ -3896,16 +3784,16 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>51.5</v>
+        <v>2.5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3919,17 +3807,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>48</v>
+        <v>-9.5</v>
       </c>
       <c r="J52" t="n">
-        <v>-3.5</v>
+        <v>-12</v>
       </c>
       <c r="K52" t="n">
-        <v>63</v>
+        <v>82.3</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3945,10 +3833,14 @@
         <v>0.909</v>
       </c>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:total</t>
+          <t>2026_04_JAX_CIN:spread:D</t>
         </is>
       </c>
     </row>
@@ -3963,16 +3855,16 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>CIN -2.5</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>51.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3986,18 +3878,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="J53" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="K53" t="n">
-        <v>62.7</v>
-      </c>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>L</t>
@@ -4014,12 +3900,12 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>언더독 JAX 드라이브 득점 차 우위 +0.98 → 반대 CIN · 10-04 09:01 PT 판</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:total:D</t>
+          <t>2026_04_JAX_CIN:spread:A2</t>
         </is>
       </c>
     </row>
@@ -4029,21 +3915,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>KC@LV</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KC -4.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4.5</v>
+        <v>51.5</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4057,36 +3943,36 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>-10</v>
+        <v>48</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.5</v>
+        <v>-3.5</v>
       </c>
       <c r="K54" t="n">
-        <v>66.3</v>
+        <v>63</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>KC 30-27 LV</t>
+          <t>JAX 22-17 CIN</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:spread</t>
+          <t>2026_04_JAX_CIN:total</t>
         </is>
       </c>
     </row>
@@ -4096,21 +3982,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KC@LV</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KC -4.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>-4.5</v>
+        <v>51.5</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4128,13 +4014,13 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>-10</v>
+        <v>48.1</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.5</v>
+        <v>-3.4</v>
       </c>
       <c r="K55" t="n">
-        <v>66.3</v>
+        <v>62.7</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -4143,7 +4029,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>KC 30-27 LV</t>
+          <t>JAX 22-17 CIN</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -4157,7 +4043,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:spread:D</t>
+          <t>2026_04_JAX_CIN:total:D</t>
         </is>
       </c>
     </row>
@@ -4172,16 +4058,16 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>KC -4.5</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>47.5</v>
+        <v>4.5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4199,32 +4085,22 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>38.8</v>
+        <v>-9.6</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.699999999999999</v>
+        <v>-5.1</v>
       </c>
       <c r="K56" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>KC 30-27 LV</t>
-        </is>
-      </c>
-      <c r="N56" t="n">
-        <v>-1</v>
-      </c>
+        <v>65.09999999999999</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:total</t>
+          <t>2026_04_KC_LV:spread</t>
         </is>
       </c>
     </row>
@@ -4239,16 +4115,16 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>KC -4.5</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>47.5</v>
+        <v>-4.5</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4266,13 +4142,13 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>38.9</v>
+        <v>-10</v>
       </c>
       <c r="J57" t="n">
-        <v>-8.6</v>
+        <v>-5.5</v>
       </c>
       <c r="K57" t="n">
-        <v>79.3</v>
+        <v>66.3</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -4295,7 +4171,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:total:D</t>
+          <t>2026_04_KC_LV:spread:D</t>
         </is>
       </c>
     </row>
@@ -4305,21 +4181,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LA@PHI</t>
+          <t>KC@LV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LA -3.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>-3.5</v>
+        <v>47.5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4333,34 +4209,26 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>LA 24-20 PHI</t>
-        </is>
-      </c>
-      <c r="N58" t="n">
-        <v>0.909</v>
-      </c>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="K58" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026_04_LA_PHI:spread:D</t>
+          <t>2026_04_KC_LV:total</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4238,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LA@PHI</t>
+          <t>KC@LV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4380,11 +4248,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>42.5</v>
+        <v>47.5</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4398,36 +4266,40 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>46.5</v>
+        <v>38.9</v>
       </c>
       <c r="J59" t="n">
-        <v>4</v>
+        <v>-8.6</v>
       </c>
       <c r="K59" t="n">
-        <v>64.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>LA 24-20 PHI</t>
+          <t>KC 30-27 LV</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026_04_LA_PHI:total</t>
+          <t>2026_04_KC_LV:total:D</t>
         </is>
       </c>
     </row>
@@ -4442,16 +4314,16 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>LA -3.5</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>42.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4468,18 +4340,12 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="J60" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K60" t="n">
-        <v>65.2</v>
-      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4488,7 +4354,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
@@ -4498,7 +4364,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026_04_LA_PHI:total:D</t>
+          <t>2026_04_LA_PHI:spread:D</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4374,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LAC@SEA</t>
+          <t>LA@PHI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4518,11 +4384,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LAC +7</t>
+          <t>LA -3.5</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>-7</v>
+        <v>3.5</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4536,36 +4402,26 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.9</v>
+        <v>-7.5</v>
       </c>
       <c r="J61" t="n">
-        <v>-2.1</v>
+        <v>-4</v>
       </c>
       <c r="K61" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>LAC 23-30 SEA</t>
-        </is>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
+        <v>62.1</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026_04_LAC_SEA:spread</t>
+          <t>2026_04_LA_PHI:spread</t>
         </is>
       </c>
     </row>
@@ -4575,21 +4431,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LAC@SEA</t>
+          <t>LA@PHI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SEA -7</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>-7</v>
+        <v>42.5</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -4603,40 +4459,36 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.9</v>
+        <v>46.5</v>
       </c>
       <c r="J62" t="n">
-        <v>-2.1</v>
+        <v>4</v>
       </c>
       <c r="K62" t="n">
-        <v>56.4</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>LAC 23-30 SEA</t>
+          <t>LA 24-20 PHI</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>0.909</v>
       </c>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026_04_LAC_SEA:spread:D</t>
+          <t>2026_04_LA_PHI:total</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4498,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LAC@SEA</t>
+          <t>LA@PHI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4674,17 +4526,17 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>31.4</v>
+        <v>46.6</v>
       </c>
       <c r="J63" t="n">
-        <v>-11.1</v>
+        <v>4.1</v>
       </c>
       <c r="K63" t="n">
-        <v>85.5</v>
+        <v>65.2</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -4693,17 +4545,21 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>LAC 23-30 SEA</t>
+          <t>LA 24-20 PHI</t>
         </is>
       </c>
       <c r="N63" t="n">
         <v>-1</v>
       </c>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026_04_LAC_SEA:total</t>
+          <t>2026_04_LA_PHI:total:D</t>
         </is>
       </c>
     </row>
@@ -4718,16 +4574,16 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>LAC +7</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>42.5</v>
+        <v>-7</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -4741,40 +4597,26 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>31.5</v>
+        <v>4.3</v>
       </c>
       <c r="J64" t="n">
-        <v>-11</v>
+        <v>-2.7</v>
       </c>
       <c r="K64" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>LAC 23-30 SEA</t>
-        </is>
-      </c>
-      <c r="N64" t="n">
-        <v>-1</v>
-      </c>
+        <v>58.1</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026_04_LAC_SEA:total:D</t>
+          <t>2026_04_LAC_SEA:spread</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4626,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MIA@MIN</t>
+          <t>LAC@SEA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4794,11 +4636,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MIA +10</t>
+          <t>SEA -7</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>10</v>
+        <v>-7</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4815,21 +4657,27 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>56.4</v>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>P</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>MIA 10-15 MIN</t>
+          <t>LAC 23-30 SEA</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0.909</v>
+        <v>0</v>
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -4839,7 +4687,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026_04_MIA_MIN:spread:D</t>
+          <t>2026_04_LAC_SEA:spread:D</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4697,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MIA@MIN</t>
+          <t>LAC@SEA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4859,11 +4707,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>38.5</v>
+        <v>42.5</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4877,34 +4725,26 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>MIA 10-15 MIN</t>
-        </is>
-      </c>
-      <c r="N66" t="n">
-        <v>0.909</v>
-      </c>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K66" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026_04_MIA_MIN:total:D</t>
+          <t>2026_04_LAC_SEA:total</t>
         </is>
       </c>
     </row>
@@ -4914,21 +4754,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>LAC@SEA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NE +7</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>-7</v>
+        <v>42.5</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4942,36 +4782,40 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.6</v>
+        <v>31.5</v>
       </c>
       <c r="J67" t="n">
-        <v>-4.4</v>
+        <v>-11</v>
       </c>
       <c r="K67" t="n">
-        <v>63.2</v>
+        <v>85.3</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>NE 29-26 BUF</t>
+          <t>LAC 23-30 SEA</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:spread</t>
+          <t>2026_04_LAC_SEA:total:D</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4825,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>MIA@MIN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4991,11 +4835,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BUF -7</t>
+          <t>MIA +10</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>-7</v>
+        <v>10</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5012,27 +4856,21 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J68" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="K68" t="n">
-        <v>63.2</v>
-      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>NE 29-26 BUF</t>
+          <t>MIA 10-15 MIN</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -5042,7 +4880,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:spread:D</t>
+          <t>2026_04_MIA_MIN:spread:D</t>
         </is>
       </c>
     </row>
@@ -5052,7 +4890,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>MIA@MIN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5062,11 +4900,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>Under 38.5</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>49.5</v>
+        <v>38.5</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5080,18 +4918,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I69" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="J69" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K69" t="n">
-        <v>70.59999999999999</v>
-      </c>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>W</t>
@@ -5099,17 +4931,21 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>NE 29-26 BUF</t>
+          <t>MIA 10-15 MIN</t>
         </is>
       </c>
       <c r="N69" t="n">
         <v>0.909</v>
       </c>
       <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:total</t>
+          <t>2026_04_MIA_MIN:total:D</t>
         </is>
       </c>
     </row>
@@ -5124,16 +4960,16 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>NE +7</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>49.5</v>
+        <v>-7</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5147,34 +4983,26 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>바람 언더(관찰)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>NE 29-26 BUF</t>
-        </is>
-      </c>
-      <c r="N70" t="n">
-        <v>-1</v>
-      </c>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="K70" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>예보 16mph(NWS 지속·10-04 08:30 PT) · 총점 42+ · 실측 wind 결측</t>
-        </is>
-      </c>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:total:wind</t>
+          <t>2026_04_NE_BUF:spread</t>
         </is>
       </c>
     </row>
@@ -5189,16 +5017,16 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>BUF -7</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>49.5</v>
+        <v>-7</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5216,17 +5044,17 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>55.3</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
-        <v>5.8</v>
+        <v>-4.4</v>
       </c>
       <c r="K71" t="n">
-        <v>70.90000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5235,7 +5063,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
@@ -5245,7 +5073,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:total:D</t>
+          <t>2026_04_NE_BUF:spread:D</t>
         </is>
       </c>
     </row>
@@ -5255,21 +5083,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NYJ@CHI</t>
+          <t>NE@BUF</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CHI -3.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>-3.5</v>
+        <v>49.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5287,32 +5115,22 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>10.1</v>
+        <v>57.4</v>
       </c>
       <c r="J72" t="n">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
       <c r="K72" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>NYJ 12-23 CHI</t>
-        </is>
-      </c>
-      <c r="N72" t="n">
-        <v>0.909</v>
-      </c>
+        <v>77.3</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:spread</t>
+          <t>2026_04_NE_BUF:total</t>
         </is>
       </c>
     </row>
@@ -5322,21 +5140,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NYJ@CHI</t>
+          <t>NE@BUF</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NYJ +3.5</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3.5</v>
+        <v>49.5</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5350,18 +5168,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I73" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J73" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K73" t="n">
-        <v>69.5</v>
-      </c>
+          <t>바람 언더(관찰)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>L</t>
@@ -5369,7 +5181,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>NYJ 12-23 CHI</t>
+          <t>NE 29-26 BUF</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -5378,12 +5190,12 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>예보 16mph(NWS 지속·10-04 08:30 PT) · 총점 42+ · 실측 wind 결측</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:spread:D</t>
+          <t>2026_04_NE_BUF:total:wind</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5205,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NYJ@CHI</t>
+          <t>NE@BUF</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5403,11 +5215,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>43.5</v>
+        <v>49.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5421,36 +5233,40 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>46.8</v>
+        <v>55.3</v>
       </c>
       <c r="J74" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="K74" t="n">
-        <v>62.4</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>NYJ 12-23 CHI</t>
+          <t>NE 29-26 BUF</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:total</t>
+          <t>2026_04_NE_BUF:total:D</t>
         </is>
       </c>
     </row>
@@ -5465,16 +5281,16 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Under 43.5</t>
+          <t>CHI -3.5</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>43.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -5488,40 +5304,26 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>46.9</v>
+        <v>10.4</v>
       </c>
       <c r="J75" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="K75" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>NYJ 12-23 CHI</t>
-        </is>
-      </c>
-      <c r="N75" t="n">
-        <v>0.909</v>
-      </c>
+        <v>70.3</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:total:D</t>
+          <t>2026_04_NYJ_CHI:spread</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5333,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>NYJ@CHI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5541,15 +5343,15 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CLE +8.5</t>
+          <t>NYJ +3.5</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-270</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5559,34 +5361,40 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K76" t="n">
+        <v>69.5</v>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>PIT 24-27 CLE</t>
+          <t>NYJ 12-23 CHI</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0.37</v>
+        <v>-1</v>
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>원 라인 +2.5 · 총점 38.5 · 가격 Polymarket No 73c(표시가 — 실베팅 아님)</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:spread:T</t>
+          <t>2026_04_NYJ_CHI:spread:D</t>
         </is>
       </c>
     </row>
@@ -5596,21 +5404,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>NYJ@CHI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>PIT -2.5</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>-2.5</v>
+        <v>43.5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -5624,17 +5432,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>-0.7</v>
+        <v>46.8</v>
       </c>
       <c r="J77" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="K77" t="n">
-        <v>56.9</v>
+        <v>62.4</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -5643,21 +5451,17 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>PIT 24-27 CLE</t>
+          <t>NYJ 12-23 CHI</t>
         </is>
       </c>
       <c r="N77" t="n">
         <v>-1</v>
       </c>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:spread:D</t>
+          <t>2026_04_NYJ_CHI:total</t>
         </is>
       </c>
     </row>
@@ -5667,66 +5471,68 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>NYJ@CHI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PIT -2.5</t>
+          <t>Under 43.5</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>-2.5</v>
+        <v>43.5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-108</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>placed</t>
+          <t>suggested</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>실베팅</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="J78" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K78" t="n">
+        <v>62.7</v>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>PIT 24-27 CLE</t>
+          <t>NYJ 12-23 CHI</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>2026-10-01 11:36</t>
-        </is>
-      </c>
+        <v>0.909</v>
+      </c>
+      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Paul 자체 판단 0.5u — 발행 판단은 패스(굳이 하나만 PIT -2.5). 체결 Polymarket 「PIT to win by over 2.5 → Yes」 52c(≈ -108, 손익분기 52.0%). Ramsey(PIT CB) Q 상태에서 베팅</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:spread:P</t>
+          <t>2026_04_NYJ_CHI:total:D</t>
         </is>
       </c>
     </row>
@@ -5741,20 +5547,20 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>CLE +8.5</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>38.5</v>
+        <v>8.5</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-270</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5764,21 +5570,15 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="J79" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="K79" t="n">
-        <v>65.8</v>
-      </c>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5787,13 +5587,17 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>-1</v>
+        <v>0.37</v>
       </c>
       <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 38.5 · 가격 Polymarket No 73c(표시가 — 실베팅 아님)</t>
+        </is>
+      </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:total</t>
+          <t>2026_04_PIT_CLE:spread:T</t>
         </is>
       </c>
     </row>
@@ -5808,16 +5612,16 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>PIT -2.5</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>38.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -5835,17 +5639,17 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>34.2</v>
+        <v>-0.7</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.3</v>
+        <v>2.3</v>
       </c>
       <c r="K80" t="n">
-        <v>65.8</v>
+        <v>56.9</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5854,7 +5658,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
@@ -5864,7 +5668,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:total:D</t>
+          <t>2026_04_PIT_CLE:spread:D</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5678,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TEN@BAL</t>
+          <t>PIT@CLE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5884,36 +5688,30 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>BAL -11.5</t>
+          <t>PIT -2.5</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>-11.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-108</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>suggested</t>
+          <t>placed</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="J81" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K81" t="n">
-        <v>57.2</v>
-      </c>
+          <t>실베팅</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
           <t>L</t>
@@ -5921,17 +5719,25 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>TEN 18-24 BAL</t>
+          <t>PIT 24-27 CLE</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
+        <v>-0.5</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:36</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Paul 자체 판단 0.5u — 발행 판단은 패스(굳이 하나만 PIT -2.5). 체결 Polymarket 「PIT to win by over 2.5 → Yes」 52c(≈ -108, 손익분기 52.0%). Ramsey(PIT CB) Q 상태에서 베팅</t>
+        </is>
+      </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>2026_04_TEN_BAL:spread</t>
+          <t>2026_04_PIT_CLE:spread:P</t>
         </is>
       </c>
     </row>
@@ -5941,21 +5747,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TEN@BAL</t>
+          <t>PIT@CLE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>TEN +11.5</t>
+          <t>Under 38.5</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>11.5</v>
+        <v>38.5</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -5969,40 +5775,36 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>13.9</v>
+        <v>34.2</v>
       </c>
       <c r="J82" t="n">
-        <v>2.4</v>
+        <v>-4.3</v>
       </c>
       <c r="K82" t="n">
-        <v>57.2</v>
+        <v>65.8</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>TEN 18-24 BAL</t>
+          <t>PIT 24-27 CLE</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>2026_04_TEN_BAL:spread:D</t>
+          <t>2026_04_PIT_CLE:total</t>
         </is>
       </c>
     </row>
@@ -6012,7 +5814,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TEN@BAL</t>
+          <t>PIT@CLE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6022,11 +5824,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>42.5</v>
+        <v>38.5</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6040,36 +5842,40 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>47.9</v>
+        <v>34.2</v>
       </c>
       <c r="J83" t="n">
-        <v>5.4</v>
+        <v>-4.3</v>
       </c>
       <c r="K83" t="n">
-        <v>69.59999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>TEN 18-24 BAL</t>
+          <t>PIT 24-27 CLE</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>2026_04_TEN_BAL:total</t>
+          <t>2026_04_PIT_CLE:total:D</t>
         </is>
       </c>
     </row>
@@ -6084,61 +5890,246 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>BAL -11.5</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="J84" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K84" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>2026_04_TEN_BAL:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>TEN +11.5</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J85" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K85" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>TEN 18-24 BAL</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>2026_04_TEN_BAL:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>4</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
           <t>total</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Over 42.5</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>48</v>
+      </c>
+      <c r="J86" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K86" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>2026_04_TEN_BAL:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>4</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
         <is>
           <t>Under 42.5</t>
         </is>
       </c>
-      <c r="E84" t="n">
+      <c r="E87" t="n">
         <v>42.5</v>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>-110</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I84" t="n">
+      <c r="I87" t="n">
         <v>48</v>
       </c>
-      <c r="J84" t="n">
+      <c r="J87" t="n">
         <v>5.5</v>
       </c>
-      <c r="K84" t="n">
+      <c r="K87" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>TEN 18-24 BAL</t>
         </is>
       </c>
-      <c r="N84" t="n">
+      <c r="N87" t="n">
         <v>0.909</v>
       </c>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
         <is>
           <t>발행 방향</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>2026_04_TEN_BAL:total:D</t>
         </is>
@@ -6264,7 +6255,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>발행 방향(페이퍼)</t>
+          <t>발행 방향(예측 쪽)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6279,15 +6270,12 @@
       <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="n">
-        <v>46.2</v>
-      </c>
       <c r="G4" t="n">
         <v>-3.09</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>발행 세션 방향 줄 — 패스 포함 전 경기·스프레드+총점(10/1~)</t>
+          <t>발행 세션 방향 줄 — 예측 점수에서 나온 쪽(10/1~). 2018~25 어떤 별점에서도 스프레드 ≈49% = 동전 · 유닛 미표시</t>
         </is>
       </c>
     </row>
@@ -6298,22 +6286,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>52.5</v>
+        <v>54.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09</v>
+        <v>0.82</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -6701,22 +6689,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.27</v>
+        <v>-2.27</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -6727,22 +6715,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>54.5</v>
+        <v>52.9</v>
       </c>
       <c r="G25" t="n">
-        <v>0.91</v>
+        <v>0.18</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -6753,22 +6741,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C26" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>48.3</v>
+        <v>47.4</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.27</v>
+        <v>-1.82</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:Q109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -535,11 +535,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARI@SF</t>
+          <t>ARI@LAC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -549,15 +549,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SF -7.5</t>
+          <t>LAC -2.5</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>-7.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -567,18 +567,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>61.7</v>
-      </c>
+          <t>티저 다리(소급)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>L</t>
@@ -586,45 +580,49 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ARI 30-36 SF</t>
+          <t>ARI 26-14 LAC</t>
         </is>
       </c>
       <c r="N2" t="n">
         <v>-1</v>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>소급 · 원 라인 -8.5 · 총점 47.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026_03_ARI_SF:spread</t>
+          <t>2026_01_ARI_LAC:spread:TB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ARI@SF</t>
+          <t>BUF@HOU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>HOU +7.5</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.5</v>
+        <v>7.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -634,18 +632,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>61</v>
-      </c>
-      <c r="J3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>88.3</v>
-      </c>
+          <t>티저 다리(소급)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>W</t>
@@ -653,45 +645,49 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ARI 30-36 SF</t>
+          <t>BUF 36-31 HOU</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.909</v>
+        <v>0.353</v>
       </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>소급 · 원 라인 +1.5 · 총점 44.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026_03_ARI_SF:total</t>
+          <t>2026_01_BUF_HOU:spread:TB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ATL@GB</t>
+          <t>CLE@JAX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>JAX -2.5</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>43.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -701,18 +697,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>65.5</v>
-      </c>
+          <t>티저 다리(소급)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>W</t>
@@ -720,45 +710,49 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ATL 35-14 GB</t>
+          <t>CLE 10-34 JAX</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.909</v>
+        <v>0.353</v>
       </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>소급 · 원 라인 -8.5 · 총점 40.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026_03_ATL_GB:total</t>
+          <t>2026_01_CLE_JAX:spread:TB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BAL@DAL</t>
+          <t>DEN@KC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>DEN +8.5</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53.5</v>
+        <v>8.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -768,46 +762,44 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>85.90000000000001</v>
-      </c>
+          <t>티저 다리(소급)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>BAL 34-31 DAL</t>
+          <t>DEN 10-31 KC</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>소급 · 원 라인 +2.5 · 총점 42.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026_03_BAL_DAL:total</t>
+          <t>2026_01_DEN_KC:spread:TB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CAR@CLE</t>
+          <t>GB@MIN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -817,15 +809,15 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CLE +2.5</t>
+          <t>GB +8.5</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -835,64 +827,62 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>58</v>
-      </c>
+          <t>티저 다리(소급)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CAR 18-21 CLE</t>
+          <t>GB 22-39 MIN</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>소급 · 원 라인 +2.5 · 총점 46.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026_03_CAR_CLE:spread</t>
+          <t>2026_01_GB_MIN:spread:TB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CAR@CLE</t>
+          <t>NYJ@TEN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Under 41.5</t>
+          <t>NYJ +7.5</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>41.5</v>
+        <v>7.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -902,18 +892,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>68.8</v>
-      </c>
+          <t>티저 다리(소급)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>W</t>
@@ -921,27 +905,31 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>CAR 18-21 CLE</t>
+          <t>NYJ 23-10 TEN</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.909</v>
+        <v>0.353</v>
       </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>소급 · 원 라인 +1.5 · 총점 39.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026_03_CAR_CLE:total</t>
+          <t>2026_01_NYJ_TEN:spread:TB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CIN@PIT</t>
+          <t>CAR@ATL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -951,15 +939,15 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PIT +3.5</t>
+          <t>ATL +8.5</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -969,64 +957,62 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>68.2</v>
-      </c>
+          <t>티저 다리(소급)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>CIN 27-30 PIT</t>
+          <t>CAR 34-3 ATL</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>소급 · 원 라인 +2.5 · 총점 43.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026_03_CIN_PIT:spread</t>
+          <t>2026_02_CAR_ATL:spread:TB</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIN@PIT</t>
+          <t>CLE@TB</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>TB -2.5</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1036,64 +1022,62 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>74.3</v>
-      </c>
+          <t>티저 다리(소급)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>CIN 27-30 PIT</t>
+          <t>CLE 23-19 TB</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>소급 · 원 라인 -8.5 · 총점 41.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026_03_CIN_PIT:total</t>
+          <t>2026_02_CLE_TB:spread:TB</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KC@MIA</t>
+          <t>JAX@DEN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>JAX +8.5</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>45.5</v>
+        <v>8.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1103,46 +1087,44 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>51</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>69.90000000000001</v>
-      </c>
+          <t>티저 다리(소급)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>KC 24-10 MIA</t>
+          <t>JAX 13-20 DEN</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
+        <v>0.353</v>
       </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>소급 · 원 라인 +2.5 · 총점 45.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026_03_KC_MIA:total</t>
+          <t>2026_02_JAX_DEN:spread:TB</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA@DEN</t>
+          <t>NO@BAL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1152,15 +1134,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LA +1.5</t>
+          <t>BAL -2.5</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>-1.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1170,18 +1152,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="K11" t="n">
-        <v>64.3</v>
-      </c>
+          <t>티저 다리(소급)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>L</t>
@@ -1189,41 +1165,45 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>LA 26-30 DEN</t>
+          <t>NO 24-17 BAL</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>-1</v>
       </c>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>소급 · 원 라인 -8.5 · 총점 45.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026_03_LA_DEN:spread</t>
+          <t>2026_02_NO_BAL:spread:TB</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA@DEN</t>
+          <t>PHI@TEN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>TEN +7</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>43.5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1237,18 +1217,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>47</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>63.1</v>
-      </c>
+          <t>각도 관찰 A1(소급)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>W</t>
@@ -1256,17 +1230,21 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>LA 26-30 DEN</t>
+          <t>PHI 24-20 TEN</t>
         </is>
       </c>
       <c r="N12" t="n">
         <v>0.909</v>
       </c>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>소급 · 원정 PHI -7 페이버릿 · DK 마감</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026_03_LA_DEN:total</t>
+          <t>2026_02_PHI_TEN:spread:A1B</t>
         </is>
       </c>
     </row>
@@ -1276,21 +1254,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA@DEN</t>
+          <t>ARI@SF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>SF -7.5</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>44.5</v>
+        <v>-7.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1299,17 +1277,23 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>placed</t>
+          <t>suggested</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>실베팅</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>61.7</v>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>L</t>
@@ -1317,25 +1301,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>LA 26-30 DEN</t>
+          <t>ARI 30-36 SF</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>-1</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Paul 실베팅 9/27(claude.ai 대화 — 언더 44.5) · 9/28 사후 기록 · 라이브 진입이면 라인·배당 정정 필요</t>
-        </is>
-      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026_03_LA_DEN:total:P</t>
+          <t>2026_03_ARI_SF:spread</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1321,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LV@NO</t>
+          <t>ARI@SF</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1355,15 +1331,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NO -3.5</t>
+          <t>SF -1.5</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>-3.5</v>
+        <v>-1.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1373,36 +1349,34 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>56.4</v>
-      </c>
+          <t>티저 다리(소급)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>LV 35-27 NO</t>
+          <t>ARI 30-36 SF</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>-1</v>
+        <v>0.353</v>
       </c>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>소급 · 원 라인 -7.5 · 총점 48.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026_03_LV_NO:spread</t>
+          <t>2026_03_ARI_SF:spread:TB</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1386,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LV@NO</t>
+          <t>ARI@SF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1422,11 +1396,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Under 43.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>43.5</v>
+        <v>48.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1444,32 +1418,32 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>33.6</v>
+        <v>61</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.9</v>
+        <v>12.5</v>
       </c>
       <c r="K15" t="n">
-        <v>82.8</v>
+        <v>88.3</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>LV 35-27 NO</t>
+          <t>ARI 30-36 SF</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026_03_LV_NO:total</t>
+          <t>2026_03_ARI_SF:total</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1453,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIN@TB</t>
+          <t>ATL@GB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1489,11 +1463,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>42.5</v>
+        <v>43.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1507,17 +1481,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>31</v>
+        <v>47.7</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.5</v>
+        <v>4.2</v>
       </c>
       <c r="K16" t="n">
-        <v>86.2</v>
+        <v>65.5</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1526,7 +1500,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>MIN 23-16 TB</t>
+          <t>ATL 35-14 GB</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -1536,7 +1510,7 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026_03_MIN_TB:total</t>
+          <t>2026_03_ATL_GB:total</t>
         </is>
       </c>
     </row>
@@ -1546,21 +1520,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NYJ@DET</t>
+          <t>BAL@DAL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DET -7</t>
+          <t>Over 53.5</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-7</v>
+        <v>53.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1578,32 +1552,32 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>12.8</v>
+        <v>64.8</v>
       </c>
       <c r="J17" t="n">
-        <v>5.8</v>
+        <v>11.3</v>
       </c>
       <c r="K17" t="n">
-        <v>67.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>NYJ 24-31 DET</t>
+          <t>BAL 34-31 DAL</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.909</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026_03_NYJ_DET:spread</t>
+          <t>2026_03_BAL_DAL:total</t>
         </is>
       </c>
     </row>
@@ -1613,21 +1587,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NYJ@DET</t>
+          <t>CAR@CLE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>CLE +2.5</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>49.5</v>
+        <v>2.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1645,13 +1619,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>54.1</v>
+        <v>0.1</v>
       </c>
       <c r="J18" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="K18" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1660,7 +1634,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>NYJ 24-31 DET</t>
+          <t>CAR 18-21 CLE</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1670,7 +1644,7 @@
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026_03_NYJ_DET:total</t>
+          <t>2026_03_CAR_CLE:spread</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1654,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PHI@CHI</t>
+          <t>CAR@CLE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1690,25 +1664,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PHI -3.5</t>
+          <t>CLE +8.5</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>-3.5</v>
+        <v>8.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>placed</t>
+          <t>suggested</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>관심(설명문)</t>
+          <t>티저 다리(소급)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1716,30 +1690,26 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>PHI 7-27 CHI</t>
+          <t>CAR 18-21 CLE</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2026-09-28 13:15</t>
-        </is>
-      </c>
+        <v>0.353</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Paul 실베팅 9/28 — 설명문 판단(소액 관심) 동일</t>
+          <t>소급 · 원 라인 +2.5 · 총점 41.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026_03_PHI_CHI:spread</t>
+          <t>2026_03_CAR_CLE:spread:TB</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1719,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PHI@CHI</t>
+          <t>CAR@CLE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1759,7 +1729,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>Under 41.5</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1777,36 +1747,36 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>참고 ※</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>46.1</v>
+        <v>36.4</v>
       </c>
       <c r="J20" t="n">
-        <v>4.6</v>
+        <v>-5.1</v>
       </c>
       <c r="K20" t="n">
-        <v>67</v>
+        <v>68.8</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>PHI 7-27 CHI</t>
+          <t>CAR 18-21 CLE</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026_03_PHI_CHI:total</t>
+          <t>2026_03_CAR_CLE:total</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1786,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SEA@WAS</t>
+          <t>CIN@PIT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1826,11 +1796,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SEA -8.5</t>
+          <t>PIT +3.5</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1844,36 +1814,36 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>-11.7</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.2</v>
+        <v>6.2</v>
       </c>
       <c r="K21" t="n">
-        <v>59.6</v>
+        <v>68.2</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>SEA 31-33 WAS</t>
+          <t>CIN 27-30 PIT</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026_03_SEA_WAS:spread</t>
+          <t>2026_03_CIN_PIT:spread</t>
         </is>
       </c>
     </row>
@@ -1883,21 +1853,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TEN@NYG</t>
+          <t>CIN@PIT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NYG -2.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-2.5</v>
+        <v>42.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1915,13 +1885,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.1</v>
+        <v>49.4</v>
       </c>
       <c r="J22" t="n">
-        <v>4.6</v>
+        <v>6.9</v>
       </c>
       <c r="K22" t="n">
-        <v>63.8</v>
+        <v>74.3</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1930,7 +1900,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>TEN 7-12 NYG</t>
+          <t>CIN 27-30 PIT</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -1940,7 +1910,7 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026_03_TEN_NYG:spread</t>
+          <t>2026_03_CIN_PIT:total</t>
         </is>
       </c>
     </row>
@@ -1950,25 +1920,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TEN@NYG</t>
+          <t>HOU@IND</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Over 37.5</t>
+          <t>IND +7.5</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>37.5</v>
+        <v>7.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1978,46 +1948,44 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>83.09999999999999</v>
-      </c>
+          <t>티저 다리(소급)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>TEN 7-12 NYG</t>
+          <t>HOU 17-19 IND</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>-1</v>
+        <v>0.353</v>
       </c>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>소급 · 원 라인 +1.5 · 총점 42.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026_03_TEN_NYG:total</t>
+          <t>2026_03_HOU_IND:spread:TB</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ARI@NYG</t>
+          <t>KC@MIA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2027,11 +1995,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NYG +2.5</t>
+          <t>MIA +10</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2045,54 +2013,62 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J24" t="n">
-        <v>6</v>
-      </c>
-      <c r="K24" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>각도 관찰 A1(소급)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>KC 24-10 MIA</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>-1</v>
+      </c>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>소급 · 원정 KC -10 페이버릿 · DK 마감</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026_04_ARI_NYG:spread</t>
+          <t>2026_03_KC_MIA:spread:A1B</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ARI@NYG</t>
+          <t>KC@MIA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NYG +8.5</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>8.5</v>
+        <v>45.5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2102,44 +2078,46 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>51</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>69.90000000000001</v>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>ARI 24-36 NYG</t>
+          <t>KC 24-10 MIA</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0.833</v>
+        <v>-1</v>
       </c>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>원 라인 +2.5 · 총점 44.5 · 가격 미기록(−120 티저 환산 손익분기 73.9%)</t>
-        </is>
-      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026_04_ARI_NYG:spread:T</t>
+          <t>2026_03_KC_MIA:total</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ARI@NYG</t>
+          <t>LA@DEN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2149,11 +2127,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ARI -2.5</t>
+          <t>LA +1.5</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-2.5</v>
+        <v>-1.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2167,17 +2145,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>-3.2</v>
       </c>
       <c r="J26" t="n">
-        <v>4.4</v>
+        <v>-4.7</v>
       </c>
       <c r="K26" t="n">
-        <v>63.2</v>
+        <v>64.3</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2186,49 +2164,45 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>ARI 24-36 NYG</t>
+          <t>LA 26-30 DEN</t>
         </is>
       </c>
       <c r="N26" t="n">
         <v>-1</v>
       </c>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026_04_ARI_NYG:spread:D</t>
+          <t>2026_03_LA_DEN:spread</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ARI@NYG</t>
+          <t>LA@DEN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>LA +7.5</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>44.5</v>
+        <v>7.5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2238,36 +2212,44 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>티저 다리(소급)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>LA 26-30 DEN</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0.353</v>
+      </c>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>소급 · 원 라인 +1.5 · 총점 44.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026_04_ARI_NYG:total</t>
+          <t>2026_03_LA_DEN:spread:TB</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ARI@NYG</t>
+          <t>LA@DEN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2277,11 +2259,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>44.5</v>
+        <v>43.5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2295,119 +2277,129 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>54.8</v>
+        <v>47</v>
       </c>
       <c r="J28" t="n">
-        <v>10.3</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>83.59999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>ARI 24-36 NYG</t>
+          <t>LA 26-30 DEN</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026_04_ARI_NYG:total:D</t>
+          <t>2026_03_LA_DEN:total</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ATL@NO</t>
+          <t>LA@DEN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ATL +7.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>7.5</v>
+        <v>44.5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-120</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>suggested</t>
+          <t>placed</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
+          <t>실베팅</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>LA 26-30 DEN</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>원 라인 +1.5 · 총점 47.5 · 가격 미기록(−120 티저 환산 손익분기 73.9%)</t>
+          <t>Paul 실베팅 9/27(claude.ai 대화 — 언더 44.5) · 9/28 사후 기록 · 라이브 진입이면 라인·배당 정정 필요</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026_04_ATL_NO:spread:T</t>
+          <t>2026_03_LA_DEN:total:P</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ATL@NO</t>
+          <t>LV@NO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>NO -3.5</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>47.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2421,67 +2413,85 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>38.9</v>
+        <v>5.6</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.6</v>
+        <v>2.1</v>
       </c>
       <c r="K30" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+        <v>56.4</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>LV 35-27 NO</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>-1</v>
+      </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026_04_ATL_NO:total</t>
+          <t>2026_03_LV_NO:spread</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DAL@HOU</t>
+          <t>LV@NO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>HOU ML</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>Under 43.5</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>43.5</v>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-148</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>placed</t>
+          <t>suggested</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>실베팅</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="K31" t="n">
+        <v>82.8</v>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>L</t>
@@ -2489,35 +2499,27 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>DAL 34-30 HOU</t>
+          <t>LV 35-27 NO</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>2026-10-04 09:27</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Paul 실베팅 — A2 패턴(드라이브 우위 언더독 DAL의 반대) ML. 배당은 수집값(DK −148) 그대로(Paul). 금액 미확인 — 권장 0.5u 로 임시</t>
-        </is>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026_04_DAL_HOU:ml:P</t>
+          <t>2026_03_LV_NO:total</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DAL@HOU</t>
+          <t>MIN@TB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2527,15 +2529,15 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>HOU -3</t>
+          <t>MIN +7.5</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-3</v>
+        <v>7.5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2545,50 +2547,58 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>티저 다리(소급)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>MIN 23-16 TB</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0.353</v>
+      </c>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>소급 · 원 라인 +1.5 · 총점 42.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026_04_DAL_HOU:spread</t>
+          <t>2026_03_MIN_TB:spread:TB</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DAL@HOU</t>
+          <t>MIN@TB</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>HOU -3</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-3</v>
+        <v>42.5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2602,50 +2612,46 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.2</v>
+        <v>31</v>
       </c>
       <c r="J33" t="n">
-        <v>4.2</v>
+        <v>-11.5</v>
       </c>
       <c r="K33" t="n">
-        <v>62.7</v>
+        <v>86.2</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>DAL 34-30 HOU</t>
+          <t>MIN 23-16 TB</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026_04_DAL_HOU:spread:D</t>
+          <t>2026_03_MIN_TB:total</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DAL@HOU</t>
+          <t>NYJ@DET</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2655,11 +2661,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>HOU -3</t>
+          <t>DET -7</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2673,44 +2679,46 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K34" t="n">
+        <v>67.2</v>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>DAL 34-30 HOU</t>
+          <t>NYJ 24-31 DET</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>언더독 DAL 드라이브 득점 차 우위 +0.91 → 반대 HOU · 10-04 09:01 PT 판</t>
-        </is>
-      </c>
+      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026_04_DAL_HOU:spread:A2</t>
+          <t>2026_03_NYJ_DET:spread</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DAL@HOU</t>
+          <t>NYJ@DET</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2720,11 +2728,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2738,50 +2746,60 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>55.8</v>
+        <v>54.1</v>
       </c>
       <c r="J35" t="n">
-        <v>7.3</v>
+        <v>4.6</v>
       </c>
       <c r="K35" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>NYJ 24-31 DET</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026_04_DAL_HOU:total</t>
+          <t>2026_03_NYJ_DET:total</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DAL@HOU</t>
+          <t>PHI@CHI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>PHI -3.5</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>48.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2790,69 +2808,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>suggested</t>
+          <t>placed</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>53</v>
-      </c>
-      <c r="J36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K36" t="n">
-        <v>66.59999999999999</v>
-      </c>
+          <t>관심(설명문)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>DAL 34-30 HOU</t>
+          <t>PHI 7-27 CHI</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="O36" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:15</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>Paul 실베팅 9/28 — 설명문 판단(소액 관심) 동일</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026_04_DAL_HOU:total:D</t>
+          <t>2026_03_PHI_CHI:spread</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DEN@SF</t>
+          <t>PHI@CHI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DEN +3</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>41.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2866,12 +2882,18 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+          <t>참고 ※</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K37" t="n">
+        <v>67</v>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>L</t>
@@ -2879,45 +2901,41 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>DEN 14-24 SF</t>
+          <t>PHI 7-27 CHI</t>
         </is>
       </c>
       <c r="N37" t="n">
         <v>-1</v>
       </c>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026_04_DEN_SF:spread:D</t>
+          <t>2026_03_PHI_CHI:total</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DEN@SF</t>
+          <t>SEA@WAS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>SEA -8.5</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>48.5</v>
+        <v>8.5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2931,54 +2949,64 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>55.6</v>
+        <v>-11.7</v>
       </c>
       <c r="J38" t="n">
-        <v>7.1</v>
+        <v>-3.2</v>
       </c>
       <c r="K38" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+        <v>59.6</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>SEA 31-33 WAS</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>-1</v>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026_04_DEN_SF:total</t>
+          <t>2026_03_SEA_WAS:spread</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DEN@SF</t>
+          <t>SEA@WAS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>SEA -2.5</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>48.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2988,18 +3016,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="J39" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K39" t="n">
-        <v>71.40000000000001</v>
-      </c>
+          <t>티저 다리(소급)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>L</t>
@@ -3007,7 +3029,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>DEN 14-24 SF</t>
+          <t>SEA 31-33 WAS</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -3016,22 +3038,22 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>소급 · 원 라인 -8.5 · 총점 40.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026_04_DEN_SF:total:D</t>
+          <t>2026_03_SEA_WAS:spread:TB</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DET@CAR</t>
+          <t>SEA@WAS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3041,11 +3063,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DET -3.5</t>
+          <t>WAS +8.5</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-3.5</v>
+        <v>8.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3059,7 +3081,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>각도 관찰 A1(소급)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -3067,36 +3089,36 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>DET 26-32 CAR</t>
+          <t>SEA 31-33 WAS</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>소급 · 원정 SEA -8.5 페이버릿 · DK 마감</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026_04_DET_CAR:spread:D</t>
+          <t>2026_03_SEA_WAS:spread:A1B</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DET@CAR</t>
+          <t>TEN@NYG</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3106,11 +3128,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CAR +4.5</t>
+          <t>NYG -2.5</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3124,54 +3146,64 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>-2.3</v>
+        <v>7.1</v>
       </c>
       <c r="J41" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="K41" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+        <v>63.8</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>TEN 7-12 NYG</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026_04_DET_CAR:spread</t>
+          <t>2026_03_TEN_NYG:spread</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DET@CAR</t>
+          <t>TEN@NYG</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>TEN +8.5</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>51.5</v>
+        <v>8.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3181,7 +3213,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>티저 다리(소급)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -3194,31 +3226,31 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>DET 26-32 CAR</t>
+          <t>TEN 7-12 NYG</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0.909</v>
+        <v>0.353</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>소급 · 원 라인 +2.5 · 총점 37.5 · DK 마감 · 2팀 −120 티저 다리 환산 −283</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026_04_DET_CAR:total:D</t>
+          <t>2026_03_TEN_NYG:spread:TB</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DET@CAR</t>
+          <t>TEN@NYG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3228,11 +3260,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Over 37.5</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>52.5</v>
+        <v>37.5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3246,26 +3278,36 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>57.5</v>
+        <v>47.6</v>
       </c>
       <c r="J43" t="n">
-        <v>5</v>
+        <v>10.1</v>
       </c>
       <c r="K43" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+        <v>83.09999999999999</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>TEN 7-12 NYG</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>-1</v>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026_04_DET_CAR:total</t>
+          <t>2026_03_TEN_NYG:total</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3317,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GB@TB</t>
+          <t>ARI@NYG</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3285,11 +3327,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>GB -3</t>
+          <t>NYG +2.5</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3303,17 +3345,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>-5.8</v>
+        <v>3.5</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.8</v>
+        <v>6</v>
       </c>
       <c r="K44" t="n">
-        <v>58.6</v>
+        <v>67.7</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
@@ -3322,7 +3364,7 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:spread</t>
+          <t>2026_04_ARI_NYG:spread</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3374,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GB@TB</t>
+          <t>ARI@NYG</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3342,15 +3384,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GB -3</t>
+          <t>NYG +8.5</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-3</v>
+        <v>8.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3360,40 +3402,34 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="J45" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="K45" t="n">
-        <v>57.6</v>
-      </c>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>GB 17-14 TB</t>
+          <t>ARI 24-36 NYG</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>0.353</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>원 라인 +2.5 · 총점 44.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%) · 10/5 유닛 정정</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:spread:D</t>
+          <t>2026_04_ARI_NYG:spread:T</t>
         </is>
       </c>
     </row>
@@ -3403,21 +3439,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GB@TB</t>
+          <t>ARI@NYG</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>ARI -2.5</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>38.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3431,26 +3467,40 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>42.6</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K46" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+        <v>63.2</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>ARI 24-36 NYG</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>-1</v>
+      </c>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:total</t>
+          <t>2026_04_ARI_NYG:spread:D</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3510,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GB@TB</t>
+          <t>ARI@NYG</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3470,11 +3520,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>38.5</v>
+        <v>44.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3488,40 +3538,26 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>43</v>
+        <v>50.7</v>
       </c>
       <c r="J47" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="K47" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>GB 17-14 TB</t>
-        </is>
-      </c>
-      <c r="N47" t="n">
-        <v>0.909</v>
-      </c>
+        <v>72.40000000000001</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026_04_GB_TB:total:D</t>
+          <t>2026_04_ARI_NYG:total</t>
         </is>
       </c>
     </row>
@@ -3531,21 +3567,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IND@WAS</t>
+          <t>ARI@NYG</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>IND -4.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4.5</v>
+        <v>44.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3559,26 +3595,40 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>-10.7</v>
+        <v>54.8</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.2</v>
+        <v>10.3</v>
       </c>
       <c r="K48" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+        <v>83.59999999999999</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>ARI 24-36 NYG</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>-1</v>
+      </c>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026_04_IND_WAS:spread</t>
+          <t>2026_04_ARI_NYG:total:D</t>
         </is>
       </c>
     </row>
@@ -3588,25 +3638,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IND@WAS</t>
+          <t>ATL@NO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>ATL +7.5</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>46.5</v>
+        <v>7.5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3616,36 +3666,24 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="J49" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>IND 30-13 WAS</t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>-1</v>
-      </c>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>원 라인 +1.5 · 총점 47.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%) · 10/5 유닛 정정</t>
+        </is>
+      </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026_04_IND_WAS:total</t>
+          <t>2026_04_ATL_NO:spread:T</t>
         </is>
       </c>
     </row>
@@ -3655,64 +3693,52 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JAX@CIN</t>
+          <t>ATL@NO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CIN ML</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>NO -1.5</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-148</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>placed</t>
+          <t>suggested</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>실베팅</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>JAX 22-17 CIN</t>
-        </is>
-      </c>
-      <c r="N50" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>2026-10-04 09:27</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Paul 실베팅 — A2 패턴(드라이브 우위 언더독 JAX의 반대) ML. 배당은 수집값(DK −148) 그대로(Paul). 금액 미확인 — 권장 0.5u 로 임시</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:ml:P</t>
+          <t>2026_04_ATL_NO:spread:D</t>
         </is>
       </c>
     </row>
@@ -3722,21 +3748,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JAX@CIN</t>
+          <t>ATL@NO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-2.5</v>
+        <v>47.5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3754,13 +3780,13 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>-9.800000000000001</v>
+        <v>38.9</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.3</v>
+        <v>-8.6</v>
       </c>
       <c r="K51" t="n">
-        <v>82.8</v>
+        <v>79.3</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
@@ -3769,7 +3795,7 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:spread</t>
+          <t>2026_04_ATL_NO:total</t>
         </is>
       </c>
     </row>
@@ -3779,21 +3805,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JAX@CIN</t>
+          <t>ATL@NO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2.5</v>
+        <v>47.5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3811,27 +3837,17 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>-9.5</v>
+        <v>38.9</v>
       </c>
       <c r="J52" t="n">
-        <v>-12</v>
+        <v>-8.6</v>
       </c>
       <c r="K52" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>JAX 22-17 CIN</t>
-        </is>
-      </c>
-      <c r="N52" t="n">
-        <v>0.909</v>
-      </c>
+        <v>79.3</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -3840,7 +3856,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:spread:D</t>
+          <t>2026_04_ATL_NO:total:D</t>
         </is>
       </c>
     </row>
@@ -3850,35 +3866,33 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JAX@CIN</t>
+          <t>DAL@HOU</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CIN -2.5</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>-2.5</v>
-      </c>
+          <t>HOU ML</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-148</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>suggested</t>
+          <t>placed</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+          <t>실베팅</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -3891,21 +3905,25 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>JAX 22-17 CIN</t>
+          <t>DAL 34-30 HOU</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O53" t="inlineStr"/>
+        <v>-0.5</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-10-04 09:27</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>언더독 JAX 드라이브 득점 차 우위 +0.98 → 반대 CIN · 10-04 09:01 PT 판</t>
+          <t>Paul 실베팅 — A2 패턴(드라이브 우위 언더독 DAL의 반대) ML. 배당은 수집값(DK −148) 그대로(Paul). 금액 미확인 — 권장 0.5u 로 임시</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:spread:A2</t>
+          <t>2026_04_DAL_HOU:ml:P</t>
         </is>
       </c>
     </row>
@@ -3915,21 +3933,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JAX@CIN</t>
+          <t>DAL@HOU</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>HOU -3</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>51.5</v>
+        <v>-3</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3943,36 +3961,26 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>48</v>
+        <v>7.1</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.5</v>
+        <v>4.1</v>
       </c>
       <c r="K54" t="n">
-        <v>63</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>JAX 22-17 CIN</t>
-        </is>
-      </c>
-      <c r="N54" t="n">
-        <v>0.909</v>
-      </c>
+        <v>62.4</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:total</t>
+          <t>2026_04_DAL_HOU:spread</t>
         </is>
       </c>
     </row>
@@ -3982,21 +3990,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JAX@CIN</t>
+          <t>DAL@HOU</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>HOU -3</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>51.5</v>
+        <v>-3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4014,10 +4022,10 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>48.1</v>
+        <v>7.2</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.4</v>
+        <v>4.2</v>
       </c>
       <c r="K55" t="n">
         <v>62.7</v>
@@ -4029,7 +4037,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>JAX 22-17 CIN</t>
+          <t>DAL 34-30 HOU</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -4043,7 +4051,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026_04_JAX_CIN:total:D</t>
+          <t>2026_04_DAL_HOU:spread:D</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4061,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>KC@LV</t>
+          <t>DAL@HOU</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4063,11 +4071,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KC -4.5</t>
+          <t>HOU -3</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4.5</v>
+        <v>-3</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4081,26 +4089,34 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>-9.6</v>
-      </c>
-      <c r="J56" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>DAL 34-30 HOU</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>-1</v>
+      </c>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>언더독 DAL 드라이브 득점 차 우위 +0.91 → 반대 HOU · 10-04 09:01 PT 판</t>
+        </is>
+      </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:spread</t>
+          <t>2026_04_DAL_HOU:spread:A2</t>
         </is>
       </c>
     </row>
@@ -4110,21 +4126,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KC@LV</t>
+          <t>DAL@HOU</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KC -4.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>-4.5</v>
+        <v>48.5</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4138,40 +4154,26 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>-10</v>
+        <v>55.8</v>
       </c>
       <c r="J57" t="n">
-        <v>-5.5</v>
+        <v>7.3</v>
       </c>
       <c r="K57" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>KC 30-27 LV</t>
-        </is>
-      </c>
-      <c r="N57" t="n">
-        <v>-1</v>
-      </c>
+        <v>75.7</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:spread:D</t>
+          <t>2026_04_DAL_HOU:total</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4183,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KC@LV</t>
+          <t>DAL@HOU</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4191,11 +4193,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4209,26 +4211,40 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>41.2</v>
+        <v>53</v>
       </c>
       <c r="J58" t="n">
-        <v>-6.3</v>
+        <v>4.5</v>
       </c>
       <c r="K58" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+        <v>66.59999999999999</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>DAL 34-30 HOU</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:total</t>
+          <t>2026_04_DAL_HOU:total:D</t>
         </is>
       </c>
     </row>
@@ -4238,21 +4254,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KC@LV</t>
+          <t>DEN@SF</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>DEN +3</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>47.5</v>
+        <v>3</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4269,15 +4285,9 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="J59" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="K59" t="n">
-        <v>79.3</v>
-      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>L</t>
@@ -4285,7 +4295,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>KC 30-27 LV</t>
+          <t>DEN 14-24 SF</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -4299,7 +4309,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026_04_KC_LV:total:D</t>
+          <t>2026_04_DEN_SF:spread:D</t>
         </is>
       </c>
     </row>
@@ -4309,21 +4319,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LA@PHI</t>
+          <t>DEN@SF</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LA -3.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>-3.5</v>
+        <v>48.5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4337,34 +4347,26 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>LA 24-20 PHI</t>
-        </is>
-      </c>
-      <c r="N60" t="n">
-        <v>0.909</v>
-      </c>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="J60" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026_04_LA_PHI:spread:D</t>
+          <t>2026_04_DEN_SF:total</t>
         </is>
       </c>
     </row>
@@ -4374,21 +4376,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LA@PHI</t>
+          <t>DEN@SF</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LA -3.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3.5</v>
+        <v>48.5</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4402,26 +4404,40 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>-7.5</v>
+        <v>54.4</v>
       </c>
       <c r="J61" t="n">
-        <v>-4</v>
+        <v>5.9</v>
       </c>
       <c r="K61" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+        <v>71.40000000000001</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>DEN 14-24 SF</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>-1</v>
+      </c>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026_04_LA_PHI:spread</t>
+          <t>2026_04_DEN_SF:total:D</t>
         </is>
       </c>
     </row>
@@ -4431,21 +4447,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LA@PHI</t>
+          <t>DET@CAR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>DET -3.5</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>42.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -4459,36 +4475,34 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I62" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="J62" t="n">
-        <v>4</v>
-      </c>
-      <c r="K62" t="n">
-        <v>64.90000000000001</v>
-      </c>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>LA 24-20 PHI</t>
+          <t>DET 26-32 CAR</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026_04_LA_PHI:total</t>
+          <t>2026_04_DET_CAR:spread:D</t>
         </is>
       </c>
     </row>
@@ -4498,21 +4512,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LA@PHI</t>
+          <t>DET@CAR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>CAR +4.5</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>42.5</v>
+        <v>4.5</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -4526,40 +4540,26 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>46.6</v>
+        <v>-2.3</v>
       </c>
       <c r="J63" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="K63" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>LA 24-20 PHI</t>
-        </is>
-      </c>
-      <c r="N63" t="n">
-        <v>-1</v>
-      </c>
+        <v>56.7</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026_04_LA_PHI:total:D</t>
+          <t>2026_04_DET_CAR:spread</t>
         </is>
       </c>
     </row>
@@ -4569,21 +4569,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LAC@SEA</t>
+          <t>DET@CAR</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LAC +7</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>-7</v>
+        <v>51.5</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -4597,26 +4597,34 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I64" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J64" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="K64" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>DET 26-32 CAR</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026_04_LAC_SEA:spread</t>
+          <t>2026_04_DET_CAR:total:D</t>
         </is>
       </c>
     </row>
@@ -4626,21 +4634,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LAC@SEA</t>
+          <t>DET@CAR</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SEA -7</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>-7</v>
+        <v>52.5</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4654,40 +4662,26 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.9</v>
+        <v>57.5</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.1</v>
+        <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>LAC 23-30 SEA</t>
-        </is>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
+        <v>68.2</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026_04_LAC_SEA:spread:D</t>
+          <t>2026_04_DET_CAR:total</t>
         </is>
       </c>
     </row>
@@ -4697,21 +4691,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LAC@SEA</t>
+          <t>GB@TB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>GB -3</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>42.5</v>
+        <v>3</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4725,17 +4719,17 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>30.5</v>
+        <v>-5.8</v>
       </c>
       <c r="J66" t="n">
-        <v>-12</v>
+        <v>-2.8</v>
       </c>
       <c r="K66" t="n">
-        <v>87.3</v>
+        <v>58.6</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
@@ -4744,7 +4738,7 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026_04_LAC_SEA:total</t>
+          <t>2026_04_GB_TB:spread</t>
         </is>
       </c>
     </row>
@@ -4754,21 +4748,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LAC@SEA</t>
+          <t>GB@TB</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>GB -3</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>42.5</v>
+        <v>-3</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4786,26 +4780,26 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>31.5</v>
+        <v>-5.5</v>
       </c>
       <c r="J67" t="n">
-        <v>-11</v>
+        <v>-2.5</v>
       </c>
       <c r="K67" t="n">
-        <v>85.3</v>
+        <v>57.6</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>LAC 23-30 SEA</t>
+          <t>GB 17-14 TB</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -4815,7 +4809,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2026_04_LAC_SEA:total:D</t>
+          <t>2026_04_GB_TB:spread:D</t>
         </is>
       </c>
     </row>
@@ -4825,21 +4819,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MIA@MIN</t>
+          <t>GB@TB</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MIA +10</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>10</v>
+        <v>38.5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4853,34 +4847,26 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>MIA 10-15 MIN</t>
-        </is>
-      </c>
-      <c r="N68" t="n">
-        <v>0.909</v>
-      </c>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="J68" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2026_04_MIA_MIN:spread:D</t>
+          <t>2026_04_GB_TB:total</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4876,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MIA@MIN</t>
+          <t>GB@TB</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4921,9 +4907,15 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>43</v>
+      </c>
+      <c r="J69" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K69" t="n">
+        <v>66.5</v>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>W</t>
@@ -4931,7 +4923,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>MIA 10-15 MIN</t>
+          <t>GB 17-14 TB</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -4945,7 +4937,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2026_04_MIA_MIN:total:D</t>
+          <t>2026_04_GB_TB:total:D</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4947,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>IND@WAS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4965,11 +4957,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NE +7</t>
+          <t>IND -4.5</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>-7</v>
+        <v>4.5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4987,13 +4979,13 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>-10.7</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.6</v>
+        <v>-6.2</v>
       </c>
       <c r="K70" t="n">
-        <v>66.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
@@ -5002,7 +4994,7 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:spread</t>
+          <t>2026_04_IND_WAS:spread</t>
         </is>
       </c>
     </row>
@@ -5012,21 +5004,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>IND@WAS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BUF -7</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>-7</v>
+        <v>46.5</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5040,17 +5032,17 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>51.6</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.4</v>
+        <v>5.1</v>
       </c>
       <c r="K71" t="n">
-        <v>63.2</v>
+        <v>68.5</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -5059,21 +5051,17 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>NE 29-26 BUF</t>
+          <t>IND 30-13 WAS</t>
         </is>
       </c>
       <c r="N71" t="n">
         <v>-1</v>
       </c>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:spread:D</t>
+          <t>2026_04_IND_WAS:total</t>
         </is>
       </c>
     </row>
@@ -5083,54 +5071,64 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>49.5</v>
-      </c>
+          <t>CIN ML</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-148</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>suggested</t>
+          <t>placed</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I72" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="J72" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="K72" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+          <t>실베팅</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>JAX 22-17 CIN</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2026-10-04 09:27</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Paul 실베팅 — A2 패턴(드라이브 우위 언더독 JAX의 반대) ML. 배당은 수집값(DK −148) 그대로(Paul). 금액 미확인 — 권장 0.5u 로 임시</t>
+        </is>
+      </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:total</t>
+          <t>2026_04_JAX_CIN:ml:P</t>
         </is>
       </c>
     </row>
@@ -5140,21 +5138,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>49.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5168,34 +5166,26 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>바람 언더(관찰)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>NE 29-26 BUF</t>
-        </is>
-      </c>
-      <c r="N73" t="n">
-        <v>-1</v>
-      </c>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="K73" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>예보 16mph(NWS 지속·10-04 08:30 PT) · 총점 42+ · 실측 wind 결측</t>
-        </is>
-      </c>
+      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:total:wind</t>
+          <t>2026_04_JAX_CIN:spread</t>
         </is>
       </c>
     </row>
@@ -5205,21 +5195,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NE@BUF</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>49.5</v>
+        <v>2.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5237,13 +5227,13 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>55.3</v>
+        <v>-9.5</v>
       </c>
       <c r="J74" t="n">
-        <v>5.8</v>
+        <v>-12</v>
       </c>
       <c r="K74" t="n">
-        <v>70.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -5252,7 +5242,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>NE 29-26 BUF</t>
+          <t>JAX 22-17 CIN</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -5266,7 +5256,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2026_04_NE_BUF:total:D</t>
+          <t>2026_04_JAX_CIN:spread:D</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5266,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NYJ@CHI</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5286,11 +5276,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CHI -3.5</t>
+          <t>CIN -2.5</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>-3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -5304,26 +5294,34 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J75" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K75" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>JAX 22-17 CIN</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>-1</v>
+      </c>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>언더독 JAX 드라이브 득점 차 우위 +0.98 → 반대 CIN · 10-04 09:01 PT 판</t>
+        </is>
+      </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:spread</t>
+          <t>2026_04_JAX_CIN:spread:A2</t>
         </is>
       </c>
     </row>
@@ -5333,21 +5331,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NYJ@CHI</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NYJ +3.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3.5</v>
+        <v>51.5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -5361,40 +5359,36 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>10.1</v>
+        <v>48</v>
       </c>
       <c r="J76" t="n">
-        <v>6.6</v>
+        <v>-3.5</v>
       </c>
       <c r="K76" t="n">
-        <v>69.5</v>
+        <v>63</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>NYJ 12-23 CHI</t>
+          <t>JAX 22-17 CIN</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:spread:D</t>
+          <t>2026_04_JAX_CIN:total</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5398,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NYJ@CHI</t>
+          <t>JAX@CIN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5414,11 +5408,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>43.5</v>
+        <v>51.5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -5432,17 +5426,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>46.8</v>
+        <v>48.1</v>
       </c>
       <c r="J77" t="n">
-        <v>3.3</v>
+        <v>-3.4</v>
       </c>
       <c r="K77" t="n">
-        <v>62.4</v>
+        <v>62.7</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -5451,17 +5445,21 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>NYJ 12-23 CHI</t>
+          <t>JAX 22-17 CIN</t>
         </is>
       </c>
       <c r="N77" t="n">
         <v>-1</v>
       </c>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:total</t>
+          <t>2026_04_JAX_CIN:total:D</t>
         </is>
       </c>
     </row>
@@ -5471,21 +5469,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NYJ@CHI</t>
+          <t>KC@LV</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Under 43.5</t>
+          <t>KC -4.5</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>43.5</v>
+        <v>4.5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -5499,40 +5497,26 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>46.9</v>
+        <v>-9.6</v>
       </c>
       <c r="J78" t="n">
-        <v>3.4</v>
+        <v>-5.1</v>
       </c>
       <c r="K78" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>NYJ 12-23 CHI</t>
-        </is>
-      </c>
-      <c r="N78" t="n">
-        <v>0.909</v>
-      </c>
+        <v>65.09999999999999</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2026_04_NYJ_CHI:total:D</t>
+          <t>2026_04_KC_LV:spread</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5526,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>KC@LV</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5552,15 +5536,15 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CLE +8.5</t>
+          <t>KC -4.5</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>8.5</v>
+        <v>-4.5</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-270</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5570,34 +5554,40 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J79" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="K79" t="n">
+        <v>66.3</v>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>PIT 24-27 CLE</t>
+          <t>KC 30-27 LV</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0.37</v>
+        <v>-1</v>
       </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>원 라인 +2.5 · 총점 38.5 · 가격 Polymarket No 73c(표시가 — 실베팅 아님)</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:spread:T</t>
+          <t>2026_04_KC_LV:spread:D</t>
         </is>
       </c>
     </row>
@@ -5607,21 +5597,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>KC@LV</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>PIT -2.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>-2.5</v>
+        <v>47.5</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -5635,40 +5625,26 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>-0.7</v>
+        <v>41.2</v>
       </c>
       <c r="J80" t="n">
-        <v>2.3</v>
+        <v>-6.3</v>
       </c>
       <c r="K80" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>PIT 24-27 CLE</t>
-        </is>
-      </c>
-      <c r="N80" t="n">
-        <v>-1</v>
-      </c>
+        <v>72.5</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:spread:D</t>
+          <t>2026_04_KC_LV:total</t>
         </is>
       </c>
     </row>
@@ -5678,40 +5654,46 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>KC@LV</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>PIT -2.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>-2.5</v>
+        <v>47.5</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-108</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>placed</t>
+          <t>suggested</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>실베팅</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="K81" t="n">
+        <v>79.3</v>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>L</t>
@@ -5719,25 +5701,21 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>PIT 24-27 CLE</t>
+          <t>KC 30-27 LV</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>2026-10-01 11:36</t>
-        </is>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Paul 자체 판단 0.5u — 발행 판단은 패스(굳이 하나만 PIT -2.5). 체결 Polymarket 「PIT to win by over 2.5 → Yes」 52c(≈ -108, 손익분기 52.0%). Ramsey(PIT CB) Q 상태에서 베팅</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:spread:P</t>
+          <t>2026_04_KC_LV:total:D</t>
         </is>
       </c>
     </row>
@@ -5747,21 +5725,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>LA@PHI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>LA -3.5</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>38.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -5775,36 +5753,34 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="J82" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="K82" t="n">
-        <v>65.8</v>
-      </c>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>PIT 24-27 CLE</t>
+          <t>LA 24-20 PHI</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:total</t>
+          <t>2026_04_LA_PHI:spread:D</t>
         </is>
       </c>
     </row>
@@ -5814,21 +5790,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PIT@CLE</t>
+          <t>LA@PHI</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>LA -3.5</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>38.5</v>
+        <v>3.5</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -5842,40 +5818,26 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>34.2</v>
+        <v>-7.5</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.3</v>
+        <v>-4</v>
       </c>
       <c r="K83" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>PIT 24-27 CLE</t>
-        </is>
-      </c>
-      <c r="N83" t="n">
-        <v>0.909</v>
-      </c>
+        <v>62.1</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>2026_04_PIT_CLE:total:D</t>
+          <t>2026_04_LA_PHI:spread</t>
         </is>
       </c>
     </row>
@@ -5885,21 +5847,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TEN@BAL</t>
+          <t>LA@PHI</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>BAL -11.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>-11.5</v>
+        <v>42.5</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -5913,26 +5875,36 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>15.7</v>
+        <v>46.5</v>
       </c>
       <c r="J84" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K84" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+        <v>64.90000000000001</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>LA 24-20 PHI</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>2026_04_TEN_BAL:spread</t>
+          <t>2026_04_LA_PHI:total</t>
         </is>
       </c>
     </row>
@@ -5942,21 +5914,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TEN@BAL</t>
+          <t>LA@PHI</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>TEN +11.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>11.5</v>
+        <v>42.5</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -5974,26 +5946,26 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>13.9</v>
+        <v>46.6</v>
       </c>
       <c r="J85" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="K85" t="n">
-        <v>57.2</v>
+        <v>65.2</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>TEN 18-24 BAL</t>
+          <t>LA 24-20 PHI</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
@@ -6003,7 +5975,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>2026_04_TEN_BAL:spread:D</t>
+          <t>2026_04_LA_PHI:total:D</t>
         </is>
       </c>
     </row>
@@ -6013,21 +5985,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TEN@BAL</t>
+          <t>LAC@SEA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>LAC +7</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>42.5</v>
+        <v>-7</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6041,17 +6013,17 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>48</v>
+        <v>4.3</v>
       </c>
       <c r="J86" t="n">
-        <v>5.5</v>
+        <v>-2.7</v>
       </c>
       <c r="K86" t="n">
-        <v>69.90000000000001</v>
+        <v>58.1</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
@@ -6060,7 +6032,7 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>2026_04_TEN_BAL:total</t>
+          <t>2026_04_LAC_SEA:spread</t>
         </is>
       </c>
     </row>
@@ -6070,21 +6042,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TEN@BAL</t>
+          <t>LAC@SEA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>SEA -7</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>42.5</v>
+        <v>-7</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6102,26 +6074,26 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>48</v>
+        <v>4.9</v>
       </c>
       <c r="J87" t="n">
-        <v>5.5</v>
+        <v>-2.1</v>
       </c>
       <c r="K87" t="n">
-        <v>69.90000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>P</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>TEN 18-24 BAL</t>
+          <t>LAC 23-30 SEA</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0.909</v>
+        <v>0</v>
       </c>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
@@ -6130,6 +6102,1450 @@
         </is>
       </c>
       <c r="Q87" t="inlineStr">
+        <is>
+          <t>2026_04_LAC_SEA:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>LAC@SEA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Under 42.5</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J88" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K88" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>2026_04_LAC_SEA:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>LAC@SEA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Under 42.5</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J89" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K89" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>LAC 23-30 SEA</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>2026_04_LAC_SEA:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>4</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MIA@MIN</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>MIA +10</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>10</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>MIA 10-15 MIN</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>2026_04_MIA_MIN:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>4</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>MIA@MIN</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Under 38.5</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>MIA 10-15 MIN</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>2026_04_MIA_MIN:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>4</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NE@BUF</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NE +7</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J92" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="K92" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>2026_04_NE_BUF:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NE@BUF</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>BUF -7</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J93" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="K93" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>NE 29-26 BUF</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>2026_04_NE_BUF:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NE@BUF</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Over 49.5</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="J94" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K94" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>2026_04_NE_BUF:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>4</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>NE@BUF</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Under 49.5</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>바람 언더(관찰)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>NE 29-26 BUF</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>예보 16mph(NWS 지속·10-04 08:30 PT) · 총점 42+ · 실측 wind 결측</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>2026_04_NE_BUF:total:wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>4</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NE@BUF</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Over 49.5</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K96" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>NE 29-26 BUF</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>2026_04_NE_BUF:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>4</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NYJ@CHI</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>CHI -3.5</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J97" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K97" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2026_04_NYJ_CHI:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>4</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>NYJ@CHI</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NYJ +3.5</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J98" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K98" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>NYJ 12-23 CHI</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>2026_04_NYJ_CHI:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>4</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NYJ@CHI</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Over 43.5</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="J99" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K99" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>NYJ 12-23 CHI</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>2026_04_NYJ_CHI:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>4</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>NYJ@CHI</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Under 43.5</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="J100" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K100" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>NYJ 12-23 CHI</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>2026_04_NYJ_CHI:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>4</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PIT@CLE</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CLE +8.5</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-270</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 38.5 · 가격 Polymarket No 73c(표시가 — 실베팅 아님)</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2026_04_PIT_CLE:spread:T</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>4</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PIT@CLE</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>PIT -2.5</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="J102" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K102" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>2026_04_PIT_CLE:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>4</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PIT@CLE</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>PIT -2.5</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-108</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>placed</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>실베팅</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:36</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Paul 자체 판단 0.5u — 발행 판단은 패스(굳이 하나만 PIT -2.5). 체결 Polymarket 「PIT to win by over 2.5 → Yes」 52c(≈ -108, 손익분기 52.0%). Ramsey(PIT CB) Q 상태에서 베팅</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>2026_04_PIT_CLE:spread:P</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>4</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PIT@CLE</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Under 38.5</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="J104" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="K104" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>2026_04_PIT_CLE:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>4</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PIT@CLE</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Over 38.5</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="J105" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="K105" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>PIT 24-27 CLE</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>2026_04_PIT_CLE:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>4</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BAL -11.5</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="J106" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K106" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>2026_04_TEN_BAL:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>4</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>TEN +11.5</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J107" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K107" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>TEN 18-24 BAL</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>2026_04_TEN_BAL:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>4</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Over 42.5</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>48</v>
+      </c>
+      <c r="J108" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K108" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>2026_04_TEN_BAL:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>TEN@BAL</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Under 42.5</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>48</v>
+      </c>
+      <c r="J109" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K109" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>TEN 18-24 BAL</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
         <is>
           <t>2026_04_TEN_BAL:total:D</t>
         </is>
@@ -6146,7 +7562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6331,7 +7747,7 @@
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2</v>
+        <v>0.72</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -6372,91 +7788,94 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>각도 관찰 A1(원정 큰 페이버릿 반대)·페이퍼</t>
+          <t>각도 관찰 A1(소급)·1~3주 백테스트</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
+      <c r="F8" t="n">
+        <v>66.7</v>
+      </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2023~25 탐색 약한 꼴(10/4~) — 30픽/시즌 끝 보고 · &lt;50% 폐기 · ≥55% &amp; CLV ≥0 이면 상정</t>
+          <t>2026-10-05 소급(backfill_weeks.py) — 같은 규칙을 마감 라인에 적용, 전향 판정 표본과 별개</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)·페이퍼</t>
+          <t>티저 다리(소급)·1~3주 백테스트</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>58.8</v>
       </c>
       <c r="G9" t="n">
-        <v>-2</v>
+        <v>-3.47</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2023~25 탐색 약한 꼴(10/4~) — 30픽/시즌 끝 보고 · &lt;50% 폐기 · ≥55% &amp; CLV ≥0 이면 상정</t>
+          <t>2026-10-05 소급(backfill_weeks.py) — 같은 규칙을 마감 라인에 적용, 전향 판정 표본과 별개</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>평균 CLV · 실베팅</t>
+          <t>라인 뒤 새 정보(관찰·페이퍼)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+          <t>발행 「- 새 정보:」 줄(10/5~ 사전 등록 55b93ea) — 30픽: 평균 CLV&gt;0 &amp; ≥52.4% 상정 · &lt;50% 또는 CLV≤−0.5 폐기</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>평균 CLV · 발행 판단</t>
+          <t>각도 관찰 A1(원정 큰 페이버릿 반대)·페이퍼</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6471,61 +7890,91 @@
       <c r="E11" t="n">
         <v>0</v>
       </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+          <t>2023~25 탐색 약한 꼴(10/4~) — 30픽/시즌 끝 보고 · &lt;50% 폐기 · ≥55% &amp; CLV ≥0 이면 상정</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>평균 CLV · 발행 방향</t>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)·페이퍼</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05</v>
+        <v>-2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+          <t>2023~25 탐색 약한 꼴(10/4~) — 30픽/시즌 끝 보고 · &lt;50% 폐기 · ≥55% &amp; CLV ≥0 이면 상정</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>평균 CLV · 바람 언더</t>
+          <t>평균 CLV · 실베팅</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>평균 CLV · 발행 판단</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
         </is>
@@ -6534,109 +7983,102 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>실베팅 · 시장별</t>
+          <t>평균 CLV · 발행 방향</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>28</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>21</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  spread</t>
+          <t>평균 CLV · 바람 언더</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  total</t>
+          <t>평균 CLV · 라인 뒤 새 정보</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>실베팅 · 등급별</t>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  관심(설명문)</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>실베팅 · 시장별</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  실베팅</t>
+          <t xml:space="preserve">  spread</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -6645,120 +8087,205 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5</v>
+        <v>-1.5</v>
       </c>
       <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  total</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>모델 엣지 구간(전체 페이퍼 — 모델 검증)</t>
+          <t>실베팅 · 등급별</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| &lt;2</t>
+          <t xml:space="preserve">  관심(설명문)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.66</v>
+        <v>-1</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| 2~3.5</t>
+          <t xml:space="preserve">  실베팅</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.27</v>
+        <v>-2.5</v>
       </c>
       <c r="H24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  |엣지| 3.5~5</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>17</v>
-      </c>
-      <c r="C25" t="n">
-        <v>9</v>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>모델 엣지 구간(전체 페이퍼 — 모델 검증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  |엣지| &lt;2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>36</v>
+      </c>
+      <c r="C27" t="n">
+        <v>18</v>
+      </c>
+      <c r="D27" t="n">
+        <v>18</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>50</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-6.79</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  |엣지| 2~3.5</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  |엣지| 3.5~5</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>17</v>
+      </c>
+      <c r="C29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t xml:space="preserve">  |엣지| ≥5</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B30" t="n">
         <v>20</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C30" t="n">
         <v>9</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D30" t="n">
         <v>10</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E30" t="n">
         <v>1</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F30" t="n">
         <v>47.4</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G30" t="n">
         <v>-1.82</v>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6771,7 +8298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6843,25 +8370,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
       <c r="G2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6881,39 +8405,112 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B5" t="n">
         <v>3</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -3357,9 +3357,19 @@
       <c r="K44" t="n">
         <v>67.7</v>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>ARI 24-36 NYG</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
@@ -3550,9 +3560,19 @@
       <c r="K47" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>ARI 24-36 NYG</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
@@ -3672,9 +3692,19 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>ATL 45-24 NO</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0.353</v>
+      </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -3727,9 +3757,19 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>ATL 45-24 NO</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>-1</v>
+      </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -3788,9 +3828,19 @@
       <c r="K51" t="n">
         <v>79.3</v>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>ATL 45-24 NO</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>-1</v>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
@@ -3845,9 +3895,19 @@
       <c r="K52" t="n">
         <v>79.3</v>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>ATL 45-24 NO</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -3973,9 +4033,19 @@
       <c r="K54" t="n">
         <v>62.4</v>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>DAL 34-30 HOU</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>-1</v>
+      </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
@@ -4166,9 +4236,19 @@
       <c r="K57" t="n">
         <v>75.7</v>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>DAL 34-30 HOU</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
@@ -4359,9 +4439,19 @@
       <c r="K60" t="n">
         <v>75.2</v>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>DEN 14-24 SF</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>-1</v>
+      </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
@@ -4552,9 +4642,19 @@
       <c r="K63" t="n">
         <v>56.7</v>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>DET 26-32 CAR</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
@@ -4674,9 +4774,19 @@
       <c r="K65" t="n">
         <v>68.2</v>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>DET 26-32 CAR</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
@@ -4731,9 +4841,19 @@
       <c r="K66" t="n">
         <v>58.6</v>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>GB 17-14 TB</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
@@ -4859,9 +4979,19 @@
       <c r="K68" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>GB 17-14 TB</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>-1</v>
+      </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
@@ -4987,9 +5117,19 @@
       <c r="K70" t="n">
         <v>68.2</v>
       </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>IND 30-13 WAS</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
@@ -5178,9 +5318,19 @@
       <c r="K73" t="n">
         <v>82.8</v>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>JAX 22-17 CIN</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
@@ -5509,9 +5659,19 @@
       <c r="K78" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>KC 30-27 LV</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>-1</v>
+      </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
@@ -5637,9 +5797,19 @@
       <c r="K80" t="n">
         <v>72.5</v>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>KC 30-27 LV</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>-1</v>
+      </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
@@ -5830,9 +6000,19 @@
       <c r="K83" t="n">
         <v>62.1</v>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>LA 24-20 PHI</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
@@ -6025,9 +6205,19 @@
       <c r="K86" t="n">
         <v>58.1</v>
       </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>LAC 23-30 SEA</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
@@ -6153,9 +6343,19 @@
       <c r="K88" t="n">
         <v>87.3</v>
       </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>LAC 23-30 SEA</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>-1</v>
+      </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr">
@@ -6411,9 +6611,19 @@
       <c r="K92" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>NE 29-26 BUF</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
@@ -6539,9 +6749,19 @@
       <c r="K94" t="n">
         <v>77.3</v>
       </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>NE 29-26 BUF</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr">
@@ -6732,9 +6952,19 @@
       <c r="K97" t="n">
         <v>70.3</v>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>NYJ 12-23 CHI</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr">
@@ -7341,9 +7571,19 @@
       <c r="K106" t="n">
         <v>62.7</v>
       </c>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>TEN 18-24 BAL</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>-1</v>
+      </c>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr">
@@ -7469,9 +7709,19 @@
       <c r="K108" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>TEN 18-24 BAL</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>-1</v>
+      </c>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr">
@@ -7675,19 +7925,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.09</v>
+        <v>-3.18</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -7702,22 +7952,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>54.2</v>
+        <v>54.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.82</v>
+        <v>1.82</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -7732,10 +7982,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -7747,7 +7997,7 @@
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>0.72</v>
+        <v>1.08</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -7987,19 +8237,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -8190,13 +8440,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -8205,7 +8455,7 @@
         <v>50</v>
       </c>
       <c r="G27" t="n">
-        <v>-6.79</v>
+        <v>-7.44</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -8216,22 +8466,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>37.5</v>
+        <v>44.4</v>
       </c>
       <c r="G28" t="n">
-        <v>-2.27</v>
+        <v>-1.36</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -8242,22 +8492,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>52.9</v>
+        <v>47.6</v>
       </c>
       <c r="G29" t="n">
-        <v>0.18</v>
+        <v>-1.91</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -8268,22 +8518,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>47.4</v>
+        <v>54.3</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.82</v>
+        <v>1.27</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q109"/>
+  <dimension ref="A1:Q140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7801,6 +7801,1759 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>5</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BAL@ATL</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>BAL +3</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="J110" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="K110" t="n">
+        <v>63</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>2026_05_BAL_ATL:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>5</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>BAL@ATL</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Over 43.5</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J111" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K111" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>2026_05_BAL_ATL:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>5</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>CHI@GB</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>GB +2.5</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J112" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K112" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>2026_05_CHI_GB:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>5</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CHI@GB</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>GB +8.5</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-283</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 45.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>2026_05_CHI_GB:spread:T</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>5</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CHI@GB</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Over 45.5</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="J114" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K114" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>2026_05_CHI_GB:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>5</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CIN@MIA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>MIA +6.5</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="J115" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K115" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>2026_05_CIN_MIA:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>5</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CIN@MIA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Over 42.5</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="J116" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K116" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>2026_05_CIN_MIA:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>5</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CLE@NYJ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>CLE +2.5</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="J117" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="K117" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>2026_05_CLE_NYJ:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>5</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CLE@NYJ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CLE +8.5</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-283</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 39.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>2026_05_CLE_NYJ:spread:T</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>5</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>HOU@TEN</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>HOU -7.5</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="J119" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="K119" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>2026_05_HOU_TEN:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>5</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>HOU@TEN</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>HOU -1.5</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-283</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>원 라인 -7.5 · 총점 37.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>2026_05_HOU_TEN:spread:T</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>5</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>HOU@TEN</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>TEN +7.5</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>각도 관찰 A1(원정 큰 페이버릿 반대)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>원정 HOU -7.5 페이버릿 · 10-08 15:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>2026_05_HOU_TEN:spread:A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>5</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>IND@PIT</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>IND +2.5</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="J122" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="K122" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>2026_05_IND_PIT:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>5</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>IND@PIT</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>IND +8.5</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-283</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 44.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>2026_05_IND_PIT:spread:T</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>5</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>IND@PIT</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Over 44.5</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="J124" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K124" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>2026_05_IND_PIT:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>5</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>LV@NE</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NE -3.5</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J125" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K125" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>2026_05_LV_NE:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>5</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>LV@NE</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NE -3.5</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>언더독 LV 드라이브 득점 차 우위 +1.33 → 반대 NE · 10-08 15:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>2026_05_LV_NE:spread:A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>5</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>LV@NE</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Under 45.5</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>42</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="K127" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>2026_05_LV_NE:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>5</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>MIN@NO</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NO +8.5</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-283</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>2026_05_MIN_NO:spread:T</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>5</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>MIN@NO</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Under 41.5</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J129" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K129" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>2026_05_MIN_NO:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>5</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>NYG@WAS</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NYG +3.5</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="K130" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>2026_05_NYG_WAS:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>5</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>NYG@WAS</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>WAS -3.5</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>언더독 NYG 드라이브 득점 차 우위 +0.77 → 반대 WAS · 10-08 15:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>2026_05_NYG_WAS:spread:A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>5</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>NYG@WAS</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Over 41.5</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="J132" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="K132" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>2026_05_NYG_WAS:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>5</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PHI@JAX</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>JAX -1.5</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-283</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>원 라인 -7.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>2026_05_PHI_JAX:spread:T</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>5</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SF@SEA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>SF +3</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="J134" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="K134" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>2026_05_SF_SEA:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>5</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SF@SEA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>SEA -3</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>언더독 SF 드라이브 득점 차 우위 +0.76 → 반대 SEA · 10-08 15:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>2026_05_SF_SEA:spread:A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>5</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>TB +8.5</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J136" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K136" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>2026_05_TB_DAL:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>5</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>DAL -2.5</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-283</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>원 라인 -8.5 · 총점 48.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>2026_05_TB_DAL:spread:T</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>5</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DAL -8.5</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J138" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K138" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>2026_05_TB_DAL:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>5</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Over 48.5</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="J139" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K139" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>2026_05_TB_DAL:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>5</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Over 48.5</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="J140" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K140" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>2026_05_TB_DAL:total:D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7978,7 +9731,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>티저 다리(관찰·페이퍼)</t>
+          <t>티저 다리(관찰·페이퍼 — 10/10 폐지, 기록만)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -8001,7 +9754,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>웡 티저 다리(10/1~) — 손익분기 73.9%(−120 2팀 환산) · 60다리 보고 · &lt;72% 폐기 · 평균 표시가 73.0c(n 1)</t>
+          <t>웡 티저 다리(10/1~10/10 · Paul 「티저는 별로」로 적립 중단) — 손익분기 73.9%(−120 2팀 환산) · 평균 표시가 73.0c(n 1)</t>
         </is>
       </c>
     </row>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q140"/>
+  <dimension ref="A1:Q149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7817,11 +7817,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>BAL +3</t>
+          <t>BAL +3.5</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>-3</v>
+        <v>3.5</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -7835,26 +7835,24 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I110" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="J110" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="K110" t="n">
-        <v>63</v>
-      </c>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>원정 BAL 결장 확정 · 개장 +4.5 → 지금 -3.5(홈 기준, +8점 반대 이동) · 10-10 04:23 PT 판</t>
+        </is>
+      </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>2026_05_BAL_ATL:spread</t>
+          <t>2026_05_BAL_ATL:spread:A3</t>
         </is>
       </c>
     </row>
@@ -7864,21 +7862,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BAL@ATL</t>
+          <t>CHI@GB</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>GB +1.5</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>43.5</v>
+        <v>1.5</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -7896,13 +7894,13 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>49.3</v>
+        <v>2.4</v>
       </c>
       <c r="J111" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="K111" t="n">
-        <v>70.90000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
@@ -7911,7 +7909,7 @@
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>2026_05_BAL_ATL:total</t>
+          <t>2026_05_CHI_GB:spread</t>
         </is>
       </c>
     </row>
@@ -7931,15 +7929,15 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>GB +2.5</t>
+          <t>GB +8.5</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7949,26 +7947,24 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I112" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J112" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K112" t="n">
-        <v>63.8</v>
-      </c>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 45.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>2026_05_CHI_GB:spread</t>
+          <t>2026_05_CHI_GB:spread:T</t>
         </is>
       </c>
     </row>
@@ -7988,15 +7984,15 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>GB +8.5</t>
+          <t>GB +1.5</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8006,7 +8002,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -8018,12 +8014,12 @@
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>원 라인 +2.5 · 총점 45.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>홈 GB 결장 확정 · 개장 -3 → 지금 +1.5(홈 기준, +4.5점 반대 이동) · 10-10 04:23 PT 판</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>2026_05_CHI_GB:spread:T</t>
+          <t>2026_05_CHI_GB:spread:A3</t>
         </is>
       </c>
     </row>
@@ -8065,13 +8061,13 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="J114" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K114" t="n">
-        <v>66.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
@@ -8100,11 +8096,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>MIA +6.5</t>
+          <t>MIA +7</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -8122,13 +8118,13 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>-2.1</v>
+        <v>-1.7</v>
       </c>
       <c r="J115" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="K115" t="n">
-        <v>63.4</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
@@ -8152,16 +8148,16 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>MIA +7</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>42.5</v>
+        <v>7</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -8175,26 +8171,24 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I116" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="J116" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="K116" t="n">
-        <v>83.59999999999999</v>
-      </c>
+          <t>각도 관찰 A1(원정 큰 페이버릿 반대)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>원정 CIN -7 페이버릿 · 10-10 04:23 PT 판</t>
+        </is>
+      </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>2026_05_CIN_MIA:total</t>
+          <t>2026_05_CIN_MIA:spread:A1</t>
         </is>
       </c>
     </row>
@@ -8204,21 +8198,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CLE@NYJ</t>
+          <t>CIN@MIA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>CLE +2.5</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>-2.5</v>
+        <v>43.5</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -8236,13 +8230,13 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>-3.9</v>
+        <v>52.8</v>
       </c>
       <c r="J117" t="n">
-        <v>-6.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K117" t="n">
-        <v>68.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
@@ -8251,7 +8245,7 @@
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>2026_05_CLE_NYJ:spread</t>
+          <t>2026_05_CIN_MIA:total</t>
         </is>
       </c>
     </row>
@@ -8271,15 +8265,15 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>CLE +8.5</t>
+          <t>CLE +2.5</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>8.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8289,24 +8283,26 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J118" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="K118" t="n">
+        <v>56.4</v>
+      </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>원 라인 +2.5 · 총점 39.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
-        </is>
-      </c>
+      <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>2026_05_CLE_NYJ:spread:T</t>
+          <t>2026_05_CLE_NYJ:spread</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8312,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HOU@TEN</t>
+          <t>CLE@NYJ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8326,15 +8322,15 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>HOU -7.5</t>
+          <t>CLE +8.5</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8344,26 +8340,24 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I119" t="n">
-        <v>-12.3</v>
-      </c>
-      <c r="J119" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="K119" t="n">
-        <v>64.3</v>
-      </c>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 39.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:spread</t>
+          <t>2026_05_CLE_NYJ:spread:T</t>
         </is>
       </c>
     </row>
@@ -8373,25 +8367,25 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HOU@TEN</t>
+          <t>CLE@NYJ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>HOU -1.5</t>
+          <t>Under 39.5</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>-1.5</v>
+        <v>39.5</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8401,24 +8395,26 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>33</v>
+      </c>
+      <c r="J120" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="K120" t="n">
+        <v>73.3</v>
+      </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>원 라인 -7.5 · 총점 37.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
-        </is>
-      </c>
+      <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:spread:T</t>
+          <t>2026_05_CLE_NYJ:total</t>
         </is>
       </c>
     </row>
@@ -8428,7 +8424,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HOU@TEN</t>
+          <t>DEN@LAC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8438,11 +8434,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>TEN +7.5</t>
+          <t>DEN -3.5</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -8456,24 +8452,26 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>각도 관찰 A1(원정 큰 페이버릿 반대)</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="J121" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K121" t="n">
+        <v>59.3</v>
+      </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>원정 HOU -7.5 페이버릿 · 10-08 15:51 PT 판</t>
-        </is>
-      </c>
+      <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:spread:A1</t>
+          <t>2026_05_DEN_LAC:spread</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8481,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>IND@PIT</t>
+          <t>DEN@LAC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8493,11 +8491,11 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>IND +2.5</t>
+          <t>LAC +3.5</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>-2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -8511,26 +8509,24 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I122" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="J122" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="K122" t="n">
-        <v>58.6</v>
-      </c>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>홈 LAC 결장 확정 · 개장 -2.5 → 지금 +3.5(홈 기준, +6점 반대 이동) · 10-10 04:23 PT 판</t>
+        </is>
+      </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>2026_05_IND_PIT:spread</t>
+          <t>2026_05_DEN_LAC:spread:A3</t>
         </is>
       </c>
     </row>
@@ -8540,25 +8536,25 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IND@PIT</t>
+          <t>DEN@LAC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>IND +8.5</t>
+          <t>Under 41.5</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>8.5</v>
+        <v>41.5</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -8568,24 +8564,26 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="J123" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="K123" t="n">
+        <v>72.2</v>
+      </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr">
-        <is>
-          <t>원 라인 +2.5 · 총점 44.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
-        </is>
-      </c>
+      <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>2026_05_IND_PIT:spread:T</t>
+          <t>2026_05_DEN_LAC:total</t>
         </is>
       </c>
     </row>
@@ -8595,21 +8593,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IND@PIT</t>
+          <t>DET@ARI</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>DET -5.5</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>44.5</v>
+        <v>-5.5</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -8623,26 +8621,24 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I124" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="J124" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K124" t="n">
-        <v>65.2</v>
-      </c>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>원정 DET 결장 확정 · 개장 +8.5 → 지금 +5.5(홈 기준, +3점 반대 이동) · 10-10 04:23 PT 판</t>
+        </is>
+      </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>2026_05_IND_PIT:total</t>
+          <t>2026_05_DET_ARI:spread:A3</t>
         </is>
       </c>
     </row>
@@ -8652,7 +8648,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LV@NE</t>
+          <t>HOU@TEN</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8662,11 +8658,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NE -3.5</t>
+          <t>HOU -7</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>-3.5</v>
+        <v>7</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -8684,13 +8680,13 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>13.4</v>
+        <v>-12.5</v>
       </c>
       <c r="J125" t="n">
-        <v>9.9</v>
+        <v>-5.5</v>
       </c>
       <c r="K125" t="n">
-        <v>77.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
@@ -8699,7 +8695,7 @@
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:spread</t>
+          <t>2026_05_HOU_TEN:spread</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8705,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LV@NE</t>
+          <t>HOU@TEN</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8719,15 +8715,15 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NE -3.5</t>
+          <t>HOU -1.5</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>-3.5</v>
+        <v>-1.5</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -8737,7 +8733,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+          <t>티저 다리(관찰)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -8749,12 +8745,12 @@
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>언더독 LV 드라이브 득점 차 우위 +1.33 → 반대 NE · 10-08 15:51 PT 판</t>
+          <t>원 라인 -7.5 · 총점 37.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:spread:A2</t>
+          <t>2026_05_HOU_TEN:spread:T</t>
         </is>
       </c>
     </row>
@@ -8764,21 +8760,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LV@NE</t>
+          <t>HOU@TEN</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>TEN +7</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>45.5</v>
+        <v>7</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -8792,26 +8788,24 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I127" t="n">
-        <v>42</v>
-      </c>
-      <c r="J127" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="K127" t="n">
-        <v>62.9</v>
-      </c>
+          <t>각도 관찰 A1(원정 큰 페이버릿 반대)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>원정 HOU -7 페이버릿 · 10-10 04:23 PT 판</t>
+        </is>
+      </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:total</t>
+          <t>2026_05_HOU_TEN:spread:A1</t>
         </is>
       </c>
     </row>
@@ -8821,7 +8815,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MIN@NO</t>
+          <t>HOU@TEN</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8831,15 +8825,15 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NO +8.5</t>
+          <t>TEN +7</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -8849,7 +8843,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -8861,12 +8855,12 @@
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>원 라인 +2.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>홈 TEN 결장 확정 · 개장 +3.5 → 지금 +7(홈 기준, +3.5점 반대 이동) · 10-10 04:23 PT 판</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>2026_05_MIN_NO:spread:T</t>
+          <t>2026_05_HOU_TEN:spread:A3</t>
         </is>
       </c>
     </row>
@@ -8876,21 +8870,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MIN@NO</t>
+          <t>IND@PIT</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Under 41.5</t>
+          <t>IND +3</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>41.5</v>
+        <v>-3</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -8904,17 +8898,17 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>32.5</v>
+        <v>-0.4</v>
       </c>
       <c r="J129" t="n">
-        <v>-9</v>
+        <v>-3.4</v>
       </c>
       <c r="K129" t="n">
-        <v>80.40000000000001</v>
+        <v>60.2</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
@@ -8923,7 +8917,7 @@
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>2026_05_MIN_NO:total</t>
+          <t>2026_05_IND_PIT:spread</t>
         </is>
       </c>
     </row>
@@ -8933,7 +8927,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NYG@WAS</t>
+          <t>IND@PIT</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8943,15 +8937,15 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NYG +3.5</t>
+          <t>IND +8.5</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>-3.5</v>
+        <v>8.5</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -8961,26 +8955,24 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I130" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J130" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="K130" t="n">
-        <v>63.5</v>
-      </c>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 44.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>2026_05_NYG_WAS:spread</t>
+          <t>2026_05_IND_PIT:spread:T</t>
         </is>
       </c>
     </row>
@@ -8990,21 +8982,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NYG@WAS</t>
+          <t>IND@PIT</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>WAS -3.5</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>-3.5</v>
+        <v>43.5</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -9018,24 +9010,26 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="J131" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K131" t="n">
+        <v>69</v>
+      </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>언더독 NYG 드라이브 득점 차 우위 +0.77 → 반대 WAS · 10-08 15:51 PT 판</t>
-        </is>
-      </c>
+      <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>2026_05_NYG_WAS:spread:A2</t>
+          <t>2026_05_IND_PIT:total</t>
         </is>
       </c>
     </row>
@@ -9045,21 +9039,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NYG@WAS</t>
+          <t>LV@NE</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>NE -3.5</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>41.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -9077,13 +9071,13 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>52.6</v>
+        <v>13.9</v>
       </c>
       <c r="J132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="K132" t="n">
-        <v>85.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
@@ -9092,7 +9086,7 @@
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>2026_05_NYG_WAS:total</t>
+          <t>2026_05_LV_NE:spread</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9096,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PHI@JAX</t>
+          <t>LV@NE</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -9112,15 +9106,15 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>JAX -1.5</t>
+          <t>NE -3.5</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>-1.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9130,7 +9124,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -9142,12 +9136,12 @@
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>원 라인 -7.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>언더독 LV 드라이브 득점 차 우위 +1.33 → 반대 NE · 10-10 04:23 PT 판</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>2026_05_PHI_JAX:spread:T</t>
+          <t>2026_05_LV_NE:spread:A2</t>
         </is>
       </c>
     </row>
@@ -9157,7 +9151,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SF@SEA</t>
+          <t>LV@NE</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9167,11 +9161,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>SF +3</t>
+          <t>NE -3.5</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>-3</v>
+        <v>-3.5</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -9185,26 +9179,24 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I134" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="J134" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="K134" t="n">
-        <v>60.2</v>
-      </c>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>홈 NE 결장 확정 · 개장 -8.5 → 지금 -3.5(홈 기준, +5점 반대 이동) · 10-10 04:23 PT 판</t>
+        </is>
+      </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>2026_05_SF_SEA:spread</t>
+          <t>2026_05_LV_NE:spread:A3</t>
         </is>
       </c>
     </row>
@@ -9214,21 +9206,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SF@SEA</t>
+          <t>LV@NE</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>SEA -3</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>-3</v>
+        <v>45.5</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -9242,24 +9234,26 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>42</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="K135" t="n">
+        <v>63.2</v>
+      </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>언더독 SF 드라이브 득점 차 우위 +0.76 → 반대 SEA · 10-08 15:51 PT 판</t>
-        </is>
-      </c>
+      <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>2026_05_SF_SEA:spread:A2</t>
+          <t>2026_05_LV_NE:total</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9263,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TB@DAL</t>
+          <t>MIN@NO</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9279,15 +9273,15 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>TB +8.5</t>
+          <t>NO +8.5</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>-8.5</v>
+        <v>8.5</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -9297,26 +9291,24 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I136" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J136" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="K136" t="n">
-        <v>59.3</v>
-      </c>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>2026_05_TB_DAL:spread</t>
+          <t>2026_05_MIN_NO:spread:T</t>
         </is>
       </c>
     </row>
@@ -9326,25 +9318,25 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TB@DAL</t>
+          <t>MIN@NO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>DAL -2.5</t>
+          <t>Under 41.5</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>-2.5</v>
+        <v>41.5</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -9354,24 +9346,26 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="J137" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="K137" t="n">
+        <v>81.09999999999999</v>
+      </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>원 라인 -8.5 · 총점 48.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
-        </is>
-      </c>
+      <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>2026_05_TB_DAL:spread:T</t>
+          <t>2026_05_MIN_NO:total</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9375,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TB@DAL</t>
+          <t>NYG@WAS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9391,11 +9385,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>DAL -8.5</t>
+          <t>NYG +3.5</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>-8.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -9409,30 +9403,26 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>5.4</v>
+        <v>-5.5</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.1</v>
+        <v>-9</v>
       </c>
       <c r="K138" t="n">
-        <v>59.3</v>
+        <v>75.5</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>2026_05_TB_DAL:spread:D</t>
+          <t>2026_05_NYG_WAS:spread</t>
         </is>
       </c>
     </row>
@@ -9442,21 +9432,21 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TB@DAL</t>
+          <t>NYG@WAS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>WAS -3.5</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>48.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -9470,26 +9460,24 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I139" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="J139" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K139" t="n">
-        <v>66.2</v>
-      </c>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>언더독 NYG 드라이브 득점 차 우위 +0.77 → 반대 WAS · 10-10 04:23 PT 판</t>
+        </is>
+      </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>2026_05_TB_DAL:total</t>
+          <t>2026_05_NYG_WAS:spread:A2</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9487,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TB@DAL</t>
+          <t>NYG@WAS</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9509,11 +9497,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>48.5</v>
+        <v>41.5</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -9527,28 +9515,537 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>52.9</v>
+        <v>48.3</v>
       </c>
       <c r="J140" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="K140" t="n">
-        <v>66.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr">
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>2026_05_NYG_WAS:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>5</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PHI@JAX</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>JAX -1.5</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-283</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>원 라인 -7.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>2026_05_PHI_JAX:spread:T</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>5</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PHI@JAX</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>PHI +7.5</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>원정 PHI 결장 확정 · 개장 +2.5 → 지금 -7.5(홈 기준, +10점 반대 이동) · 10-10 04:23 PT 판</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>2026_05_PHI_JAX:spread:A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>5</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SF@SEA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>SF +3</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="J143" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K143" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>2026_05_SF_SEA:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>5</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SF@SEA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SEA -3</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>언더독 SF 드라이브 득점 차 우위 +0.76 → 반대 SEA · 10-10 04:23 PT 판</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>2026_05_SF_SEA:spread:A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>5</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>TB +9.5</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J145" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="K145" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>2026_05_TB_DAL:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>5</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>DAL -2.5</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-283</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>원 라인 -8.5 · 총점 48.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>2026_05_TB_DAL:spread:T</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>5</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>DAL -8.5</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J147" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K147" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
         <is>
           <t>발행 방향</t>
         </is>
       </c>
-      <c r="Q140" t="inlineStr">
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>2026_05_TB_DAL:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>5</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Over 49.5</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="J148" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K148" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>2026_05_TB_DAL:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>5</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Over 48.5</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="J149" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K149" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
         <is>
           <t>2026_05_TB_DAL:total:D</t>
         </is>
@@ -9565,7 +10062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9935,47 +10432,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>평균 CLV · 실베팅</t>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)·페이퍼</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
+          <t>2023~25 탐색 약한 꼴(10/4~) — 30픽/시즌 끝 보고 · &lt;50% 폐기 · ≥55% &amp; CLV ≥0 이면 상정</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>평균 CLV · 발행 판단</t>
+          <t>평균 CLV · 실베팅</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.33</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -9986,23 +10486,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>평균 CLV · 발행 방향</t>
+          <t>평균 CLV · 발행 판단</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>22</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -10013,23 +10510,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>평균 CLV · 바람 언더</t>
+          <t>평균 CLV · 발행 방향</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -10040,11 +10537,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>평균 CLV · 라인 뒤 새 정보</t>
+          <t>평균 CLV · 바람 언더</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -10053,6 +10550,9 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
@@ -10061,53 +10561,51 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>실베팅 · 시장별</t>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>평균 CLV · 라인 뒤 새 정보</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>픽/우리 쪽 이동/반대/같음 · 「유닛」 칸 = 평균 CLV(점)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  spread</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>실베팅 · 시장별</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  total</t>
+          <t xml:space="preserve">  spread</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -10116,57 +10614,57 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>실베팅 · 등급별</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  total</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  관심(설명문)</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>실베팅 · 등급별</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  실베팅</t>
+          <t xml:space="preserve">  관심(설명문)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -10175,120 +10673,146 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  실베팅</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
         <v>-2.5</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>모델 엣지 구간(전체 페이퍼 — 모델 검증)</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| &lt;2</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>38</v>
-      </c>
-      <c r="C27" t="n">
-        <v>19</v>
-      </c>
-      <c r="D27" t="n">
-        <v>19</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>50</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-7.44</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>모델 엣지 구간(전체 페이퍼 — 모델 검증)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| 2~3.5</t>
+          <t xml:space="preserve">  |엣지| &lt;2</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.36</v>
+        <v>-7.44</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  |엣지| 3.5~5</t>
+          <t xml:space="preserve">  |엣지| 2~3.5</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>47.6</v>
+        <v>44.4</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.91</v>
+        <v>-1.36</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t xml:space="preserve">  |엣지| 3.5~5</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>21</v>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="n">
+        <v>11</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t xml:space="preserve">  |엣지| ≥5</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B31" t="n">
         <v>36</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C31" t="n">
         <v>19</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D31" t="n">
         <v>16</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E31" t="n">
         <v>1</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F31" t="n">
         <v>54.3</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G31" t="n">
         <v>1.27</v>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q149"/>
+  <dimension ref="A1:Q175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7817,11 +7817,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>BAL +3.5</t>
+          <t>BAL +3</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>원정 BAL 결장 확정 · 개장 +4.5 → 지금 -3.5(홈 기준, +8점 반대 이동) · 10-10 04:23 PT 판</t>
+          <t>원정 BAL 결장 확정 · 개장 +4.5 → 지금 -3(홈 기준, +7.5점 반대 이동) · 10-11 08:35 PT 판</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CHI@GB</t>
+          <t>BAL@ATL</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7872,11 +7872,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>GB +1.5</t>
+          <t>BAL +3.5</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -7890,26 +7890,24 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I111" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J111" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K111" t="n">
-        <v>61.9</v>
-      </c>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>2026_05_CHI_GB:spread</t>
+          <t>2026_05_BAL_ATL:spread:D</t>
         </is>
       </c>
     </row>
@@ -7919,25 +7917,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CHI@GB</t>
+          <t>BAL@ATL</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>GB +8.5</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>8.5</v>
+        <v>43.5</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7947,7 +7945,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -7959,12 +7957,12 @@
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>원 라인 +2.5 · 총점 45.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>2026_05_CHI_GB:spread:T</t>
+          <t>2026_05_BAL_ATL:total:D</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7972,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CHI@GB</t>
+          <t>BUF@LA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7984,11 +7982,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>GB +1.5</t>
+          <t>LA -3</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1.5</v>
+        <v>-3</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8002,7 +8000,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -8014,12 +8012,12 @@
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>홈 GB 결장 확정 · 개장 -3 → 지금 +1.5(홈 기준, +4.5점 반대 이동) · 10-10 04:23 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>2026_05_CHI_GB:spread:A3</t>
+          <t>2026_05_BUF_LA:spread:D</t>
         </is>
       </c>
     </row>
@@ -8029,7 +8027,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CHI@GB</t>
+          <t>BUF@LA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -8039,11 +8037,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>Over 54.5</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>45.5</v>
+        <v>54.5</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -8057,26 +8055,24 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I114" t="n">
-        <v>50</v>
-      </c>
-      <c r="J114" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K114" t="n">
-        <v>66.59999999999999</v>
-      </c>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>2026_05_CHI_GB:total</t>
+          <t>2026_05_BUF_LA:total:D</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8082,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CIN@MIA</t>
+          <t>CHI@GB</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -8096,11 +8092,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>MIA +7</t>
+          <t>GB +1.5</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -8118,13 +8114,13 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>-1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J115" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="K115" t="n">
-        <v>65.90000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
@@ -8133,7 +8129,7 @@
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>2026_05_CIN_MIA:spread</t>
+          <t>2026_05_CHI_GB:spread</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8139,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CIN@MIA</t>
+          <t>CHI@GB</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -8153,15 +8149,15 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>MIA +7</t>
+          <t>GB +8.5</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8171,7 +8167,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>각도 관찰 A1(원정 큰 페이버릿 반대)</t>
+          <t>티저 다리(관찰)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -8183,12 +8179,12 @@
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>원정 CIN -7 페이버릿 · 10-10 04:23 PT 판</t>
+          <t>원 라인 +2.5 · 총점 45.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>2026_05_CIN_MIA:spread:A1</t>
+          <t>2026_05_CHI_GB:spread:T</t>
         </is>
       </c>
     </row>
@@ -8198,21 +8194,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CIN@MIA</t>
+          <t>CHI@GB</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>GB +1.5</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>43.5</v>
+        <v>1.5</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -8226,26 +8222,24 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I117" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="J117" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="K117" t="n">
-        <v>81.2</v>
-      </c>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>홈 GB 결장 확정 · 개장 -3 → 지금 +1.5(홈 기준, +4.5점 반대 이동) · 10-11 08:35 PT 판</t>
+        </is>
+      </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>2026_05_CIN_MIA:total</t>
+          <t>2026_05_CHI_GB:spread:A3</t>
         </is>
       </c>
     </row>
@@ -8255,7 +8249,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CLE@NYJ</t>
+          <t>CHI@GB</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8265,11 +8259,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>CLE +2.5</t>
+          <t>CHI -1.5</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>-2.5</v>
+        <v>-1.5</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -8283,26 +8277,30 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J118" t="n">
-        <v>-2.1</v>
+        <v>3.9</v>
       </c>
       <c r="K118" t="n">
-        <v>56.4</v>
+        <v>61.9</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>2026_05_CLE_NYJ:spread</t>
+          <t>2026_05_CHI_GB:spread:D</t>
         </is>
       </c>
     </row>
@@ -8312,25 +8310,25 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CLE@NYJ</t>
+          <t>CHI@GB</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>CLE +8.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>8.5</v>
+        <v>47.5</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8340,7 +8338,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -8352,12 +8350,12 @@
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>원 라인 +2.5 · 총점 39.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>2026_05_CLE_NYJ:spread:T</t>
+          <t>2026_05_CHI_GB:total:D</t>
         </is>
       </c>
     </row>
@@ -8367,21 +8365,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CLE@NYJ</t>
+          <t>CIN@MIA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Under 39.5</t>
+          <t>MIA +7</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>39.5</v>
+        <v>7</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -8399,13 +8397,13 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>33</v>
+        <v>-1.7</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.5</v>
+        <v>5.3</v>
       </c>
       <c r="K120" t="n">
-        <v>73.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
@@ -8414,7 +8412,7 @@
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>2026_05_CLE_NYJ:total</t>
+          <t>2026_05_CIN_MIA:spread</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8422,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DEN@LAC</t>
+          <t>CIN@MIA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8434,11 +8432,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>DEN -3.5</t>
+          <t>MIA +7</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -8452,26 +8450,24 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I121" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="J121" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="K121" t="n">
-        <v>59.3</v>
-      </c>
+          <t>각도 관찰 A1(원정 큰 페이버릿 반대)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>원정 CIN -7 페이버릿 · 10-11 08:35 PT 판</t>
+        </is>
+      </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>2026_05_DEN_LAC:spread</t>
+          <t>2026_05_CIN_MIA:spread:A1</t>
         </is>
       </c>
     </row>
@@ -8481,7 +8477,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DEN@LAC</t>
+          <t>CIN@MIA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8491,11 +8487,11 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LAC +3.5</t>
+          <t>MIA +7</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -8509,24 +8505,30 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="J122" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K122" t="n">
+        <v>65.90000000000001</v>
+      </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>홈 LAC 결장 확정 · 개장 -2.5 → 지금 +3.5(홈 기준, +6점 반대 이동) · 10-10 04:23 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>2026_05_DEN_LAC:spread:A3</t>
+          <t>2026_05_CIN_MIA:spread:D</t>
         </is>
       </c>
     </row>
@@ -8536,7 +8538,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DEN@LAC</t>
+          <t>CIN@MIA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8546,11 +8548,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Under 41.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>41.5</v>
+        <v>44.5</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -8568,13 +8570,13 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>35.3</v>
+        <v>52.8</v>
       </c>
       <c r="J123" t="n">
-        <v>-6.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K123" t="n">
-        <v>72.2</v>
+        <v>78.5</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
@@ -8583,7 +8585,7 @@
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>2026_05_DEN_LAC:total</t>
+          <t>2026_05_CIN_MIA:total</t>
         </is>
       </c>
     </row>
@@ -8593,21 +8595,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DET@ARI</t>
+          <t>CIN@MIA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>DET -5.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>-5.5</v>
+        <v>44.5</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -8621,24 +8623,30 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="J124" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K124" t="n">
+        <v>78.5</v>
+      </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>원정 DET 결장 확정 · 개장 +8.5 → 지금 +5.5(홈 기준, +3점 반대 이동) · 10-10 04:23 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>2026_05_DET_ARI:spread:A3</t>
+          <t>2026_05_CIN_MIA:total:D</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8656,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>HOU@TEN</t>
+          <t>CLE@NYJ</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8658,11 +8666,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>HOU -7</t>
+          <t>CLE +2.5</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>7</v>
+        <v>-2.5</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -8676,17 +8684,17 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>-12.5</v>
+        <v>0.4</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.5</v>
+        <v>-2.1</v>
       </c>
       <c r="K125" t="n">
-        <v>66.3</v>
+        <v>56.4</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
@@ -8695,7 +8703,7 @@
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:spread</t>
+          <t>2026_05_CLE_NYJ:spread</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8713,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>HOU@TEN</t>
+          <t>CLE@NYJ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8715,11 +8723,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>HOU -1.5</t>
+          <t>CLE +8.5</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>-1.5</v>
+        <v>8.5</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -8745,12 +8753,12 @@
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>원 라인 -7.5 · 총점 37.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>원 라인 +2.5 · 총점 39.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:spread:T</t>
+          <t>2026_05_CLE_NYJ:spread:T</t>
         </is>
       </c>
     </row>
@@ -8760,7 +8768,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>HOU@TEN</t>
+          <t>CLE@NYJ</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8770,11 +8778,11 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>TEN +7</t>
+          <t>NYJ -2.5</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>7</v>
+        <v>-2.5</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -8788,24 +8796,30 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>각도 관찰 A1(원정 큰 페이버릿 반대)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="K127" t="n">
+        <v>56.4</v>
+      </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>원정 HOU -7 페이버릿 · 10-10 04:23 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:spread:A1</t>
+          <t>2026_05_CLE_NYJ:spread:D</t>
         </is>
       </c>
     </row>
@@ -8815,21 +8829,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>HOU@TEN</t>
+          <t>CLE@NYJ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>TEN +7</t>
+          <t>Under 38.5</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>7</v>
+        <v>38.5</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -8843,24 +8857,26 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>33</v>
+      </c>
+      <c r="J128" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="K128" t="n">
+        <v>70</v>
+      </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>홈 TEN 결장 확정 · 개장 +3.5 → 지금 +7(홈 기준, +3.5점 반대 이동) · 10-10 04:23 PT 판</t>
-        </is>
-      </c>
+      <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:spread:A3</t>
+          <t>2026_05_CLE_NYJ:total</t>
         </is>
       </c>
     </row>
@@ -8870,21 +8886,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>IND@PIT</t>
+          <t>CLE@NYJ</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>IND +3</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>-3</v>
+        <v>38.5</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -8898,26 +8914,30 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>-0.4</v>
+        <v>33</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.4</v>
+        <v>-5.5</v>
       </c>
       <c r="K129" t="n">
-        <v>60.2</v>
+        <v>70</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>2026_05_IND_PIT:spread</t>
+          <t>2026_05_CLE_NYJ:total:D</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8947,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>IND@PIT</t>
+          <t>DEN@LAC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8937,15 +8957,15 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>IND +8.5</t>
+          <t>DEN -3.5</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -8955,24 +8975,26 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K130" t="n">
+        <v>59.3</v>
+      </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>원 라인 +2.5 · 총점 44.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
-        </is>
-      </c>
+      <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>2026_05_IND_PIT:spread:T</t>
+          <t>2026_05_DEN_LAC:spread</t>
         </is>
       </c>
     </row>
@@ -8982,21 +9004,21 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>IND@PIT</t>
+          <t>DEN@LAC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>LAC +3.5</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>43.5</v>
+        <v>3.5</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -9010,26 +9032,24 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I131" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="J131" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K131" t="n">
-        <v>69</v>
-      </c>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>홈 LAC 결장 확정 · 개장 -2.5 → 지금 +3.5(홈 기준, +6점 반대 이동) · 10-11 08:35 PT 판</t>
+        </is>
+      </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>2026_05_IND_PIT:total</t>
+          <t>2026_05_DEN_LAC:spread:A3</t>
         </is>
       </c>
     </row>
@@ -9039,7 +9059,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LV@NE</t>
+          <t>DEN@LAC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -9049,11 +9069,11 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NE -3.5</t>
+          <t>LAC +3.5</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>-3.5</v>
+        <v>3.5</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -9067,26 +9087,30 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>13.9</v>
+        <v>-6.6</v>
       </c>
       <c r="J132" t="n">
-        <v>10.4</v>
+        <v>-3.1</v>
       </c>
       <c r="K132" t="n">
-        <v>78.90000000000001</v>
+        <v>59.3</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:spread</t>
+          <t>2026_05_DEN_LAC:spread:D</t>
         </is>
       </c>
     </row>
@@ -9096,21 +9120,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>LV@NE</t>
+          <t>DEN@LAC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NE -3.5</t>
+          <t>Under 41.5</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>-3.5</v>
+        <v>41.5</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -9124,24 +9148,26 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="J133" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="K133" t="n">
+        <v>72.2</v>
+      </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>언더독 LV 드라이브 득점 차 우위 +1.33 → 반대 NE · 10-10 04:23 PT 판</t>
-        </is>
-      </c>
+      <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:spread:A2</t>
+          <t>2026_05_DEN_LAC:total</t>
         </is>
       </c>
     </row>
@@ -9151,21 +9177,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>LV@NE</t>
+          <t>DEN@LAC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NE -3.5</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>-3.5</v>
+        <v>41.5</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -9179,24 +9205,30 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="J134" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="K134" t="n">
+        <v>72.2</v>
+      </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>홈 NE 결장 확정 · 개장 -8.5 → 지금 -3.5(홈 기준, +5점 반대 이동) · 10-10 04:23 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:spread:A3</t>
+          <t>2026_05_DEN_LAC:total:D</t>
         </is>
       </c>
     </row>
@@ -9206,21 +9238,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>LV@NE</t>
+          <t>DET@ARI</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>DET -5.5</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>45.5</v>
+        <v>-5.5</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -9234,26 +9266,24 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I135" t="n">
-        <v>42</v>
-      </c>
-      <c r="J135" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="K135" t="n">
-        <v>63.2</v>
-      </c>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>원정 DET 결장 확정 · 개장 +8.5 → 지금 +5.5(홈 기준, +3점 반대 이동) · 10-11 08:35 PT 판</t>
+        </is>
+      </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:total</t>
+          <t>2026_05_DET_ARI:spread:A3</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9293,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MIN@NO</t>
+          <t>DET@ARI</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9273,15 +9303,15 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NO +8.5</t>
+          <t>ARI +5.5</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -9291,7 +9321,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -9303,12 +9333,12 @@
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>원 라인 +2.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>2026_05_MIN_NO:spread:T</t>
+          <t>2026_05_DET_ARI:spread:D</t>
         </is>
       </c>
     </row>
@@ -9318,7 +9348,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MIN@NO</t>
+          <t>DET@ARI</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9328,11 +9358,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Under 41.5</t>
+          <t>Over 54.5</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>41.5</v>
+        <v>54.5</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -9346,26 +9376,24 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I137" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="J137" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="K137" t="n">
-        <v>81.09999999999999</v>
-      </c>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>2026_05_MIN_NO:total</t>
+          <t>2026_05_DET_ARI:total:D</t>
         </is>
       </c>
     </row>
@@ -9375,7 +9403,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NYG@WAS</t>
+          <t>HOU@TEN</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9385,11 +9413,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NYG +3.5</t>
+          <t>HOU -6.5</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>-3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -9407,13 +9435,13 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>-5.5</v>
+        <v>-12.5</v>
       </c>
       <c r="J138" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="K138" t="n">
-        <v>75.5</v>
+        <v>67.7</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
@@ -9422,7 +9450,7 @@
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>2026_05_NYG_WAS:spread</t>
+          <t>2026_05_HOU_TEN:spread</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9460,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>NYG@WAS</t>
+          <t>HOU@TEN</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9442,15 +9470,15 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>WAS -3.5</t>
+          <t>HOU -1.5</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>-3.5</v>
+        <v>-1.5</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -9460,7 +9488,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+          <t>티저 다리(관찰)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -9472,12 +9500,12 @@
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>언더독 NYG 드라이브 득점 차 우위 +0.77 → 반대 WAS · 10-10 04:23 PT 판</t>
+          <t>원 라인 -7.5 · 총점 37.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>2026_05_NYG_WAS:spread:A2</t>
+          <t>2026_05_HOU_TEN:spread:T</t>
         </is>
       </c>
     </row>
@@ -9487,21 +9515,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NYG@WAS</t>
+          <t>HOU@TEN</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>TEN +6.5</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>41.5</v>
+        <v>6.5</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -9515,26 +9543,24 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I140" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="J140" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K140" t="n">
-        <v>74.09999999999999</v>
-      </c>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>홈 TEN 결장 확정 · 개장 +3.5 → 지금 +6.5(홈 기준, +3점 반대 이동) · 10-11 08:35 PT 판</t>
+        </is>
+      </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>2026_05_NYG_WAS:total</t>
+          <t>2026_05_HOU_TEN:spread:A3</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9570,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PHI@JAX</t>
+          <t>HOU@TEN</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9554,15 +9580,15 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>JAX -1.5</t>
+          <t>HOU -6.5</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>-1.5</v>
+        <v>-6.5</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -9572,24 +9598,30 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="J141" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K141" t="n">
+        <v>67.7</v>
+      </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>원 라인 -7.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>2026_05_PHI_JAX:spread:T</t>
+          <t>2026_05_HOU_TEN:spread:D</t>
         </is>
       </c>
     </row>
@@ -9599,21 +9631,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PHI@JAX</t>
+          <t>HOU@TEN</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>PHI +7.5</t>
+          <t>Under 37.5</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>7.5</v>
+        <v>37.5</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -9627,7 +9659,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -9639,12 +9671,12 @@
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>원정 PHI 결장 확정 · 개장 +2.5 → 지금 -7.5(홈 기준, +10점 반대 이동) · 10-10 04:23 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>2026_05_PHI_JAX:spread:A3</t>
+          <t>2026_05_HOU_TEN:total:D</t>
         </is>
       </c>
     </row>
@@ -9654,7 +9686,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SF@SEA</t>
+          <t>IND@PIT</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9664,7 +9696,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>SF +3</t>
+          <t>IND +3</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -9686,13 +9718,13 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="J143" t="n">
-        <v>-3.1</v>
+        <v>-3.4</v>
       </c>
       <c r="K143" t="n">
-        <v>59.5</v>
+        <v>60.2</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
@@ -9701,7 +9733,7 @@
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>2026_05_SF_SEA:spread</t>
+          <t>2026_05_IND_PIT:spread</t>
         </is>
       </c>
     </row>
@@ -9711,7 +9743,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SF@SEA</t>
+          <t>IND@PIT</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9721,15 +9753,15 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>SEA -3</t>
+          <t>IND +8.5</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>-3</v>
+        <v>8.5</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -9739,7 +9771,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+          <t>티저 다리(관찰)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -9751,12 +9783,12 @@
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>언더독 SF 드라이브 득점 차 우위 +0.76 → 반대 SEA · 10-10 04:23 PT 판</t>
+          <t>원 라인 +2.5 · 총점 44.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>2026_05_SF_SEA:spread:A2</t>
+          <t>2026_05_IND_PIT:spread:T</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9798,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TB@DAL</t>
+          <t>IND@PIT</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9776,11 +9808,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>TB +9.5</t>
+          <t>IND +3</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>-9.5</v>
+        <v>3</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -9794,26 +9826,30 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.6</v>
+        <v>-0.4</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.9</v>
+        <v>-3.4</v>
       </c>
       <c r="K145" t="n">
-        <v>67.59999999999999</v>
+        <v>60.2</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>2026_05_TB_DAL:spread</t>
+          <t>2026_05_IND_PIT:spread:D</t>
         </is>
       </c>
     </row>
@@ -9823,25 +9859,25 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TB@DAL</t>
+          <t>IND@PIT</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>DAL -2.5</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>-2.5</v>
+        <v>41.5</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -9851,24 +9887,26 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="J146" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K146" t="n">
+        <v>75.40000000000001</v>
+      </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr">
-        <is>
-          <t>원 라인 -8.5 · 총점 48.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
-        </is>
-      </c>
+      <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>2026_05_TB_DAL:spread:T</t>
+          <t>2026_05_IND_PIT:total</t>
         </is>
       </c>
     </row>
@@ -9878,21 +9916,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TB@DAL</t>
+          <t>IND@PIT</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>DAL -8.5</t>
+          <t>Under 41.5</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>-8.5</v>
+        <v>41.5</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -9910,13 +9948,13 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>5.4</v>
+        <v>48.7</v>
       </c>
       <c r="J147" t="n">
-        <v>-3.1</v>
+        <v>7.2</v>
       </c>
       <c r="K147" t="n">
-        <v>59.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
@@ -9929,7 +9967,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>2026_05_TB_DAL:spread:D</t>
+          <t>2026_05_IND_PIT:total:D</t>
         </is>
       </c>
     </row>
@@ -9939,21 +9977,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TB@DAL</t>
+          <t>LV@NE</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>NE -3.5</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>49.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -9967,17 +10005,17 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>53.1</v>
+        <v>13.9</v>
       </c>
       <c r="J148" t="n">
-        <v>3.6</v>
+        <v>10.4</v>
       </c>
       <c r="K148" t="n">
-        <v>63.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
@@ -9986,7 +10024,7 @@
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>2026_05_TB_DAL:total</t>
+          <t>2026_05_LV_NE:spread</t>
         </is>
       </c>
     </row>
@@ -9996,21 +10034,21 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TB@DAL</t>
+          <t>LV@NE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>NE -3.5</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>48.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -10024,28 +10062,1514 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I149" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="J149" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K149" t="n">
-        <v>66.2</v>
-      </c>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
+          <t>언더독 LV 드라이브 득점 차 우위 +1.33 → 반대 NE · 10-11 08:35 PT 판</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>2026_05_LV_NE:spread:A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>5</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>LV@NE</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NE -3.5</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>홈 NE 결장 확정 · 개장 -8.5 → 지금 -3.5(홈 기준, +5점 반대 이동) · 10-11 08:35 PT 판</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>2026_05_LV_NE:spread:A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>5</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>LV@NE</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LV +3.5</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K151" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
           <t>발행 방향</t>
         </is>
       </c>
-      <c r="Q149" t="inlineStr">
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>2026_05_LV_NE:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>5</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>LV@NE</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Under 45.5</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>42</v>
+      </c>
+      <c r="J152" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="K152" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>2026_05_LV_NE:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>5</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>LV@NE</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Under 45.5</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>42</v>
+      </c>
+      <c r="J153" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="K153" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>2026_05_LV_NE:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>5</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>MIN@NO</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NO +8.5</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-283</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>2026_05_MIN_NO:spread:T</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>5</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>MIN@NO</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NO +2.5</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>2026_05_MIN_NO:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>5</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>MIN@NO</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Under 41.5</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="J156" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="K156" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>2026_05_MIN_NO:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>5</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>MIN@NO</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Over 41.5</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="J157" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="K157" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>2026_05_MIN_NO:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>5</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>NYG@WAS</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NYG +3.5</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="J158" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K158" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>2026_05_NYG_WAS:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>5</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>NYG@WAS</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>WAS -3.5</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>언더독 NYG 드라이브 득점 차 우위 +0.77 → 반대 WAS · 10-11 08:35 PT 판</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>2026_05_NYG_WAS:spread:A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>5</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>NYG@WAS</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NYG +3.5</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="J160" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K160" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>2026_05_NYG_WAS:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>5</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>NYG@WAS</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Over 41.5</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="J161" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K161" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>2026_05_NYG_WAS:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>5</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>NYG@WAS</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Over 41.5</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="J162" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K162" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>2026_05_NYG_WAS:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>5</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>PHI@JAX</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>JAX -1.5</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-283</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>원 라인 -7.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>2026_05_PHI_JAX:spread:T</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>5</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>PHI@JAX</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>PHI +7.5</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>원정 PHI 결장 확정 · 개장 +2.5 → 지금 -7.5(홈 기준, +10점 반대 이동) · 10-10 04:23 PT 판</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>2026_05_PHI_JAX:spread:A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>5</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PHI@JAX</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>PHI +7.5</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>2026_05_PHI_JAX:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>5</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>PHI@JAX</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Over 41.5</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>2026_05_PHI_JAX:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>5</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SF@SEA</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>SF +3</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="J167" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K167" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>2026_05_SF_SEA:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>5</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>SF@SEA</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>SEA -3</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>언더독 SF 드라이브 득점 차 우위 +0.76 → 반대 SEA · 10-11 08:35 PT 판</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>2026_05_SF_SEA:spread:A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>5</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SF@SEA</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>SF +3</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>3</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="J169" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K169" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>2026_05_SF_SEA:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>5</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SF@SEA</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Over 45.5</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>2026_05_SF_SEA:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>5</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>TB +9.5</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J171" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="K171" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>2026_05_TB_DAL:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>5</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>DAL -2.5</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-283</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>원 라인 -8.5 · 총점 48.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>2026_05_TB_DAL:spread:T</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>5</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>DAL -8.5</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J173" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K173" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>2026_05_TB_DAL:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>5</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Over 49.5</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="J174" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K174" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>2026_05_TB_DAL:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>5</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Over 48.5</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="J175" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K175" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
         <is>
           <t>2026_05_TB_DAL:total:D</t>
         </is>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q175"/>
+  <dimension ref="A1:Q172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7817,11 +7817,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>BAL +3</t>
+          <t>BAL +3.5</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -7841,13 +7841,23 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>BAL 30-23 ATL</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>원정 BAL 결장 확정 · 개장 +4.5 → 지금 -3(홈 기준, +7.5점 반대 이동) · 10-11 08:35 PT 판</t>
+          <t>원정 BAL 결장 확정 · 개장 +4.5 → 지금 -3.5(홈 기준, +8점 반대 이동) · 10-11 15:46 PT 판</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -7872,11 +7882,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>BAL +3.5</t>
+          <t>ATL -3.5</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -7896,9 +7906,19 @@
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>BAL 30-23 ATL</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>-1</v>
+      </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -7927,7 +7947,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>Under 43.5</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -7951,9 +7971,19 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>BAL 30-23 ATL</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>-1</v>
+      </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -8114,17 +8144,27 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J115" t="n">
-        <v>3.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K115" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+        <v>77.40000000000001</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>CHI 7-31 GB</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr">
@@ -8173,9 +8213,19 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>CHI 7-31 GB</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>0.353</v>
+      </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -8228,9 +8278,19 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>CHI 7-31 GB</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -8289,9 +8349,19 @@
       <c r="K118" t="n">
         <v>61.9</v>
       </c>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>CHI 7-31 GB</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>-1</v>
+      </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -8344,9 +8414,19 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>CHI 7-31 GB</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>-1</v>
+      </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -8397,17 +8477,27 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>-1.7</v>
+        <v>-3</v>
       </c>
       <c r="J120" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="K120" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>CIN 31-24 MIA</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr">
@@ -8456,9 +8546,19 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>CIN 31-24 MIA</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -8517,9 +8617,19 @@
       <c r="K122" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>CIN 31-24 MIA</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -8570,17 +8680,27 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>52.8</v>
+        <v>53.4</v>
       </c>
       <c r="J123" t="n">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="K123" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+        <v>80.2</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>CIN 31-24 MIA</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr">
@@ -8635,9 +8755,19 @@
       <c r="K124" t="n">
         <v>78.5</v>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>CIN 31-24 MIA</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -8666,15 +8796,15 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>CLE +2.5</t>
+          <t>CLE +8.5</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>-2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -8684,26 +8814,34 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I125" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J125" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="K125" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>CLE 12-17 NYJ</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0.353</v>
+      </c>
       <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 39.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>2026_05_CLE_NYJ:spread</t>
+          <t>2026_05_CLE_NYJ:spread:T</t>
         </is>
       </c>
     </row>
@@ -8723,15 +8861,15 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>CLE +8.5</t>
+          <t>NYJ -2.5</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>8.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -8741,24 +8879,40 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="K126" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>CLE 12-17 NYJ</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>원 라인 +2.5 · 총점 39.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>2026_05_CLE_NYJ:spread:T</t>
+          <t>2026_05_CLE_NYJ:spread:D</t>
         </is>
       </c>
     </row>
@@ -8773,16 +8927,16 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NYJ -2.5</t>
+          <t>Under 38.5</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>-2.5</v>
+        <v>38.5</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -8796,30 +8950,36 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.4</v>
+        <v>29.4</v>
       </c>
       <c r="J127" t="n">
-        <v>-2.1</v>
+        <v>-9.1</v>
       </c>
       <c r="K127" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+        <v>80.7</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>CLE 12-17 NYJ</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>2026_05_CLE_NYJ:spread:D</t>
+          <t>2026_05_CLE_NYJ:total</t>
         </is>
       </c>
     </row>
@@ -8839,7 +8999,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -8857,7 +9017,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -8869,14 +9029,28 @@
       <c r="K128" t="n">
         <v>70</v>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>CLE 12-17 NYJ</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>-1</v>
+      </c>
       <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>2026_05_CLE_NYJ:total</t>
+          <t>2026_05_CLE_NYJ:total:D</t>
         </is>
       </c>
     </row>
@@ -8886,21 +9060,21 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CLE@NYJ</t>
+          <t>DEN@LAC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>DEN -3.5</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>38.5</v>
+        <v>3.5</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -8914,30 +9088,36 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>33</v>
+        <v>-6.6</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.5</v>
+        <v>-3.1</v>
       </c>
       <c r="K129" t="n">
-        <v>70</v>
-      </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
+        <v>59.3</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>DEN 23-17 LAC</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>2026_05_CLE_NYJ:total:D</t>
+          <t>2026_05_DEN_LAC:spread</t>
         </is>
       </c>
     </row>
@@ -8957,7 +9137,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>DEN -3.5</t>
+          <t>LAC +3.5</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -8975,26 +9155,34 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I130" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="J130" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="K130" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>DEN 23-17 LAC</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>-1</v>
+      </c>
       <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>홈 LAC 결장 확정 · 개장 -2.5 → 지금 +3.5(홈 기준, +6점 반대 이동) · 10-11 12:01 PT 판</t>
+        </is>
+      </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>2026_05_DEN_LAC:spread</t>
+          <t>2026_05_DEN_LAC:spread:A3</t>
         </is>
       </c>
     </row>
@@ -9032,24 +9220,40 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="J131" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K131" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>DEN 23-17 LAC</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>-1</v>
+      </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>홈 LAC 결장 확정 · 개장 -2.5 → 지금 +3.5(홈 기준, +6점 반대 이동) · 10-11 08:35 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>2026_05_DEN_LAC:spread:A3</t>
+          <t>2026_05_DEN_LAC:spread:D</t>
         </is>
       </c>
     </row>
@@ -9064,16 +9268,16 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LAC +3.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3.5</v>
+        <v>42.5</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -9087,30 +9291,36 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>-6.6</v>
+        <v>35.5</v>
       </c>
       <c r="J132" t="n">
-        <v>-3.1</v>
+        <v>-7</v>
       </c>
       <c r="K132" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+        <v>74.7</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>DEN 23-17 LAC</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>2026_05_DEN_LAC:spread:D</t>
+          <t>2026_05_DEN_LAC:total</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9340,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Under 41.5</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -9148,7 +9358,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -9160,14 +9370,28 @@
       <c r="K133" t="n">
         <v>72.2</v>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>DEN 23-17 LAC</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>-1</v>
+      </c>
       <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>2026_05_DEN_LAC:total</t>
+          <t>2026_05_DEN_LAC:total:D</t>
         </is>
       </c>
     </row>
@@ -9177,21 +9401,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DEN@LAC</t>
+          <t>DET@ARI</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>DET -5.5</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>41.5</v>
+        <v>-5.5</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -9205,30 +9429,34 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I134" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="J134" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="K134" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>DET 45-21 ARI</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>원정 DET 결장 확정 · 개장 +8.5 → 지금 +5.5(홈 기준, +3점 반대 이동) · 10-11 12:01 PT 판</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>2026_05_DEN_LAC:total:D</t>
+          <t>2026_05_DET_ARI:spread:A3</t>
         </is>
       </c>
     </row>
@@ -9248,11 +9476,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>DET -5.5</t>
+          <t>ARI +5.5</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>-5.5</v>
+        <v>5.5</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -9266,24 +9494,34 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>DET 45-21 ARI</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>-1</v>
+      </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>원정 DET 결장 확정 · 개장 +8.5 → 지금 +5.5(홈 기준, +3점 반대 이동) · 10-11 08:35 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>2026_05_DET_ARI:spread:A3</t>
+          <t>2026_05_DET_ARI:spread:D</t>
         </is>
       </c>
     </row>
@@ -9298,16 +9536,16 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ARI +5.5</t>
+          <t>Over 54.5</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5.5</v>
+        <v>54.5</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -9327,9 +9565,19 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>DET 45-21 ARI</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -9338,7 +9586,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>2026_05_DET_ARI:spread:D</t>
+          <t>2026_05_DET_ARI:total:D</t>
         </is>
       </c>
     </row>
@@ -9348,21 +9596,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DET@ARI</t>
+          <t>HOU@TEN</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Over 54.5</t>
+          <t>HOU -6.5</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>54.5</v>
+        <v>6.5</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -9376,24 +9624,36 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J137" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="K137" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>HOU 26-3 TEN</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>2026_05_DET_ARI:total:D</t>
+          <t>2026_05_HOU_TEN:spread</t>
         </is>
       </c>
     </row>
@@ -9413,15 +9673,15 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>HOU -6.5</t>
+          <t>HOU -1.5</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6.5</v>
+        <v>-1.5</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -9431,26 +9691,34 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I138" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="J138" t="n">
-        <v>-6</v>
-      </c>
-      <c r="K138" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>HOU 26-3 TEN</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>0.353</v>
+      </c>
       <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>원 라인 -7.5 · 총점 37.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:spread</t>
+          <t>2026_05_HOU_TEN:spread:T</t>
         </is>
       </c>
     </row>
@@ -9470,15 +9738,15 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>HOU -1.5</t>
+          <t>TEN +6.5</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>-1.5</v>
+        <v>6.5</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -9488,24 +9756,34 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>HOU 26-3 TEN</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>-1</v>
+      </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>원 라인 -7.5 · 총점 37.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>홈 TEN 결장 확정 · 개장 +3.5 → 지금 +6.5(홈 기준, +3점 반대 이동) · 10-11 08:35 PT 판</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:spread:T</t>
+          <t>2026_05_HOU_TEN:spread:A3</t>
         </is>
       </c>
     </row>
@@ -9525,11 +9803,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>TEN +6.5</t>
+          <t>HOU -6.5</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6.5</v>
+        <v>-6.5</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -9543,24 +9821,40 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="J140" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K140" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>HOU 26-3 TEN</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>홈 TEN 결장 확정 · 개장 +3.5 → 지금 +6.5(홈 기준, +3점 반대 이동) · 10-11 08:35 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:spread:A3</t>
+          <t>2026_05_HOU_TEN:spread:D</t>
         </is>
       </c>
     </row>
@@ -9575,16 +9869,16 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>HOU -6.5</t>
+          <t>Under 37.5</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>-6.5</v>
+        <v>37.5</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -9601,18 +9895,22 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I141" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="J141" t="n">
-        <v>-6</v>
-      </c>
-      <c r="K141" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>HOU 26-3 TEN</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -9621,7 +9919,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:spread:D</t>
+          <t>2026_05_HOU_TEN:total:D</t>
         </is>
       </c>
     </row>
@@ -9631,25 +9929,25 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>HOU@TEN</t>
+          <t>IND@PIT</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Under 37.5</t>
+          <t>IND +8.5</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>37.5</v>
+        <v>8.5</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -9659,24 +9957,34 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>티저 다리(관찰)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>IND 22-34 PIT</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>-1</v>
+      </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>원 라인 +2.5 · 총점 44.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:total:D</t>
+          <t>2026_05_IND_PIT:spread:T</t>
         </is>
       </c>
     </row>
@@ -9700,7 +10008,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -9714,7 +10022,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I143" t="n">
@@ -9726,14 +10034,28 @@
       <c r="K143" t="n">
         <v>60.2</v>
       </c>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>IND 22-34 PIT</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>-1</v>
+      </c>
       <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>2026_05_IND_PIT:spread</t>
+          <t>2026_05_IND_PIT:spread:D</t>
         </is>
       </c>
     </row>
@@ -9748,20 +10070,20 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>IND +8.5</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>8.5</v>
+        <v>41.5</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -9771,24 +10093,36 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="J144" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="K144" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>IND 22-34 PIT</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr">
-        <is>
-          <t>원 라인 +2.5 · 총점 44.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
-        </is>
-      </c>
+      <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>2026_05_IND_PIT:spread:T</t>
+          <t>2026_05_IND_PIT:total</t>
         </is>
       </c>
     </row>
@@ -9803,16 +10137,16 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>IND +3</t>
+          <t>Under 41.5</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3</v>
+        <v>41.5</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -9830,17 +10164,27 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>-0.4</v>
+        <v>48.7</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.4</v>
+        <v>7.2</v>
       </c>
       <c r="K145" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+        <v>75.40000000000001</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>IND 22-34 PIT</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>-1</v>
+      </c>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -9849,7 +10193,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>2026_05_IND_PIT:spread:D</t>
+          <t>2026_05_IND_PIT:total:D</t>
         </is>
       </c>
     </row>
@@ -9859,21 +10203,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>IND@PIT</t>
+          <t>LV@NE</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>NE -3.5</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>41.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -9891,22 +10235,32 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>48.7</v>
+        <v>17.1</v>
       </c>
       <c r="J146" t="n">
-        <v>7.2</v>
+        <v>13.6</v>
       </c>
       <c r="K146" t="n">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+        <v>85.2</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>LV 17-45 NE</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>2026_05_IND_PIT:total</t>
+          <t>2026_05_LV_NE:spread</t>
         </is>
       </c>
     </row>
@@ -9916,21 +10270,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>IND@PIT</t>
+          <t>LV@NE</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Under 41.5</t>
+          <t>NE -3.5</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>41.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -9944,30 +10298,34 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I147" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="J147" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K147" t="n">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>LV 17-45 NE</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>언더독 LV 드라이브 득점 차 우위 +1.33 → 반대 NE · 10-11 08:35 PT 판</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>2026_05_IND_PIT:total:D</t>
+          <t>2026_05_LV_NE:spread:A2</t>
         </is>
       </c>
     </row>
@@ -10005,26 +10363,34 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I148" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="J148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="K148" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>LV 17-45 NE</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>홈 NE 결장 확정 · 개장 -8.5 → 지금 -3.5(홈 기준, +5점 반대 이동) · 10-11 08:35 PT 판</t>
+        </is>
+      </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:spread</t>
+          <t>2026_05_LV_NE:spread:A3</t>
         </is>
       </c>
     </row>
@@ -10044,11 +10410,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NE -3.5</t>
+          <t>LV +3.5</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>-3.5</v>
+        <v>3.5</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -10062,24 +10428,40 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K149" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>LV 17-45 NE</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>-1</v>
+      </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>언더독 LV 드라이브 득점 차 우위 +1.33 → 반대 NE · 10-11 08:35 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:spread:A2</t>
+          <t>2026_05_LV_NE:spread:D</t>
         </is>
       </c>
     </row>
@@ -10094,47 +10476,63 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NE -3.5</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E150" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>42</v>
+      </c>
+      <c r="J150" t="n">
         <v>-3.5</v>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>-110</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+      <c r="K150" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>LV 17-45 NE</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>-1</v>
+      </c>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>홈 NE 결장 확정 · 개장 -8.5 → 지금 -3.5(홈 기준, +5점 반대 이동) · 10-11 08:35 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:spread:A3</t>
+          <t>2026_05_LV_NE:total:D</t>
         </is>
       </c>
     </row>
@@ -10144,7 +10542,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>LV@NE</t>
+          <t>MIN@NO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10154,15 +10552,15 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LV +3.5</t>
+          <t>NO +8.5</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -10172,30 +10570,34 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I151" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="J151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="K151" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>MIN 23-13 NO</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>-1</v>
+      </c>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>원 라인 +2.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:spread:D</t>
+          <t>2026_05_MIN_NO:spread:T</t>
         </is>
       </c>
     </row>
@@ -10205,21 +10607,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>LV@NE</t>
+          <t>MIN@NO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>NO +2.5</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>45.5</v>
+        <v>2.5</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -10233,26 +10635,34 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I152" t="n">
-        <v>42</v>
-      </c>
-      <c r="J152" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="K152" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>MIN 23-13 NO</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>-1</v>
+      </c>
       <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:total</t>
+          <t>2026_05_MIN_NO:spread:D</t>
         </is>
       </c>
     </row>
@@ -10262,7 +10672,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>LV@NE</t>
+          <t>MIN@NO</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10272,11 +10682,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>Under 41.5</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>45.5</v>
+        <v>41.5</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -10290,30 +10700,36 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>42</v>
+        <v>30.1</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.5</v>
+        <v>-11.4</v>
       </c>
       <c r="K153" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
+        <v>86.2</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>MIN 23-13 NO</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:total:D</t>
+          <t>2026_05_MIN_NO:total</t>
         </is>
       </c>
     </row>
@@ -10328,20 +10744,20 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NO +8.5</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>8.5</v>
+        <v>41.5</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -10351,24 +10767,40 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="J154" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="K154" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>MIN 23-13 NO</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>-1</v>
+      </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>원 라인 +2.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>2026_05_MIN_NO:spread:T</t>
+          <t>2026_05_MIN_NO:total:D</t>
         </is>
       </c>
     </row>
@@ -10378,7 +10810,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MIN@NO</t>
+          <t>NYG@WAS</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10388,11 +10820,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NO +2.5</t>
+          <t>NYG +3.5</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -10406,24 +10838,36 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J155" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="K155" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>NYG 27-27 WAS</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
+      <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>2026_05_MIN_NO:spread:D</t>
+          <t>2026_05_NYG_WAS:spread</t>
         </is>
       </c>
     </row>
@@ -10433,21 +10877,21 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MIN@NO</t>
+          <t>NYG@WAS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Under 41.5</t>
+          <t>WAS -3.5</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>41.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -10461,26 +10905,34 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I156" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="J156" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="K156" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>NYG 27-27 WAS</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>-1</v>
+      </c>
       <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>언더독 NYG 드라이브 득점 차 우위 +0.77 → 반대 WAS · 10-11 08:35 PT 판</t>
+        </is>
+      </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>2026_05_MIN_NO:total</t>
+          <t>2026_05_NYG_WAS:spread:A2</t>
         </is>
       </c>
     </row>
@@ -10490,21 +10942,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MIN@NO</t>
+          <t>NYG@WAS</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>NYG +3.5</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>41.5</v>
+        <v>3.5</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -10522,17 +10974,27 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>32.2</v>
+        <v>-5.5</v>
       </c>
       <c r="J157" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9</v>
       </c>
       <c r="K157" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+        <v>75.5</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>NYG 27-27 WAS</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -10541,7 +11003,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>2026_05_MIN_NO:total:D</t>
+          <t>2026_05_NYG_WAS:spread:D</t>
         </is>
       </c>
     </row>
@@ -10556,16 +11018,16 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NYG +3.5</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>-3.5</v>
+        <v>41.5</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -10583,22 +11045,32 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>-5.5</v>
+        <v>49.6</v>
       </c>
       <c r="J158" t="n">
-        <v>-9</v>
+        <v>8.1</v>
       </c>
       <c r="K158" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>NYG 27-27 WAS</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>2026_05_NYG_WAS:spread</t>
+          <t>2026_05_NYG_WAS:total</t>
         </is>
       </c>
     </row>
@@ -10613,16 +11085,16 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>WAS -3.5</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>-3.5</v>
+        <v>41.5</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -10636,24 +11108,40 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="J159" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K159" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>NYG 27-27 WAS</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>언더독 NYG 드라이브 득점 차 우위 +0.77 → 반대 WAS · 10-11 08:35 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>2026_05_NYG_WAS:spread:A2</t>
+          <t>2026_05_NYG_WAS:total:D</t>
         </is>
       </c>
     </row>
@@ -10663,7 +11151,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NYG@WAS</t>
+          <t>PHI@JAX</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10673,15 +11161,15 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NYG +3.5</t>
+          <t>JAX -1.5</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3.5</v>
+        <v>-1.5</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -10691,30 +11179,34 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I160" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="J160" t="n">
-        <v>-9</v>
-      </c>
-      <c r="K160" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>PHI 17-19 JAX</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>0.353</v>
+      </c>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>원 라인 -7.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>2026_05_NYG_WAS:spread:D</t>
+          <t>2026_05_PHI_JAX:spread:T</t>
         </is>
       </c>
     </row>
@@ -10724,21 +11216,21 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NYG@WAS</t>
+          <t>PHI@JAX</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>PHI +7.5</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>41.5</v>
+        <v>7.5</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -10752,26 +11244,34 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I161" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="J161" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K161" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>PHI 17-19 JAX</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>원정 PHI 결장 확정 · 개장 +2.5 → 지금 -7.5(홈 기준, +10점 반대 이동) · 10-10 04:23 PT 판</t>
+        </is>
+      </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>2026_05_NYG_WAS:total</t>
+          <t>2026_05_PHI_JAX:spread:A3</t>
         </is>
       </c>
     </row>
@@ -10781,21 +11281,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NYG@WAS</t>
+          <t>PHI@JAX</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>PHI +7.5</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>41.5</v>
+        <v>7.5</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -10812,18 +11312,22 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I162" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="J162" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K162" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>PHI 17-19 JAX</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
@@ -10832,7 +11336,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>2026_05_NYG_WAS:total:D</t>
+          <t>2026_05_PHI_JAX:spread:D</t>
         </is>
       </c>
     </row>
@@ -10847,20 +11351,20 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>JAX -1.5</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>-1.5</v>
+        <v>41.5</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -10870,24 +11374,34 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>PHI 17-19 JAX</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>-1</v>
+      </c>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>원 라인 -7.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>2026_05_PHI_JAX:spread:T</t>
+          <t>2026_05_PHI_JAX:total:D</t>
         </is>
       </c>
     </row>
@@ -10897,7 +11411,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PHI@JAX</t>
+          <t>SF@SEA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10907,11 +11421,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>PHI +7.5</t>
+          <t>SEA -3</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>7.5</v>
+        <v>-3</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -10925,24 +11439,34 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>SF 32-29 SEA</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>-1</v>
+      </c>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>원정 PHI 결장 확정 · 개장 +2.5 → 지금 -7.5(홈 기준, +10점 반대 이동) · 10-10 04:23 PT 판</t>
+          <t>언더독 SF 드라이브 득점 차 우위 +0.76 → 반대 SEA · 10-11 12:01 PT 판</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>2026_05_PHI_JAX:spread:A3</t>
+          <t>2026_05_SF_SEA:spread:A2</t>
         </is>
       </c>
     </row>
@@ -10952,7 +11476,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PHI@JAX</t>
+          <t>SF@SEA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10962,11 +11486,11 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>PHI +7.5</t>
+          <t>SF +3</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -10983,12 +11507,28 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+      <c r="I165" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="J165" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K165" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>SF 32-29 SEA</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
@@ -10997,7 +11537,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>2026_05_PHI_JAX:spread:D</t>
+          <t>2026_05_SF_SEA:spread:D</t>
         </is>
       </c>
     </row>
@@ -11007,7 +11547,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PHI@JAX</t>
+          <t>SF@SEA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -11017,11 +11557,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>41.5</v>
+        <v>46.5</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -11041,9 +11581,19 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>SF 32-29 SEA</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
@@ -11052,7 +11602,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>2026_05_PHI_JAX:total:D</t>
+          <t>2026_05_SF_SEA:total:D</t>
         </is>
       </c>
     </row>
@@ -11067,16 +11617,16 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SF +3</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>-3</v>
+        <v>46.5</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -11094,22 +11644,32 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>-0.1</v>
+        <v>51.4</v>
       </c>
       <c r="J167" t="n">
-        <v>-3.1</v>
+        <v>4.9</v>
       </c>
       <c r="K167" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+        <v>68.09999999999999</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>SF 32-29 SEA</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>2026_05_SF_SEA:spread</t>
+          <t>2026_05_SF_SEA:total</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11679,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SF@SEA</t>
+          <t>TB@DAL</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -11129,11 +11689,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>SEA -3</t>
+          <t>TB +9.5</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>-3</v>
+        <v>-9.5</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -11147,24 +11707,36 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J168" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="K168" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>TB 24-16 DAL</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr">
-        <is>
-          <t>언더독 SF 드라이브 득점 차 우위 +0.76 → 반대 SEA · 10-11 08:35 PT 판</t>
-        </is>
-      </c>
+      <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>2026_05_SF_SEA:spread:A2</t>
+          <t>2026_05_TB_DAL:spread</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11746,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SF@SEA</t>
+          <t>TB@DAL</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -11184,15 +11756,15 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>SF +3</t>
+          <t>DAL -2.5</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3</v>
+        <v>-2.5</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -11202,30 +11774,34 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I169" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="J169" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="K169" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>TB 24-16 DAL</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>-1</v>
+      </c>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>원 라인 -8.5 · 총점 48.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>2026_05_SF_SEA:spread:D</t>
+          <t>2026_05_TB_DAL:spread:T</t>
         </is>
       </c>
     </row>
@@ -11235,21 +11811,21 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SF@SEA</t>
+          <t>TB@DAL</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>DAL -8.5</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>45.5</v>
+        <v>-8.5</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -11266,12 +11842,28 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
+      <c r="I170" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J170" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K170" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>TB 24-16 DAL</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>-1</v>
+      </c>
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
@@ -11280,7 +11872,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>2026_05_SF_SEA:total:D</t>
+          <t>2026_05_TB_DAL:spread:D</t>
         </is>
       </c>
     </row>
@@ -11295,16 +11887,16 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>TB +9.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>-9.5</v>
+        <v>49.5</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -11318,26 +11910,36 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.6</v>
+        <v>53.3</v>
       </c>
       <c r="J171" t="n">
-        <v>-5.9</v>
+        <v>3.8</v>
       </c>
       <c r="K171" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
+        <v>64.2</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>TB 24-16 DAL</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>-1</v>
+      </c>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>2026_05_TB_DAL:spread</t>
+          <t>2026_05_TB_DAL:total</t>
         </is>
       </c>
     </row>
@@ -11352,20 +11954,20 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>DAL -2.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>-2.5</v>
+        <v>48.5</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -11375,201 +11977,38 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="J172" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K172" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>TB 24-16 DAL</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>-1</v>
+      </c>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>원 라인 -8.5 · 총점 48.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
-        <is>
-          <t>2026_05_TB_DAL:spread:T</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>5</v>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>TB@DAL</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>DAL -8.5</t>
-        </is>
-      </c>
-      <c r="E173" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>-110</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I173" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J173" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="K173" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>2026_05_TB_DAL:spread:D</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>5</v>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>TB@DAL</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Over 49.5</t>
-        </is>
-      </c>
-      <c r="E174" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>-110</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I174" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="J174" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K174" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>2026_05_TB_DAL:total</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>5</v>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>TB@DAL</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Over 48.5</t>
-        </is>
-      </c>
-      <c r="E175" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>-110</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I175" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="J175" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K175" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr">
-        <is>
-          <t>발행 방향</t>
-        </is>
-      </c>
-      <c r="Q175" t="inlineStr">
         <is>
           <t>2026_05_TB_DAL:total:D</t>
         </is>
@@ -11699,19 +12138,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.18</v>
+        <v>-11.09</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -11726,22 +12165,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>54.5</v>
+        <v>63.8</v>
       </c>
       <c r="G5" t="n">
-        <v>1.82</v>
+        <v>12.63</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -11756,22 +12195,22 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
         <v>3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>1.08</v>
+        <v>-0.51</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -11903,7 +12342,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -11912,7 +12351,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -11930,22 +12369,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>-2</v>
+        <v>-3.09</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -11960,19 +12399,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
+      <c r="F13" t="n">
+        <v>71.40000000000001</v>
+      </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -12038,19 +12480,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -12241,22 +12683,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>50</v>
+        <v>50.8</v>
       </c>
       <c r="G28" t="n">
-        <v>-7.44</v>
+        <v>-9.94</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -12267,22 +12709,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>44.4</v>
+        <v>46.7</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.36</v>
+        <v>-1.64</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -12293,22 +12735,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>47.6</v>
+        <v>42.3</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.91</v>
+        <v>-5</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -12319,22 +12761,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C31" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>54.3</v>
+        <v>61.8</v>
       </c>
       <c r="G31" t="n">
-        <v>1.27</v>
+        <v>9.91</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -12349,7 +12791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12565,6 +13007,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q172"/>
+  <dimension ref="A1:Q194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BUF@LA</t>
+          <t>CHI@GB</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8012,15 +8012,15 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LA -3</t>
+          <t>GB +8.5</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>-3</v>
+        <v>8.5</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8030,24 +8030,34 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>티저 다리(관찰)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>CHI 7-31 GB</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>0.353</v>
+      </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>원 라인 +2.5 · 총점 45.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>2026_05_BUF_LA:spread:D</t>
+          <t>2026_05_CHI_GB:spread:T</t>
         </is>
       </c>
     </row>
@@ -8057,21 +8067,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BUF@LA</t>
+          <t>CHI@GB</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Over 54.5</t>
+          <t>GB +1.5</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>54.5</v>
+        <v>1.5</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -8085,24 +8095,34 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>CHI 7-31 GB</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>홈 GB 결장 확정 · 개장 -3 → 지금 +1.5(홈 기준, +4.5점 반대 이동) · 10-11 08:35 PT 판</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>2026_05_BUF_LA:total:D</t>
+          <t>2026_05_CHI_GB:spread:A3</t>
         </is>
       </c>
     </row>
@@ -8122,11 +8142,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>GB +1.5</t>
+          <t>CHI -1.5</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -8140,21 +8160,21 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>8.300000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="J115" t="n">
-        <v>9.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="K115" t="n">
-        <v>77.40000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -8163,13 +8183,17 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>2026_05_CHI_GB:spread</t>
+          <t>2026_05_CHI_GB:spread:D</t>
         </is>
       </c>
     </row>
@@ -8189,15 +8213,15 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>GB +8.5</t>
+          <t>GB +1.5</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8207,11 +8231,15 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J116" t="n">
+        <v>3.9</v>
+      </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
@@ -8224,17 +8252,17 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0.353</v>
+        <v>0.909</v>
       </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>원 라인 +2.5 · 총점 45.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>킥오프 전 판 1011-0833 서열표로 재생성(10/11 누수 복구)</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>2026_05_CHI_GB:spread:T</t>
+          <t>2026_05_CHI_GB:spread</t>
         </is>
       </c>
     </row>
@@ -8249,16 +8277,16 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>GB +1.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1.5</v>
+        <v>47.5</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -8272,7 +8300,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -8280,7 +8308,7 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -8289,17 +8317,17 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>홈 GB 결장 확정 · 개장 -3 → 지금 +1.5(홈 기준, +4.5점 반대 이동) · 10-11 08:35 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>2026_05_CHI_GB:spread:A3</t>
+          <t>2026_05_CHI_GB:total:D</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8337,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CHI@GB</t>
+          <t>CIN@MIA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8319,11 +8347,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>CHI -1.5</t>
+          <t>MIA +7</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>-1.5</v>
+        <v>7</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -8337,40 +8365,34 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I118" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J118" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K118" t="n">
-        <v>61.9</v>
-      </c>
+          <t>각도 관찰 A1(원정 큰 페이버릿 반대)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>CHI 7-31 GB</t>
+          <t>CIN 31-24 MIA</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>원정 CIN -7 페이버릿 · 10-11 08:35 PT 판</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>2026_05_CHI_GB:spread:D</t>
+          <t>2026_05_CIN_MIA:spread:A1</t>
         </is>
       </c>
     </row>
@@ -8380,21 +8402,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CHI@GB</t>
+          <t>CIN@MIA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>MIA +7</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>47.5</v>
+        <v>7</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -8411,21 +8433,27 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
+      <c r="I119" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="J119" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K119" t="n">
+        <v>65.90000000000001</v>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>CHI 7-31 GB</t>
+          <t>CIN 31-24 MIA</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
@@ -8435,7 +8463,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>2026_05_CHI_GB:total:D</t>
+          <t>2026_05_CIN_MIA:spread:D</t>
         </is>
       </c>
     </row>
@@ -8477,14 +8505,12 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>-3</v>
+        <v>-1.7</v>
       </c>
       <c r="J120" t="n">
-        <v>4</v>
-      </c>
-      <c r="K120" t="n">
-        <v>62</v>
-      </c>
+        <v>5.3</v>
+      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>P</t>
@@ -8499,7 +8525,11 @@
         <v>0</v>
       </c>
       <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>킥오프 전 판 1011-0833 서열표로 재생성(10/11 누수 복구)</t>
+        </is>
+      </c>
       <c r="Q120" t="inlineStr">
         <is>
           <t>2026_05_CIN_MIA:spread</t>
@@ -8517,16 +8547,16 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>MIA +7</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>7</v>
+        <v>44.5</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -8540,15 +8570,21 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>각도 관찰 A1(원정 큰 페이버릿 반대)</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="J121" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K121" t="n">
+        <v>78.5</v>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -8557,17 +8593,17 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>0.909</v>
       </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>원정 CIN -7 페이버릿 · 10-11 08:35 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>2026_05_CIN_MIA:spread:A1</t>
+          <t>2026_05_CIN_MIA:total:D</t>
         </is>
       </c>
     </row>
@@ -8582,16 +8618,16 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>MIA +7</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>7</v>
+        <v>44.5</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -8605,21 +8641,19 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>-1.7</v>
+        <v>52.8</v>
       </c>
       <c r="J122" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K122" t="n">
-        <v>65.90000000000001</v>
-      </c>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -8628,17 +8662,17 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>0.909</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>킥오프 전 판 1011-0833 서열표로 재생성(10/11 누수 복구)</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>2026_05_CIN_MIA:spread:D</t>
+          <t>2026_05_CIN_MIA:total</t>
         </is>
       </c>
     </row>
@@ -8648,25 +8682,25 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CIN@MIA</t>
+          <t>CLE@NYJ</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>CLE +8.5</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>44.5</v>
+        <v>8.5</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -8676,18 +8710,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I123" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="J123" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="K123" t="n">
-        <v>80.2</v>
-      </c>
+          <t>티저 다리(관찰)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
           <t>W</t>
@@ -8695,17 +8723,21 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>CIN 31-24 MIA</t>
+          <t>CLE 12-17 NYJ</t>
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0.909</v>
+        <v>0.353</v>
       </c>
       <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>원 라인 +2.5 · 총점 39.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+        </is>
+      </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>2026_05_CIN_MIA:total</t>
+          <t>2026_05_CLE_NYJ:spread:T</t>
         </is>
       </c>
     </row>
@@ -8715,21 +8747,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CIN@MIA</t>
+          <t>CLE@NYJ</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>NYJ -2.5</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>44.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -8747,13 +8779,13 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>52.8</v>
+        <v>0.4</v>
       </c>
       <c r="J124" t="n">
-        <v>8.300000000000001</v>
+        <v>-2.1</v>
       </c>
       <c r="K124" t="n">
-        <v>78.5</v>
+        <v>56.4</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -8762,7 +8794,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>CIN 31-24 MIA</t>
+          <t>CLE 12-17 NYJ</t>
         </is>
       </c>
       <c r="N124" t="n">
@@ -8776,7 +8808,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>2026_05_CIN_MIA:total:D</t>
+          <t>2026_05_CLE_NYJ:spread:D</t>
         </is>
       </c>
     </row>
@@ -8796,15 +8828,15 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>CLE +8.5</t>
+          <t>CLE +2.5</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>8.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -8814,15 +8846,19 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J125" t="n">
+        <v>-2.1</v>
+      </c>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -8831,17 +8867,17 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>0.353</v>
+        <v>-1</v>
       </c>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>원 라인 +2.5 · 총점 39.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>킥오프 전 판 1011-0833 서열표로 재생성(10/11 누수 복구)</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>2026_05_CLE_NYJ:spread:T</t>
+          <t>2026_05_CLE_NYJ:spread</t>
         </is>
       </c>
     </row>
@@ -8856,16 +8892,16 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NYJ -2.5</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>-2.5</v>
+        <v>38.5</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -8883,17 +8919,17 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.4</v>
+        <v>33</v>
       </c>
       <c r="J126" t="n">
-        <v>-2.1</v>
+        <v>-5.5</v>
       </c>
       <c r="K126" t="n">
-        <v>56.4</v>
+        <v>70</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -8902,7 +8938,7 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
@@ -8912,7 +8948,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>2026_05_CLE_NYJ:spread:D</t>
+          <t>2026_05_CLE_NYJ:total:D</t>
         </is>
       </c>
     </row>
@@ -8954,14 +8990,12 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>29.4</v>
+        <v>33</v>
       </c>
       <c r="J127" t="n">
-        <v>-9.1</v>
-      </c>
-      <c r="K127" t="n">
-        <v>80.7</v>
-      </c>
+        <v>-5.5</v>
+      </c>
+      <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
           <t>W</t>
@@ -8976,7 +9010,11 @@
         <v>0.909</v>
       </c>
       <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>킥오프 전 판 1011-0833 서열표로 재생성(10/11 누수 복구)</t>
+        </is>
+      </c>
       <c r="Q127" t="inlineStr">
         <is>
           <t>2026_05_CLE_NYJ:total</t>
@@ -8989,21 +9027,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CLE@NYJ</t>
+          <t>DEN@LAC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>LAC +3.5</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>38.5</v>
+        <v>3.5</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -9017,18 +9055,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I128" t="n">
-        <v>33</v>
-      </c>
-      <c r="J128" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="K128" t="n">
-        <v>70</v>
-      </c>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
           <t>L</t>
@@ -9036,7 +9068,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>CLE 12-17 NYJ</t>
+          <t>DEN 23-17 LAC</t>
         </is>
       </c>
       <c r="N128" t="n">
@@ -9045,12 +9077,12 @@
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>홈 LAC 결장 확정 · 개장 -2.5 → 지금 +3.5(홈 기준, +6점 반대 이동) · 10-11 12:01 PT 판</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>2026_05_CLE_NYJ:total:D</t>
+          <t>2026_05_DEN_LAC:spread:A3</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9102,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>DEN -3.5</t>
+          <t>LAC +3.5</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -9088,7 +9120,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -9102,7 +9134,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -9111,13 +9143,17 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>2026_05_DEN_LAC:spread</t>
+          <t>2026_05_DEN_LAC:spread:D</t>
         </is>
       </c>
     </row>
@@ -9137,7 +9173,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LAC +3.5</t>
+          <t>DEN -3.5</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -9155,15 +9191,19 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-3.1</v>
+      </c>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -9172,17 +9212,17 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>홈 LAC 결장 확정 · 개장 -2.5 → 지금 +3.5(홈 기준, +6점 반대 이동) · 10-11 12:01 PT 판</t>
+          <t>킥오프 전 판 1011-1159 서열표로 재생성(10/11 누수 복구)</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>2026_05_DEN_LAC:spread:A3</t>
+          <t>2026_05_DEN_LAC:spread</t>
         </is>
       </c>
     </row>
@@ -9197,16 +9237,16 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LAC +3.5</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3.5</v>
+        <v>41.5</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -9224,13 +9264,13 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>-6.6</v>
+        <v>35.3</v>
       </c>
       <c r="J131" t="n">
-        <v>-3.1</v>
+        <v>-6.2</v>
       </c>
       <c r="K131" t="n">
-        <v>59.3</v>
+        <v>72.2</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -9253,7 +9293,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>2026_05_DEN_LAC:spread:D</t>
+          <t>2026_05_DEN_LAC:total:D</t>
         </is>
       </c>
     </row>
@@ -9295,14 +9335,12 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="J132" t="n">
-        <v>-7</v>
-      </c>
-      <c r="K132" t="n">
-        <v>74.7</v>
-      </c>
+        <v>-7.3</v>
+      </c>
+      <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
           <t>W</t>
@@ -9317,7 +9355,11 @@
         <v>0.909</v>
       </c>
       <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>킥오프 전 판 1011-1159 서열표로 재생성(10/11 누수 복구)</t>
+        </is>
+      </c>
       <c r="Q132" t="inlineStr">
         <is>
           <t>2026_05_DEN_LAC:total</t>
@@ -9330,21 +9372,21 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DEN@LAC</t>
+          <t>DET@ARI</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>DET -5.5</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>41.5</v>
+        <v>-5.5</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -9358,40 +9400,34 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I133" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="J133" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="K133" t="n">
-        <v>72.2</v>
-      </c>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>DEN 23-17 LAC</t>
+          <t>DET 45-21 ARI</t>
         </is>
       </c>
       <c r="N133" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>원정 DET 결장 확정 · 개장 +8.5 → 지금 +5.5(홈 기준, +3점 반대 이동) · 10-11 12:01 PT 판</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>2026_05_DEN_LAC:total:D</t>
+          <t>2026_05_DET_ARI:spread:A3</t>
         </is>
       </c>
     </row>
@@ -9411,11 +9447,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DET -5.5</t>
+          <t>ARI +5.5</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>-5.5</v>
+        <v>5.5</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -9429,7 +9465,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -9437,7 +9473,7 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -9446,17 +9482,17 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>원정 DET 결장 확정 · 개장 +8.5 → 지금 +5.5(홈 기준, +3점 반대 이동) · 10-11 12:01 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>2026_05_DET_ARI:spread:A3</t>
+          <t>2026_05_DET_ARI:spread:D</t>
         </is>
       </c>
     </row>
@@ -9471,16 +9507,16 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ARI +5.5</t>
+          <t>Over 54.5</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5.5</v>
+        <v>54.5</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -9502,7 +9538,7 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -9511,7 +9547,7 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -9521,7 +9557,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>2026_05_DET_ARI:spread:D</t>
+          <t>2026_05_DET_ARI:total:D</t>
         </is>
       </c>
     </row>
@@ -9531,25 +9567,25 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DET@ARI</t>
+          <t>HOU@TEN</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Over 54.5</t>
+          <t>HOU -1.5</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>54.5</v>
+        <v>-1.5</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -9559,7 +9595,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>티저 다리(관찰)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -9572,21 +9608,21 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>DET 45-21 ARI</t>
+          <t>HOU 26-3 TEN</t>
         </is>
       </c>
       <c r="N136" t="n">
-        <v>0.909</v>
+        <v>0.353</v>
       </c>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>원 라인 -7.5 · 총점 37.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>2026_05_DET_ARI:total:D</t>
+          <t>2026_05_HOU_TEN:spread:T</t>
         </is>
       </c>
     </row>
@@ -9606,7 +9642,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>HOU -6.5</t>
+          <t>TEN +6.5</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -9624,21 +9660,15 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I137" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J137" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="K137" t="n">
-        <v>76.7</v>
-      </c>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -9647,13 +9677,17 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>홈 TEN 결장 확정 · 개장 +3.5 → 지금 +6.5(홈 기준, +3점 반대 이동) · 10-11 08:35 PT 판</t>
+        </is>
+      </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:spread</t>
+          <t>2026_05_HOU_TEN:spread:A3</t>
         </is>
       </c>
     </row>
@@ -9673,15 +9707,15 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>HOU -1.5</t>
+          <t>HOU -6.5</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>-1.5</v>
+        <v>-6.5</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -9691,12 +9725,18 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="J138" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K138" t="n">
+        <v>67.7</v>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>W</t>
@@ -9708,17 +9748,17 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>0.353</v>
+        <v>0.909</v>
       </c>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>원 라인 -7.5 · 총점 37.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:spread:T</t>
+          <t>2026_05_HOU_TEN:spread:D</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9778,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>TEN +6.5</t>
+          <t>HOU -6.5</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -9756,15 +9796,19 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="J139" t="n">
+        <v>-6</v>
+      </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -9773,17 +9817,17 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>홈 TEN 결장 확정 · 개장 +3.5 → 지금 +6.5(홈 기준, +3점 반대 이동) · 10-11 08:35 PT 판</t>
+          <t>킥오프 전 판 1011-0833 서열표로 재생성(10/11 누수 복구)</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:spread:A3</t>
+          <t>2026_05_HOU_TEN:spread</t>
         </is>
       </c>
     </row>
@@ -9798,16 +9842,16 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>HOU -6.5</t>
+          <t>Under 37.5</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>-6.5</v>
+        <v>37.5</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -9824,15 +9868,9 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I140" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="J140" t="n">
-        <v>-6</v>
-      </c>
-      <c r="K140" t="n">
-        <v>67.7</v>
-      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
           <t>W</t>
@@ -9854,7 +9892,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:spread:D</t>
+          <t>2026_05_HOU_TEN:total:D</t>
         </is>
       </c>
     </row>
@@ -9864,25 +9902,25 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>HOU@TEN</t>
+          <t>IND@PIT</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Under 37.5</t>
+          <t>IND +8.5</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>37.5</v>
+        <v>8.5</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -9892,7 +9930,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>티저 다리(관찰)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -9900,26 +9938,26 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>HOU 26-3 TEN</t>
+          <t>IND 22-34 PIT</t>
         </is>
       </c>
       <c r="N141" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>원 라인 +2.5 · 총점 44.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>2026_05_HOU_TEN:total:D</t>
+          <t>2026_05_IND_PIT:spread:T</t>
         </is>
       </c>
     </row>
@@ -9939,15 +9977,15 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>IND +8.5</t>
+          <t>IND +3</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -9957,12 +9995,18 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="J142" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="K142" t="n">
+        <v>60.2</v>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>L</t>
@@ -9979,12 +10023,12 @@
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>원 라인 +2.5 · 총점 44.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>2026_05_IND_PIT:spread:T</t>
+          <t>2026_05_IND_PIT:spread:D</t>
         </is>
       </c>
     </row>
@@ -10008,7 +10052,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -10022,7 +10066,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I143" t="n">
@@ -10031,9 +10075,7 @@
       <c r="J143" t="n">
         <v>-3.4</v>
       </c>
-      <c r="K143" t="n">
-        <v>60.2</v>
-      </c>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
           <t>L</t>
@@ -10050,12 +10092,12 @@
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>킥오프 전 판 1011-0833 서열표로 재생성(10/11 누수 복구)</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>2026_05_IND_PIT:spread:D</t>
+          <t>2026_05_IND_PIT:spread</t>
         </is>
       </c>
     </row>
@@ -10075,7 +10117,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>Under 41.5</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -10093,21 +10135,21 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="J144" t="n">
-        <v>9.1</v>
+        <v>7.2</v>
       </c>
       <c r="K144" t="n">
-        <v>80.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -10116,13 +10158,17 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>2026_05_IND_PIT:total</t>
+          <t>2026_05_IND_PIT:total:D</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10188,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Under 41.5</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -10160,7 +10206,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -10169,12 +10215,10 @@
       <c r="J145" t="n">
         <v>7.2</v>
       </c>
-      <c r="K145" t="n">
-        <v>75.40000000000001</v>
-      </c>
+      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -10183,17 +10227,17 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>킥오프 전 판 1011-0833 서열표로 재생성(10/11 누수 복구)</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>2026_05_IND_PIT:total:D</t>
+          <t>2026_05_IND_PIT:total</t>
         </is>
       </c>
     </row>
@@ -10231,18 +10275,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I146" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="J146" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="K146" t="n">
-        <v>85.2</v>
-      </c>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
           <t>W</t>
@@ -10257,10 +10295,14 @@
         <v>0.909</v>
       </c>
       <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>언더독 LV 드라이브 득점 차 우위 +1.33 → 반대 NE · 10-11 08:35 PT 판</t>
+        </is>
+      </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:spread</t>
+          <t>2026_05_LV_NE:spread:A2</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10340,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -10320,12 +10362,12 @@
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>언더독 LV 드라이브 득점 차 우위 +1.33 → 반대 NE · 10-11 08:35 PT 판</t>
+          <t>홈 NE 결장 확정 · 개장 -8.5 → 지금 -3.5(홈 기준, +5점 반대 이동) · 10-11 08:35 PT 판</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:spread:A2</t>
+          <t>2026_05_LV_NE:spread:A3</t>
         </is>
       </c>
     </row>
@@ -10345,11 +10387,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NE -3.5</t>
+          <t>LV +3.5</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>-3.5</v>
+        <v>3.5</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -10363,15 +10405,21 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K148" t="n">
+        <v>78.90000000000001</v>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -10380,17 +10428,17 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>홈 NE 결장 확정 · 개장 -8.5 → 지금 -3.5(홈 기준, +5점 반대 이동) · 10-11 08:35 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:spread:A3</t>
+          <t>2026_05_LV_NE:spread:D</t>
         </is>
       </c>
     </row>
@@ -10410,11 +10458,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LV +3.5</t>
+          <t>NE -3.5</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>3.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -10428,7 +10476,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
         </is>
       </c>
       <c r="I149" t="n">
@@ -10437,12 +10485,10 @@
       <c r="J149" t="n">
         <v>10.4</v>
       </c>
-      <c r="K149" t="n">
-        <v>78.90000000000001</v>
-      </c>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -10451,17 +10497,17 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>킥오프 전 판 1011-0833 서열표로 재생성(10/11 누수 복구)</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>2026_05_LV_NE:spread:D</t>
+          <t>2026_05_LV_NE:spread</t>
         </is>
       </c>
     </row>
@@ -10542,25 +10588,25 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MIN@NO</t>
+          <t>LV@NE</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NO +8.5</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>8.5</v>
+        <v>45.5</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -10570,11 +10616,15 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>42</v>
+      </c>
+      <c r="J151" t="n">
+        <v>-3.5</v>
+      </c>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
@@ -10583,7 +10633,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>MIN 23-13 NO</t>
+          <t>LV 17-45 NE</t>
         </is>
       </c>
       <c r="N151" t="n">
@@ -10592,12 +10642,12 @@
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>원 라인 +2.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>킥오프 전 판 1011-0833 서열표로 재생성(10/11 누수 복구)</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>2026_05_MIN_NO:spread:T</t>
+          <t>2026_05_LV_NE:total</t>
         </is>
       </c>
     </row>
@@ -10617,15 +10667,15 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NO +2.5</t>
+          <t>NO +8.5</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -10635,7 +10685,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>티저 다리(관찰)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -10657,12 +10707,12 @@
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>원 라인 +2.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>2026_05_MIN_NO:spread:D</t>
+          <t>2026_05_MIN_NO:spread:T</t>
         </is>
       </c>
     </row>
@@ -10677,16 +10727,16 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Under 41.5</t>
+          <t>NO +2.5</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>41.5</v>
+        <v>2.5</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -10700,21 +10750,15 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I153" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="J153" t="n">
-        <v>-11.4</v>
-      </c>
-      <c r="K153" t="n">
-        <v>86.2</v>
-      </c>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -10723,13 +10767,17 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>2026_05_MIN_NO:total</t>
+          <t>2026_05_MIN_NO:spread:D</t>
         </is>
       </c>
     </row>
@@ -10810,21 +10858,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NYG@WAS</t>
+          <t>MIN@NO</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NYG +3.5</t>
+          <t>Under 41.5</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>-3.5</v>
+        <v>41.5</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -10842,14 +10890,12 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>-5</v>
+        <v>32.2</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="K155" t="n">
-        <v>74.3</v>
-      </c>
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
           <t>W</t>
@@ -10857,17 +10903,21 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>NYG 27-27 WAS</t>
+          <t>MIN 23-13 NO</t>
         </is>
       </c>
       <c r="N155" t="n">
         <v>0.909</v>
       </c>
       <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>킥오프 전 판 1011-0833 서열표로 재생성(10/11 누수 복구)</t>
+        </is>
+      </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>2026_05_NYG_WAS:spread</t>
+          <t>2026_05_MIN_NO:total</t>
         </is>
       </c>
     </row>
@@ -11018,16 +11068,16 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>NYG +3.5</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>41.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -11045,14 +11095,12 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>49.6</v>
+        <v>-5.5</v>
       </c>
       <c r="J158" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="K158" t="n">
-        <v>78</v>
-      </c>
+        <v>-9</v>
+      </c>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>W</t>
@@ -11067,10 +11115,14 @@
         <v>0.909</v>
       </c>
       <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>킥오프 전 판 1011-0833 서열표로 재생성(10/11 누수 복구)</t>
+        </is>
+      </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>2026_05_NYG_WAS:total</t>
+          <t>2026_05_NYG_WAS:spread</t>
         </is>
       </c>
     </row>
@@ -11151,25 +11203,25 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PHI@JAX</t>
+          <t>NYG@WAS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>JAX -1.5</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>-1.5</v>
+        <v>41.5</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>-283</t>
+          <t>-110</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11179,11 +11231,15 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>티저 다리(관찰)</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="J160" t="n">
+        <v>6.8</v>
+      </c>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
@@ -11192,21 +11248,21 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>PHI 17-19 JAX</t>
+          <t>NYG 27-27 WAS</t>
         </is>
       </c>
       <c r="N160" t="n">
-        <v>0.353</v>
+        <v>0.909</v>
       </c>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>원 라인 -7.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
+          <t>킥오프 전 판 1011-0833 서열표로 재생성(10/11 누수 복구)</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>2026_05_PHI_JAX:spread:T</t>
+          <t>2026_05_NYG_WAS:total</t>
         </is>
       </c>
     </row>
@@ -11226,15 +11282,15 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>PHI +7.5</t>
+          <t>JAX -1.5</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>7.5</v>
+        <v>-1.5</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-283</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -11244,7 +11300,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+          <t>티저 다리(관찰)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -11261,17 +11317,17 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>0.909</v>
+        <v>0.353</v>
       </c>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>원정 PHI 결장 확정 · 개장 +2.5 → 지금 -7.5(홈 기준, +10점 반대 이동) · 10-10 04:23 PT 판</t>
+          <t>원 라인 -7.5 · 총점 41.5 · 가격 미기록(2팀 −120 티저의 다리 환산 −283 · 손익분기 73.9%)</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>2026_05_PHI_JAX:spread:A3</t>
+          <t>2026_05_PHI_JAX:spread:T</t>
         </is>
       </c>
     </row>
@@ -11309,7 +11365,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -11331,12 +11387,12 @@
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>원정 PHI 결장 확정 · 개장 +2.5 → 지금 -7.5(홈 기준, +10점 반대 이동) · 10-10 04:23 PT 판</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>2026_05_PHI_JAX:spread:D</t>
+          <t>2026_05_PHI_JAX:spread:A3</t>
         </is>
       </c>
     </row>
@@ -11351,16 +11407,16 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>PHI +7.5</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>41.5</v>
+        <v>7.5</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -11382,7 +11438,7 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -11391,7 +11447,7 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
@@ -11401,7 +11457,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>2026_05_PHI_JAX:total:D</t>
+          <t>2026_05_PHI_JAX:spread:D</t>
         </is>
       </c>
     </row>
@@ -11411,21 +11467,21 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SF@SEA</t>
+          <t>PHI@JAX</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>SEA -3</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>-3</v>
+        <v>41.5</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -11439,7 +11495,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+          <t>방향(발행)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -11452,7 +11508,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>SF 32-29 SEA</t>
+          <t>PHI 17-19 JAX</t>
         </is>
       </c>
       <c r="N164" t="n">
@@ -11461,12 +11517,12 @@
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>언더독 SF 드라이브 득점 차 우위 +0.76 → 반대 SEA · 10-11 12:01 PT 판</t>
+          <t>발행 방향</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>2026_05_SF_SEA:spread:A2</t>
+          <t>2026_05_PHI_JAX:total:D</t>
         </is>
       </c>
     </row>
@@ -11486,11 +11542,11 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>SF +3</t>
+          <t>SEA -3</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -11504,21 +11560,15 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>방향(발행)</t>
-        </is>
-      </c>
-      <c r="I165" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="J165" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="K165" t="n">
-        <v>59.5</v>
-      </c>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -11527,17 +11577,17 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>0.909</v>
+        <v>-1</v>
       </c>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>발행 방향</t>
+          <t>언더독 SF 드라이브 득점 차 우위 +0.76 → 반대 SEA · 10-11 12:01 PT 판</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>2026_05_SF_SEA:spread:D</t>
+          <t>2026_05_SF_SEA:spread:A2</t>
         </is>
       </c>
     </row>
@@ -11552,16 +11602,16 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>SF +3</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>46.5</v>
+        <v>3</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -11578,9 +11628,15 @@
           <t>방향(발행)</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
+      <c r="I166" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="J166" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K166" t="n">
+        <v>59.5</v>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>W</t>
@@ -11602,7 +11658,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>2026_05_SF_SEA:total:D</t>
+          <t>2026_05_SF_SEA:spread:D</t>
         </is>
       </c>
     </row>
@@ -11640,18 +11696,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I167" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="J167" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K167" t="n">
-        <v>68.09999999999999</v>
-      </c>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>W</t>
@@ -11666,10 +11716,14 @@
         <v>0.909</v>
       </c>
       <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>2026_05_SF_SEA:total</t>
+          <t>2026_05_SF_SEA:total:D</t>
         </is>
       </c>
     </row>
@@ -11679,21 +11733,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TB@DAL</t>
+          <t>SF@SEA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>TB +9.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>-9.5</v>
+        <v>46.5</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -11707,18 +11761,16 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
+          <t>참고</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.6</v>
+        <v>51.1</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="K168" t="n">
-        <v>67.59999999999999</v>
-      </c>
+        <v>4.6</v>
+      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>W</t>
@@ -11726,17 +11778,21 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>TB 24-16 DAL</t>
+          <t>SF 32-29 SEA</t>
         </is>
       </c>
       <c r="N168" t="n">
         <v>0.909</v>
       </c>
       <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>킥오프 전 판 1011-1159 서열표로 재생성(10/11 누수 복구)</t>
+        </is>
+      </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>2026_05_TB_DAL:spread</t>
+          <t>2026_05_SF_SEA:total</t>
         </is>
       </c>
     </row>
@@ -11887,16 +11943,16 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>TB +8.5</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>49.5</v>
+        <v>-8.5</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -11914,17 +11970,15 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>53.3</v>
+        <v>5.4</v>
       </c>
       <c r="J171" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K171" t="n">
-        <v>64.2</v>
-      </c>
+        <v>-3.1</v>
+      </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -11933,13 +11987,17 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>-1</v>
+        <v>0.909</v>
       </c>
       <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>킥오프 전 판 1008-1551 서열표로 재생성(10/11 누수 복구)</t>
+        </is>
+      </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>2026_05_TB_DAL:total</t>
+          <t>2026_05_TB_DAL:spread</t>
         </is>
       </c>
     </row>
@@ -12011,6 +12069,1264 @@
       <c r="Q172" t="inlineStr">
         <is>
           <t>2026_05_TB_DAL:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>5</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>TB@DAL</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Over 48.5</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="J173" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>TB 24-16 DAL</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>킥오프 전 판 1008-1551 서열표로 재생성(10/11 누수 복구)</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>2026_05_TB_DAL:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>6</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>ARI@LA</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>LA -12.5</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="J174" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K174" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>2026_06_ARI_LA:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>6</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>ARI@LA</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Over 51.5</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="J175" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K175" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>2026_06_ARI_LA:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>6</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>BUF@LV</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>BUF -5.5</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="J176" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="K176" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>2026_06_BUF_LV:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>6</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>CAR@PHI</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>PHI +1.5</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J177" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K177" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>2026_06_CAR_PHI:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>6</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>CAR@PHI</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Over 39.5</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="J178" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="K178" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>2026_06_CAR_PHI:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>6</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>CHI@ATL</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ATL +1.5</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J179" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K179" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>2026_06_CHI_ATL:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>6</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>CHI@ATL</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Under 51.5</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="J180" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="K180" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>2026_06_CHI_ATL:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>6</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>DAL@GB</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>GB -1.5</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J181" t="n">
+        <v>7</v>
+      </c>
+      <c r="K181" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>2026_06_DAL_GB:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>6</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>DAL@GB</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Over 53.5</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="J182" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K182" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>2026_06_DAL_GB:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>6</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>LAC@KC</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>LAC +8.5</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>원정 LAC 결장 확정 · 개장 -2.5 → 지금 -8.5(홈 기준, +6점 반대 이동) · 10-14 16:40 PT 판</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>2026_06_LAC_KC:spread:A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>6</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>NO@NYG</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NYG +1.5</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J184" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K184" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>2026_06_NO_NYG:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>6</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>NO@NYG</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NO -1.5</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>언더독 NYG 드라이브 득점 차 우위 +0.51 → 반대 NO · 10-14 16:40 PT 판</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>2026_06_NO_NYG:spread:A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>6</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>NYJ@NE</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NE -7.5</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J186" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K186" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>2026_06_NYJ_NE:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>6</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>NYJ@NE</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Over 43.5</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="J187" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K187" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>2026_06_NYJ_NE:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>6</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>PIT@TB</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>TB +2.5</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>홈 TB 결장 확정 · 개장 -1.5 → 지금 +2.5(홈 기준, +4점 반대 이동) · 10-14 16:40 PT 판</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>2026_06_PIT_TB:spread:A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>6</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SEA@DEN</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>DEN +2.5</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J189" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K189" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>2026_06_SEA_DEN:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>6</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SEA@DEN</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Under 40.5</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>37</v>
+      </c>
+      <c r="J190" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="K190" t="n">
+        <v>63</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>2026_06_SEA_DEN:total</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>6</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>TEN@IND</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>IND -7</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J191" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K191" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>2026_06_TEN_IND:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>6</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>TEN@IND</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>TEN +7</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>7</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>원정 TEN 결장 확정 · 개장 -3.5 → 지금 -7(홈 기준, +3.5점 반대 이동) · 10-14 16:40 PT 판</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>2026_06_TEN_IND:spread:A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>6</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>WAS@SF</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SF -7.5</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J193" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K193" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>2026_06_WAS_SF:spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>6</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>WAS@SF</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Over 50.5</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>관찰(큰 괴리 — 페이퍼)</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="J194" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K194" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>2026_06_WAS_SF:total</t>
         </is>
       </c>
     </row>
@@ -12165,22 +13481,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C5" t="n">
         <v>37</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>63.8</v>
+        <v>60.7</v>
       </c>
       <c r="G5" t="n">
-        <v>12.63</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -12480,16 +13796,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G16" t="n">
         <v>0.07000000000000001</v>
@@ -12709,22 +14025,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>46.7</v>
+        <v>44.4</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.64</v>
+        <v>-2.73</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -12735,22 +14051,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>42.3</v>
+        <v>42.9</v>
       </c>
       <c r="G30" t="n">
-        <v>-5</v>
+        <v>-5.09</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -12761,22 +14077,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D31" t="n">
         <v>21</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>61.8</v>
+        <v>60.4</v>
       </c>
       <c r="G31" t="n">
-        <v>9.91</v>
+        <v>8.09</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q194"/>
+  <dimension ref="A1:Q198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -12147,25 +12147,23 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ARI@LA</t>
+          <t>BAL@CLE</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LA -12.5</t>
-        </is>
-      </c>
-      <c r="E174" t="n">
-        <v>-12.5</v>
-      </c>
+          <t>CLE ML</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>+142</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -12175,26 +12173,34 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I174" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="J174" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K174" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
+          <t>각도 관찰 A8(접전 .750+ 팀 → 그 팀 ML)</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>BAL 10-13 CLE</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>1.42</v>
+      </c>
       <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>CLE 한 포제션 경기 3-1(75%) · 10-18 09:02 PT 판</t>
+        </is>
+      </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>2026_06_ARI_LA:spread</t>
+          <t>2026_06_BAL_CLE:ml:A8</t>
         </is>
       </c>
     </row>
@@ -12204,21 +12210,21 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ARI@LA</t>
+          <t>BAL@CLE</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>BAL -3</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>51.5</v>
+        <v>-3</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -12232,26 +12238,34 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I175" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="J175" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K175" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>BAL 10-13 CLE</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>-1</v>
+      </c>
       <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>원정 BAL 결장 확정 · 개장 +6.5 → 지금 +3(홈 기준, +3.5점 반대 이동) · 10-18 09:02 PT 판</t>
+        </is>
+      </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>2026_06_ARI_LA:total</t>
+          <t>2026_06_BAL_CLE:spread:A3</t>
         </is>
       </c>
     </row>
@@ -12266,20 +12280,18 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>BUF -5.5</t>
-        </is>
-      </c>
-      <c r="E176" t="n">
-        <v>5.5</v>
-      </c>
+          <t>BUF ML</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-238</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -12289,26 +12301,34 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I176" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="J176" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="K176" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
+          <t>각도 관찰 A8(접전 .750+ 팀 → 그 팀 ML)</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>BUF 33-30 LV</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>0.42</v>
+      </c>
       <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>BUF 한 포제션 경기 3-1(75%) · 10-18 12:19 PT 판</t>
+        </is>
+      </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>2026_06_BUF_LV:spread</t>
+          <t>2026_06_BUF_LV:ml:A8</t>
         </is>
       </c>
     </row>
@@ -12318,25 +12338,23 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CAR@PHI</t>
+          <t>BUF@LV</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>PHI +1.5</t>
-        </is>
-      </c>
-      <c r="E177" t="n">
-        <v>1.5</v>
-      </c>
+          <t>BUF ML</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-238</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -12346,26 +12364,34 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I177" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J177" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K177" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
+          <t>관심(발행)</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>BUF 33-30 LV</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>0.42</v>
+      </c>
       <c r="O177" t="inlineStr"/>
-      <c r="P177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>발행 판단 소액 관심</t>
+        </is>
+      </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>2026_06_CAR_PHI:spread</t>
+          <t>2026_06_BUF_LV:ml:J</t>
         </is>
       </c>
     </row>
@@ -12380,16 +12406,16 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Over 39.5</t>
+          <t>PHI +3</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>39.5</v>
+        <v>3</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -12403,26 +12429,34 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I178" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="J178" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="K178" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>CAR 25-14 PHI</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>-1</v>
+      </c>
       <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>홈 PHI 결장 확정 · 개장 -6.5 → 지금 +3(홈 기준, +9.5점 반대 이동) · 10-18 09:02 PT 판</t>
+        </is>
+      </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>2026_06_CAR_PHI:total</t>
+          <t>2026_06_CAR_PHI:spread:A3</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12466,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>CHI@ATL</t>
+          <t>CAR@PHI</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -12442,11 +12476,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ATL +1.5</t>
+          <t>CAR -3</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1.5</v>
+        <v>-3</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -12460,26 +12494,34 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I179" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J179" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K179" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
+          <t>새 정보(판 이전·대조)</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>CAR 25-14 PHI</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>새 정보: PHI ★주전 OT Lane Johnson(스냅 100%) 개인 사유 결장 확정 · 발표 08:33 PT · 발표 뒤 라인 이동 +0점</t>
+        </is>
+      </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>2026_06_CHI_ATL:spread</t>
+          <t>2026_06_CAR_PHI:spread:NC</t>
         </is>
       </c>
     </row>
@@ -12494,16 +12536,16 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>CHI -1.5</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>51.5</v>
+        <v>-1.5</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -12517,26 +12559,34 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I180" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="J180" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="K180" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
+          <t>각도 관찰 A6(키 넘버 3·7 넘긴 이동 → 반대쪽 ATS)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>CHI 31-23 ATL</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>개장 +3 → 지금 +1.5(홈 기준) 키 넘버 넘김 · 이동 반대쪽 · 10-18 09:02 PT 판</t>
+        </is>
+      </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>2026_06_CHI_ATL:total</t>
+          <t>2026_06_CHI_ATL:spread:A6</t>
         </is>
       </c>
     </row>
@@ -12551,20 +12601,18 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>GB -1.5</t>
-        </is>
-      </c>
-      <c r="E181" t="n">
-        <v>-1.5</v>
-      </c>
+          <t>GB ML</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-108</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -12574,26 +12622,34 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I181" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J181" t="n">
-        <v>7</v>
-      </c>
-      <c r="K181" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
+          <t>각도 관찰 A4(작년 플옵팀 언더독 1~8주 → 그 팀 ML)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>DAL 13-23 GB</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>0.926</v>
+      </c>
       <c r="O181" t="inlineStr"/>
-      <c r="P181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>작년 플옵팀 GB 언더독(무비그 50% · 상대 DAL 비플옵) · 6주차 · 10-18 16:05 PT 판</t>
+        </is>
+      </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>2026_06_DAL_GB:spread</t>
+          <t>2026_06_DAL_GB:ml:A4</t>
         </is>
       </c>
     </row>
@@ -12608,16 +12664,16 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Over 53.5</t>
+          <t>GB +1.5</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>53.5</v>
+        <v>1.5</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -12631,26 +12687,34 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I182" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="J182" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="K182" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
+          <t>각도 관찰 A6(키 넘버 3·7 넘긴 이동 → 반대쪽 ATS)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>DAL 13-23 GB</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>개장 -3 → 지금 +1.5(홈 기준) 키 넘버 넘김 · 이동 반대쪽 · 10-18 16:05 PT 판</t>
+        </is>
+      </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>2026_06_DAL_GB:total</t>
+          <t>2026_06_DAL_GB:spread:A6</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12724,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LAC@KC</t>
+          <t>DAL@GB</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -12670,11 +12734,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LAC +8.5</t>
+          <t>GB +1.5</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -12694,18 +12758,28 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>DAL 13-23 GB</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>원정 LAC 결장 확정 · 개장 -2.5 → 지금 -8.5(홈 기준, +6점 반대 이동) · 10-14 16:40 PT 판</t>
+          <t>홈 GB 결장 확정 · 개장 -3 → 지금 +1.5(홈 기준, +4.5점 반대 이동) · 10-18 16:05 PT 판</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>2026_06_LAC_KC:spread:A3</t>
+          <t>2026_06_DAL_GB:spread:A3</t>
         </is>
       </c>
     </row>
@@ -12715,7 +12789,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>NO@NYG</t>
+          <t>HOU@JAX</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -12725,11 +12799,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NYG +1.5</t>
+          <t>HOU +2.5</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -12743,26 +12817,34 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I184" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J184" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K184" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>HOU 34-31 JAX</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>0.909</v>
+      </c>
       <c r="O184" t="inlineStr"/>
-      <c r="P184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>원정 HOU 결장 확정 · 개장 +1.5 → 지금 -2.5(홈 기준, +4점 반대 이동) · 10-17 19:12 PT 판</t>
+        </is>
+      </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>2026_06_NO_NYG:spread</t>
+          <t>2026_06_HOU_JAX:spread:A3</t>
         </is>
       </c>
     </row>
@@ -12772,25 +12854,23 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>NO@NYG</t>
+          <t>LAC@KC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NO -1.5</t>
-        </is>
-      </c>
-      <c r="E185" t="n">
-        <v>-1.5</v>
-      </c>
+          <t>LAC ML</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>+330</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -12800,24 +12880,34 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>각도 관찰 A2(드라이브 우위 언더독 반대)</t>
+          <t>각도 관찰 A4(작년 플옵팀 언더독 1~8주 → 그 팀 ML)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>LAC 6-22 KC</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>-1</v>
+      </c>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>언더독 NYG 드라이브 득점 차 우위 +0.51 → 반대 NO · 10-14 16:40 PT 판</t>
+          <t>작년 플옵팀 LAC 언더독(무비그 22% · 상대 KC 비플옵) · 6주차 · 10-18 12:19 PT 판</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>2026_06_NO_NYG:spread:A2</t>
+          <t>2026_06_LAC_KC:ml:A4</t>
         </is>
       </c>
     </row>
@@ -12827,25 +12917,23 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>NYJ@NE</t>
+          <t>LAC@KC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NE -7.5</t>
-        </is>
-      </c>
-      <c r="E186" t="n">
-        <v>-7.5</v>
-      </c>
+          <t>KC ML</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-425</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -12855,26 +12943,34 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I186" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="J186" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="K186" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
+          <t>각도 관찰 A5(3rd down 운 회귀 5~9주 → 상대 ML)</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>LAC 6-22 KC</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>0.235</v>
+      </c>
       <c r="O186" t="inlineStr"/>
-      <c r="P186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>LAC 3rd down 21위 vs 공격 EPA 32위(+11) → 상대 KC · 6주차 · 10-18 12:19 PT 판</t>
+        </is>
+      </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>2026_06_NYJ_NE:spread</t>
+          <t>2026_06_LAC_KC:ml:A5</t>
         </is>
       </c>
     </row>
@@ -12884,21 +12980,21 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NYJ@NE</t>
+          <t>LAC@KC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>LAC +7.5</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>43.5</v>
+        <v>7.5</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -12912,26 +13008,34 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I187" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="J187" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K187" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>LAC 6-22 KC</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>-1</v>
+      </c>
       <c r="O187" t="inlineStr"/>
-      <c r="P187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>원정 LAC 결장 확정 · 개장 -2.5 → 지금 -7.5(홈 기준, +5점 반대 이동) · 10-18 12:19 PT 판</t>
+        </is>
+      </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>2026_06_NYJ_NE:total</t>
+          <t>2026_06_LAC_KC:spread:A3</t>
         </is>
       </c>
     </row>
@@ -12941,7 +13045,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PIT@TB</t>
+          <t>LAC@KC</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -12951,11 +13055,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>TB +2.5</t>
+          <t>LAC +7.5</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -12969,24 +13073,34 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+          <t>각도 관찰 A6(키 넘버 3·7 넘긴 이동 → 반대쪽 ATS)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>LAC 6-22 KC</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>-1</v>
+      </c>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>홈 TB 결장 확정 · 개장 -1.5 → 지금 +2.5(홈 기준, +4점 반대 이동) · 10-14 16:40 PT 판</t>
+          <t>개장 -2.5 → 지금 -7.5(홈 기준) 키 넘버 넘김 · 이동 반대쪽 · 10-18 12:19 PT 판</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>2026_06_PIT_TB:spread:A3</t>
+          <t>2026_06_LAC_KC:spread:A6</t>
         </is>
       </c>
     </row>
@@ -12996,25 +13110,23 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SEA@DEN</t>
+          <t>NO@NYG</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>DEN +2.5</t>
-        </is>
-      </c>
-      <c r="E189" t="n">
-        <v>2.5</v>
-      </c>
+          <t>NYG ML</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-112</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -13024,26 +13136,34 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I189" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J189" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K189" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
+          <t>각도 관찰 A5(3rd down 운 회귀 5~9주 → 상대 ML)</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>NO 34-27 NYG</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>-1</v>
+      </c>
       <c r="O189" t="inlineStr"/>
-      <c r="P189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>NO 3rd down 7위 vs 공격 EPA 23위(+16) → 상대 NYG · 6주차 · 10-18 09:02 PT 판</t>
+        </is>
+      </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>2026_06_SEA_DEN:spread</t>
+          <t>2026_06_NO_NYG:ml:A5</t>
         </is>
       </c>
     </row>
@@ -13053,25 +13173,23 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SEA@DEN</t>
+          <t>NO@NYG</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Under 40.5</t>
-        </is>
-      </c>
-      <c r="E190" t="n">
-        <v>40.5</v>
-      </c>
+          <t>NYG ML</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-112</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -13081,26 +13199,34 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="I190" t="n">
-        <v>37</v>
-      </c>
-      <c r="J190" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="K190" t="n">
-        <v>63</v>
-      </c>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
+          <t>관심(발행)</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>NO 34-27 NYG</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>-1</v>
+      </c>
       <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>발행 판단 소액 관심</t>
+        </is>
+      </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>2026_06_SEA_DEN:total</t>
+          <t>2026_06_NO_NYG:ml:J</t>
         </is>
       </c>
     </row>
@@ -13110,7 +13236,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TEN@IND</t>
+          <t>NO@NYG</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -13120,11 +13246,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>IND -7</t>
+          <t>NYG +1.5</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>-7</v>
+        <v>1.5</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -13138,26 +13264,34 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I191" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J191" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K191" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>NO 34-27 NYG</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>-1</v>
+      </c>
       <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>홈 NYG 결장 확정 · 개장 -2.5 → 지금 +1.5(홈 기준, +4점 반대 이동) · 10-18 09:02 PT 판</t>
+        </is>
+      </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>2026_06_TEN_IND:spread</t>
+          <t>2026_06_NO_NYG:spread:A3</t>
         </is>
       </c>
     </row>
@@ -13167,25 +13301,23 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TEN@IND</t>
+          <t>PIT@TB</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>TEN +7</t>
-        </is>
-      </c>
-      <c r="E192" t="n">
-        <v>7</v>
-      </c>
+          <t>PIT ML</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-130</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -13195,24 +13327,34 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+          <t>각도 관찰 A5(3rd down 운 회귀 5~9주 → 상대 ML)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>PIT 26-19 TB</t>
+        </is>
+      </c>
+      <c r="N192" t="n">
+        <v>0.769</v>
+      </c>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>원정 TEN 결장 확정 · 개장 -3.5 → 지금 -7(홈 기준, +3.5점 반대 이동) · 10-14 16:40 PT 판</t>
+          <t>TB 3rd down 16위 vs 공격 EPA 27위(+11) → 상대 PIT · 6주차 · 10-18 09:02 PT 판</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>2026_06_TEN_IND:spread:A3</t>
+          <t>2026_06_PIT_TB:ml:A5</t>
         </is>
       </c>
     </row>
@@ -13222,25 +13364,23 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>WAS@SF</t>
+          <t>PIT@TB</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>SF -7.5</t>
-        </is>
-      </c>
-      <c r="E193" t="n">
-        <v>-7.5</v>
-      </c>
+          <t>PIT ML</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-130</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -13250,26 +13390,34 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I193" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J193" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K193" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
+          <t>관심(발행)</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>PIT 26-19 TB</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>0.769</v>
+      </c>
       <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>발행 판단 소액 관심</t>
+        </is>
+      </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>2026_06_WAS_SF:spread</t>
+          <t>2026_06_PIT_TB:ml:J</t>
         </is>
       </c>
     </row>
@@ -13279,54 +13427,334 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
+          <t>PIT@TB</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>TB +1.5</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>PIT 26-19 TB</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>홈 TB 결장 확정 · 개장 -1.5 → 지금 +1.5(홈 기준, +3점 반대 이동) · 10-18 09:02 PT 판</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>2026_06_PIT_TB:spread:A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>6</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SEA@DEN</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DEN +2.5</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J195" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K195" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>SEA 14-17 DEN</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>2026_06_SEA_DEN:spread:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>6</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SEA@DEN</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Under 40.5</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>방향(발행)</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>37</v>
+      </c>
+      <c r="J196" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="K196" t="n">
+        <v>63</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>SEA 14-17 DEN</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>발행 방향</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>2026_06_SEA_DEN:total:D</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>6</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>TEN@IND</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>TEN +6.5</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>TEN 26-20 IND</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>원정 TEN 결장 확정 · 개장 -3.5 → 지금 -6.5(홈 기준, +3점 반대 이동) · 10-18 09:02 PT 판</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>2026_06_TEN_IND:spread:A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>6</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
           <t>WAS@SF</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Over 50.5</t>
-        </is>
-      </c>
-      <c r="E194" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>-110</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>suggested</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>관찰(큰 괴리 — 페이퍼)</t>
-        </is>
-      </c>
-      <c r="I194" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="J194" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="K194" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>2026_06_WAS_SF:total</t>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>WAS +7.5</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>각도 관찰 A6(키 넘버 3·7 넘긴 이동 → 반대쪽 ATS)</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>WAS 17-23 SF</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>개장 -5.5 → 지금 -7.5(홈 기준) 키 넘버 넘김 · 이동 반대쪽 · 10-19 13:23 PT 판</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>2026_06_WAS_SF:spread:A6</t>
         </is>
       </c>
     </row>
@@ -13427,19 +13855,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
+      <c r="F3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -13454,10 +13885,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
         <v>32</v>
@@ -13466,7 +13897,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>-11.09</v>
+        <v>-9.27</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -13715,22 +14146,22 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
         <v>7</v>
-      </c>
-      <c r="C13" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>71.40000000000001</v>
+        <v>53.3</v>
       </c>
       <c r="G13" t="n">
-        <v>2.54</v>
+        <v>0.27</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -13796,19 +14227,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -13999,22 +14430,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C28" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D28" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>50.8</v>
+        <v>53.4</v>
       </c>
       <c r="G28" t="n">
-        <v>-9.94</v>
+        <v>-7.62</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -14025,10 +14456,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
         <v>10</v>
@@ -14037,10 +14468,10 @@
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>44.4</v>
+        <v>47.4</v>
       </c>
       <c r="G29" t="n">
-        <v>-2.73</v>
+        <v>-1.82</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -14051,10 +14482,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D30" t="n">
         <v>16</v>
@@ -14063,10 +14494,10 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>42.9</v>
+        <v>44.8</v>
       </c>
       <c r="G30" t="n">
-        <v>-5.09</v>
+        <v>-4.18</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -14107,7 +14538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14358,6 +14789,44 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/NFL_픽_추적기.xlsx
+++ b/data/NFL_픽_추적기.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q198"/>
+  <dimension ref="A1:Q232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -13758,6 +13758,2180 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>7</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>CIN@BAL</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>BAL ML</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>+124</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>각도 관찰 A10(색률 상위 8 수비 팀의 상대 → 상대 ML)</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>CIN 35-13 BAL</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>CIN 색률 8.7%(3위) → 상대 BAL · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>2026_07_CIN_BAL:ml:A10</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>7</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>CIN@BAL</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>BAL +3</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>3</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>CIN 35-13 BAL</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>홈 BAL 결장 확정 · 개장 -3.5 → 지금 +3(홈 기준, +6.5점 반대 이동) · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>2026_07_CIN_BAL:spread:A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>7</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>CLE@TEN</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CLE ML</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-135</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>각도 관찰 A10(색률 상위 8 수비 팀의 상대 → 상대 ML)</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>CLE 27-24 TEN</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>TEN 색률 7.5%(7위) → 상대 CLE · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>2026_07_CLE_TEN:ml:A10</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>7</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>CLE@TEN</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CLE ML</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-135</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>각도 관찰 A8(접전 .750+ 팀 → 그 팀 ML)</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>CLE 27-24 TEN</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>CLE 한 포제션 경기 4-1(80%) · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>2026_07_CLE_TEN:ml:A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>7</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>CLE@TEN</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CLE ML</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-135</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>관심(발행)</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>CLE 27-24 TEN</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>발행 판단 소액 관심</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>2026_07_CLE_TEN:ml:J</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>7</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>DAL@PHI</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>PHI ML</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>+185</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>각도 관찰 A4(작년 플옵팀 언더독 1~8주 → 그 팀 ML)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>DAL 38-21 PHI</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>작년 플옵팀 PHI 언더독(무비그 34% · 상대 DAL 비플옵) · 7주차 · 10-26 17:07 PT 판</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>2026_07_DAL_PHI:ml:A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>7</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>DAL@PHI</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>PHI +4.5</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>DAL 38-21 PHI</t>
+        </is>
+      </c>
+      <c r="N205" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>홈 PHI 결장 확정 · 개장 -3 → 지금 +4.5(홈 기준, +7.5점 반대 이동) · 10-26 17:07 PT 판</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>2026_07_DAL_PHI:spread:A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>7</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>DEN@ARI</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>DEN ML</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-238</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>각도 관찰 A8(접전 .750+ 팀 → 그 팀 ML)</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>DEN 30-16 ARI</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>DEN 한 포제션 경기 4-0(100%) · 10-25 12:22 PT 판</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>2026_07_DEN_ARI:ml:A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>7</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>DEN@ARI</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DEN -4.5</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>각도 관찰 A6(키 넘버 3·7 넘긴 이동 → 반대쪽 ATS)</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>DEN 30-16 ARI</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>개장 +7.5 → 지금 +4.5(홈 기준) 키 넘버 넘김 · 이동 반대쪽 · 10-25 12:22 PT 판</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>2026_07_DEN_ARI:spread:A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>7</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>DEN@ARI</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>DEN -4.5</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>DEN 30-16 ARI</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>원정 DEN 결장 확정 · 개장 +7.5 → 지금 +4.5(홈 기준, +3점 반대 이동) · 10-25 12:22 PT 판</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>2026_07_DEN_ARI:spread:A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>7</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>GB@DET</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>GB ML</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>+160</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>각도 관찰 A4(작년 플옵팀 언더독 1~8주 → 그 팀 ML)</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>GB 17-20 DET</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>작년 플옵팀 GB 언더독(무비그 37% · 상대 DET 비플옵) · 7주차 · 10-25 12:22 PT 판</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>2026_07_GB_DET:ml:A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>7</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>GB@DET</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>GB ML</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>+160</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>각도 관찰 A10(색률 상위 8 수비 팀의 상대 → 상대 ML)</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>GB 17-20 DET</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>DET 색률 8.2%(4위) → 상대 GB · 10-25 12:22 PT 판</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>2026_07_GB_DET:ml:A10</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>7</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>GB@DET</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>GB +3.5</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>각도 관찰 A6(키 넘버 3·7 넘긴 이동 → 반대쪽 ATS)</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>GB 17-20 DET</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>개장 -1.5 → 지금 -3.5(홈 기준) 키 넘버 넘김 · 이동 반대쪽 · 10-25 12:22 PT 판</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>2026_07_GB_DET:spread:A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>7</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>IND@MIN</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>IND ML</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>+260</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>각도 관찰 A5(3rd down 운 회귀 5~9주 → 상대 ML)</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>IND 10-16 MIN</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>MIN 3rd down 14위 vs 공격 EPA 27위(+13) → 상대 IND · 7주차 · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>2026_07_IND_MIN:ml:A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>7</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>IND@MIN</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>IND ML</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>+260</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>각도 관찰 A10(색률 상위 8 수비 팀의 상대 → 상대 ML)</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>IND 10-16 MIN</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>MIN 색률 9.5%(1위) → 상대 IND · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>2026_07_IND_MIN:ml:A10</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>7</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>IND@MIN</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>IND +6.5</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>IND 10-16 MIN</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>원정 IND 결장 확정 · 개장 -3 → 지금 -6.5(홈 기준, +3.5점 반대 이동) · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>2026_07_IND_MIN:spread:A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>7</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>KC@SEA</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>KC ML</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>+130</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>각도 관찰 A10(색률 상위 8 수비 팀의 상대 → 상대 ML)</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>KC 3-20 SEA</t>
+        </is>
+      </c>
+      <c r="N215" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>SEA 색률 7.5%(8위) → 상대 KC · 10-25 16:17 PT 판</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>2026_07_KC_SEA:ml:A10</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>7</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>LA@LV</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>LA -3.5</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>각도 관찰 A6(키 넘버 3·7 넘긴 이동 → 반대쪽 ATS)</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>LA 35-21 LV</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>개장 +7.5 → 지금 +3.5(홈 기준) 키 넘버 넘김 · 이동 반대쪽 · 10-25 12:22 PT 판</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>2026_07_LA_LV:spread:A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>7</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>LA@LV</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>LA -3.5</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>LA 35-21 LV</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>원정 LA 결장 확정 · 개장 +7.5 → 지금 +3.5(홈 기준, +4점 반대 이동) · 10-25 12:22 PT 판</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>2026_07_LA_LV:spread:A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>7</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>MIA@NYJ</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>NYJ ML</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-218</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>각도 관찰 A5(3rd down 운 회귀 5~9주 → 상대 ML)</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>MIA 28-25 NYJ</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>MIA 3rd down 11위 vs 공격 EPA 28위(+17) → 상대 NYJ · 7주차 · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>2026_07_MIA_NYJ:ml:A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>7</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>MIA@NYJ</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>MIA ML</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>+180</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>각도 관찰 A10(색률 상위 8 수비 팀의 상대 → 상대 ML)</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>MIA 28-25 NYJ</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>NYJ 색률 7.7%(6위) → 상대 MIA · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>2026_07_MIA_NYJ:ml:A10</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>7</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>MIA@NYJ</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>NYJ ML</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-218</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>관심(발행)</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>MIA 28-25 NYJ</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>발행 판단 소액 관심</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>2026_07_MIA_NYJ:ml:J</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>7</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>MIA@NYJ</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>MIA +3.5</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>각도 관찰 A6(키 넘버 3·7 넘긴 이동 → 반대쪽 ATS)</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>MIA 28-25 NYJ</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>개장 -2.5 → 지금 -3.5(홈 기준) 키 넘버 넘김 · 이동 반대쪽 · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>2026_07_MIA_NYJ:spread:A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>7</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>NE@CHI</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>NE ML</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>+130</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>각도 관찰 A10(색률 상위 8 수비 팀의 상대 → 상대 ML)</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>NE 24-30 CHI</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>CHI 색률 8.9%(2위) → 상대 NE · 10-22 10:12 PT 판</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>2026_07_NE_CHI:ml:A10</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>7</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>NE@CHI</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>NE +3</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>3</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>각도 관찰 A6(키 넘버 3·7 넘긴 이동 → 반대쪽 ATS)</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>NE 24-30 CHI</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>개장 -1.5 → 지금 -3(홈 기준) 키 넘버 넘김 · 이동 반대쪽 · 10-22 10:12 PT 판</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>2026_07_NE_CHI:spread:A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>7</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>NYG@HOU</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>NYG +10.5</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>각도 관찰 A6(키 넘버 3·7 넘긴 이동 → 반대쪽 ATS)</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>NYG 27-21 HOU</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>개장 -5.5 → 지금 -10.5(홈 기준) 키 넘버 넘김 · 이동 반대쪽 · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>2026_07_NYG_HOU:spread:A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>7</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>NYG@HOU</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>NYG +10.5</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>NYG 27-21 HOU</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>원정 NYG 결장 확정 · 개장 -5.5 → 지금 -10.5(홈 기준, +5점 반대 이동) · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>2026_07_NYG_HOU:spread:A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>7</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>PIT@NO</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>PIT ML</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-175</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>각도 관찰 A8(접전 .750+ 팀 → 그 팀 ML)</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>PIT 16-10 NO</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>PIT 한 포제션 경기 3-1(75%) · 10-22 10:12 PT 판</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>2026_07_PIT_NO:ml:A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>7</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>PIT@NO</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>NO +3.5</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>각도 관찰 A6(키 넘버 3·7 넘긴 이동 → 반대쪽 ATS)</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>PIT 16-10 NO</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>개장 +2.5 → 지금 +3.5(홈 기준) 키 넘버 넘김 · 이동 반대쪽 · 10-22 10:12 PT 판</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>2026_07_PIT_NO:spread:A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>7</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>SF@ATL</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>SF -2.5</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>각도 관찰 A6(키 넘버 3·7 넘긴 이동 → 반대쪽 ATS)</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>SF 20-29 ATL</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>개장 +4.5 → 지금 +2.5(홈 기준) 키 넘버 넘김 · 이동 반대쪽 · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>2026_07_SF_ATL:spread:A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>7</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>TB@CAR</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>CAR ML</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>-166</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>각도 관찰 A5(3rd down 운 회귀 5~9주 → 상대 ML)</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>TB 43-13 CAR</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>TB 3rd down 19위 vs 공격 EPA 29위(+10) → 상대 CAR · 7주차 · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>2026_07_TB_CAR:ml:A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>7</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>TB@CAR</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>CAR ML</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-166</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>관심(발행)</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>TB 43-13 CAR</t>
+        </is>
+      </c>
+      <c r="N230" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>발행 판단 소액 관심</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>2026_07_TB_CAR:ml:J</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>7</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>TB@CAR</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>TB +3</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>3</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>각도 관찰 A3(결장 팀 반대 3점+ 이동 → 결장 팀)</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>TB 43-13 CAR</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>원정 TB 결장 확정 · 개장 +1.5 → 지금 -3(홈 기준, +4.5점 반대 이동) · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>2026_07_TB_CAR:spread:A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>7</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>TB@CAR</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>TB +3</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>3</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>각도 관찰 A6(키 넘버 3·7 넘긴 이동 → 반대쪽 ATS)</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>TB 43-13 CAR</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>개장 +1.5 → 지금 -3(홈 기준) 키 넘버 넘김 · 이동 반대쪽 · 10-25 08:51 PT 판</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>2026_07_TB_CAR:spread:A6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13855,22 +16029,22 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>0.19</v>
+        <v>-1.07</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -14146,22 +16320,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>53.3</v>
+        <v>59.1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.27</v>
+        <v>2.82</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -14430,22 +16604,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="C28" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>53.4</v>
+        <v>52.5</v>
       </c>
       <c r="G28" t="n">
-        <v>-7.62</v>
+        <v>-9.6</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -14538,7 +16712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14827,6 +17001,44 @@
         <v>0.19</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-1.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
